--- a/optimize_prep/output/approx_accuracy_report.xlsx
+++ b/optimize_prep/output/approx_accuracy_report.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,10 +522,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50349451</v>
+        <v>50471836</v>
       </c>
       <c r="K2" t="n">
-        <v>50349451</v>
+        <v>50471836</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -569,10 +569,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-58827279</v>
+        <v>-57138860</v>
       </c>
       <c r="K3" t="n">
-        <v>-58827279</v>
+        <v>-57138860</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -598,28 +598,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>74180457</v>
+        <v>73602100</v>
       </c>
       <c r="E4" t="n">
-        <v>74180457</v>
+        <v>73602100</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G4" t="n">
-        <v>67065095</v>
+        <v>66390593</v>
       </c>
       <c r="H4" t="n">
-        <v>-9.59</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>7115361</v>
+        <v>7211507</v>
       </c>
       <c r="J4" t="n">
-        <v>1036983884</v>
+        <v>1038312661</v>
       </c>
       <c r="K4" t="n">
-        <v>1036983884</v>
+        <v>1038312661</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -645,34 +645,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>206478001</v>
+        <v>205495042</v>
       </c>
       <c r="E5" t="n">
-        <v>206478001</v>
+        <v>205495042</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>147240652</v>
+        <v>144776148</v>
       </c>
       <c r="H5" t="n">
-        <v>-28.69</v>
+        <v>-29.55</v>
       </c>
       <c r="I5" t="n">
-        <v>59237349</v>
+        <v>60718894</v>
       </c>
       <c r="J5" t="n">
-        <v>2990155179</v>
+        <v>2991506171</v>
       </c>
       <c r="K5" t="n">
-        <v>2990155179</v>
+        <v>2991506171</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -692,34 +692,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>78416098</v>
+        <v>78402720</v>
       </c>
       <c r="E6" t="n">
-        <v>78416098</v>
+        <v>78402720</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G6" t="n">
-        <v>70076523</v>
+        <v>70098101</v>
       </c>
       <c r="H6" t="n">
-        <v>-10.64</v>
+        <v>-10.59</v>
       </c>
       <c r="I6" t="n">
-        <v>8339575</v>
+        <v>8304619</v>
       </c>
       <c r="J6" t="n">
-        <v>721902182</v>
+        <v>725257243</v>
       </c>
       <c r="K6" t="n">
-        <v>721902182</v>
+        <v>725257243</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -739,28 +739,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>278238770</v>
+        <v>277875695</v>
       </c>
       <c r="E7" t="n">
-        <v>278238770</v>
+        <v>277875695</v>
       </c>
       <c r="F7" t="n">
         <v>-0</v>
       </c>
       <c r="G7" t="n">
-        <v>247518062</v>
+        <v>246758061</v>
       </c>
       <c r="H7" t="n">
-        <v>-11.04</v>
+        <v>-11.2</v>
       </c>
       <c r="I7" t="n">
-        <v>30720708</v>
+        <v>31117634</v>
       </c>
       <c r="J7" t="n">
-        <v>2175577674</v>
+        <v>2167298715</v>
       </c>
       <c r="K7" t="n">
-        <v>2175577674</v>
+        <v>2167298715</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -786,34 +786,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>77172037</v>
+        <v>51875442</v>
       </c>
       <c r="E8" t="n">
-        <v>77172037</v>
+        <v>51875442</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>75068206</v>
+        <v>51788172</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.73</v>
+        <v>-0.17</v>
       </c>
       <c r="I8" t="n">
-        <v>2103831</v>
+        <v>87271</v>
       </c>
       <c r="J8" t="n">
-        <v>1259866486</v>
+        <v>838672584</v>
       </c>
       <c r="K8" t="n">
-        <v>1259866486</v>
+        <v>838672584</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -833,40 +833,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>81247053</v>
+        <v>91020058</v>
       </c>
       <c r="E9" t="n">
-        <v>81247053</v>
+        <v>91020058</v>
       </c>
       <c r="F9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>72617609</v>
+        <v>81947554</v>
       </c>
       <c r="H9" t="n">
-        <v>-10.62</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>8629444</v>
+        <v>9072504</v>
       </c>
       <c r="J9" t="n">
-        <v>1422578358</v>
+        <v>1611121593</v>
       </c>
       <c r="K9" t="n">
-        <v>1422578358</v>
+        <v>1611121593</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -880,26 +880,32 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>20426849</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+        <v>20426849</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>23320287</v>
+      </c>
+      <c r="H10" t="n">
+        <v>14.16</v>
+      </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-2893438</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>400010075</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>400010075</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -907,7 +913,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -921,32 +927,26 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>41989220</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>41989220</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>27964026</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-33.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>14025194</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>626857183</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>626857183</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -954,12 +954,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -968,31 +968,31 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-63413740</v>
+        <v>41229538</v>
       </c>
       <c r="E12" t="n">
-        <v>-63413740</v>
+        <v>41229538</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-57540771</v>
+        <v>26940434</v>
       </c>
       <c r="H12" t="n">
-        <v>9.26</v>
+        <v>-34.66</v>
       </c>
       <c r="I12" t="n">
-        <v>-5872969</v>
+        <v>14289104</v>
       </c>
       <c r="J12" t="n">
-        <v>-1080387059</v>
+        <v>626098087</v>
       </c>
       <c r="K12" t="n">
-        <v>-1080387059</v>
+        <v>626098087</v>
       </c>
       <c r="L12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1001,12 +1001,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1015,26 +1015,32 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-68203209</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>-68203209</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>-62888069</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7.79</v>
+      </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-5315140</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-1214846259</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>-1214846259</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1042,7 +1048,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1083,7 +1089,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1124,12 +1130,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1152,14 +1158,12 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-3011963542</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-3011963542</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -1167,7 +1171,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1181,28 +1185,24 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-115085</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-115085</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>-115085</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-399999852</v>
+        <v>-3022423710</v>
       </c>
       <c r="K17" t="n">
-        <v>-399999852</v>
+        <v>-3022423710</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1214,7 +1214,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1228,28 +1228,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-87071005</v>
+        <v>-115085</v>
       </c>
       <c r="E18" t="n">
-        <v>-87071005</v>
+        <v>-115085</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-79255647</v>
+        <v>-115085</v>
       </c>
       <c r="H18" t="n">
-        <v>8.98</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-7815358</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-1795494097</v>
+        <v>-399999852</v>
       </c>
       <c r="K18" t="n">
-        <v>-1795494097</v>
+        <v>-399999852</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1261,12 +1261,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1275,28 +1275,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11135708</v>
+        <v>-87065677</v>
       </c>
       <c r="E19" t="n">
-        <v>11135708</v>
+        <v>-87065677</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>6305175</v>
+        <v>-79056914</v>
       </c>
       <c r="H19" t="n">
-        <v>-43.38</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>4830533</v>
+        <v>-8008763</v>
       </c>
       <c r="J19" t="n">
-        <v>200004769</v>
+        <v>-1795481344</v>
       </c>
       <c r="K19" t="n">
-        <v>200004769</v>
+        <v>-1795481344</v>
       </c>
       <c r="L19" t="n">
         <v>-0</v>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1322,28 +1322,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-22955959</v>
+        <v>11590471</v>
       </c>
       <c r="E20" t="n">
-        <v>-22955959</v>
+        <v>11590471</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-12610002</v>
+        <v>6304945</v>
       </c>
       <c r="H20" t="n">
-        <v>45.07</v>
+        <v>-45.6</v>
       </c>
       <c r="I20" t="n">
-        <v>-10345957</v>
+        <v>5285526</v>
       </c>
       <c r="J20" t="n">
-        <v>-400005649</v>
+        <v>200002790</v>
       </c>
       <c r="K20" t="n">
-        <v>-400005649</v>
+        <v>200002790</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1355,47 +1355,94 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>7900</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-23147982</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-23147982</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-12610003</v>
+      </c>
+      <c r="H21" t="n">
+        <v>45.52</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-10537979</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-400005771</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-400005771</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>8000</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>-56107546</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>-56107546</v>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
         <v>-56107546</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-1563341059</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-1563341059</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-1566608815</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-1566608815</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1410,7 +1457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:N148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,16 +1565,16 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>360914</v>
+        <v>362910</v>
       </c>
       <c r="K2" t="n">
-        <v>360914</v>
+        <v>362910</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>360914</v>
+        <v>362910</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -1566,16 +1613,16 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>810111</v>
+        <v>812915</v>
       </c>
       <c r="K3" t="n">
-        <v>810111</v>
+        <v>812915</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>810111</v>
+        <v>812915</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -1614,19 +1661,19 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>2056670</v>
+        <v>2063806</v>
       </c>
       <c r="K4" t="n">
-        <v>2056670</v>
+        <v>2063806</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>2056670</v>
+        <v>2063806</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -1662,16 +1709,16 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>-1954751</v>
+        <v>-1961472</v>
       </c>
       <c r="K5" t="n">
-        <v>-1954751</v>
+        <v>-1961472</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1954751</v>
+        <v>-1961472</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1710,19 +1757,19 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>489260</v>
+        <v>490284</v>
       </c>
       <c r="K6" t="n">
-        <v>489260</v>
+        <v>490284</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M6" t="n">
-        <v>489260</v>
+        <v>490284</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="7">
@@ -1758,16 +1805,16 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>-484128</v>
+        <v>-485140</v>
       </c>
       <c r="K7" t="n">
-        <v>-484128</v>
+        <v>-485140</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-484128</v>
+        <v>-485140</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1806,16 +1853,16 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>-570938</v>
+        <v>-573587</v>
       </c>
       <c r="K8" t="n">
-        <v>-570938</v>
+        <v>-573587</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-570938</v>
+        <v>-573587</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1858,16 +1905,16 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>9566775</v>
+        <v>9605830</v>
       </c>
       <c r="K9" t="n">
-        <v>9566775</v>
+        <v>9605830</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>9566775</v>
+        <v>9605830</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1910,16 +1957,16 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>8499741</v>
+        <v>8546347</v>
       </c>
       <c r="K10" t="n">
-        <v>8499741</v>
+        <v>8546347</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>8499741</v>
+        <v>8546347</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1962,16 +2009,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>21713941</v>
+        <v>21829742</v>
       </c>
       <c r="K11" t="n">
-        <v>21713941</v>
+        <v>21829742</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>21713941</v>
+        <v>21829742</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -2014,16 +2061,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-20194456</v>
+        <v>-20299034</v>
       </c>
       <c r="K12" t="n">
-        <v>-20194456</v>
+        <v>-20299034</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-20194456</v>
+        <v>-20299034</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2066,16 +2113,16 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-51313</v>
+        <v>-37802</v>
       </c>
       <c r="K13" t="n">
-        <v>-51313</v>
+        <v>-37802</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-51313</v>
+        <v>-37802</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2118,19 +2165,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>54834</v>
+        <v>45354</v>
       </c>
       <c r="K14" t="n">
-        <v>54834</v>
+        <v>45354</v>
       </c>
       <c r="L14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>54834</v>
+        <v>45354</v>
       </c>
       <c r="N14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2170,16 +2217,16 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-11217720</v>
+        <v>-11262611</v>
       </c>
       <c r="K15" t="n">
-        <v>-11217720</v>
+        <v>-11262611</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-11217720</v>
+        <v>-11262611</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2207,34 +2254,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1350077</v>
+        <v>1380735</v>
       </c>
       <c r="F16" t="n">
-        <v>1350077</v>
+        <v>1380735</v>
       </c>
       <c r="G16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>8465438</v>
+        <v>8592242</v>
       </c>
       <c r="I16" t="n">
-        <v>527.03</v>
+        <v>522.29</v>
       </c>
       <c r="J16" t="n">
-        <v>17393938</v>
+        <v>17335131</v>
       </c>
       <c r="K16" t="n">
-        <v>17393937</v>
+        <v>17335132</v>
       </c>
       <c r="L16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>17393937</v>
+        <v>17335132</v>
       </c>
       <c r="N16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2259,31 +2306,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-1335208</v>
+        <v>-1351464</v>
       </c>
       <c r="F17" t="n">
-        <v>-1335208</v>
+        <v>-1351464</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5780153</v>
+        <v>5860043</v>
       </c>
       <c r="I17" t="n">
-        <v>532.9</v>
+        <v>533.61</v>
       </c>
       <c r="J17" t="n">
-        <v>23195598</v>
+        <v>23159912</v>
       </c>
       <c r="K17" t="n">
-        <v>23195598</v>
+        <v>23159912</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>23195598</v>
+        <v>23159912</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2311,31 +2358,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>-3210677</v>
+        <v>-3252215</v>
       </c>
       <c r="F18" t="n">
-        <v>-3210677</v>
+        <v>-3252215</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3904684</v>
+        <v>3959292</v>
       </c>
       <c r="I18" t="n">
-        <v>221.62</v>
+        <v>221.74</v>
       </c>
       <c r="J18" t="n">
-        <v>59530034</v>
+        <v>59438266</v>
       </c>
       <c r="K18" t="n">
-        <v>59530036</v>
+        <v>59438268</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>59530036</v>
+        <v>59438268</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2363,31 +2410,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3049292</v>
+        <v>3092118</v>
       </c>
       <c r="F19" t="n">
-        <v>3049292</v>
+        <v>3092118</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>10164653</v>
+        <v>10303625</v>
       </c>
       <c r="I19" t="n">
-        <v>233.34</v>
+        <v>233.22</v>
       </c>
       <c r="J19" t="n">
-        <v>-54638150</v>
+        <v>-54554826</v>
       </c>
       <c r="K19" t="n">
-        <v>-54638151</v>
+        <v>-54554828</v>
       </c>
       <c r="L19" t="n">
         <v>-0</v>
       </c>
       <c r="M19" t="n">
-        <v>-54638151</v>
+        <v>-54554828</v>
       </c>
       <c r="N19" t="n">
         <v>-0</v>
@@ -2415,31 +2462,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-2615152</v>
+        <v>-2658217</v>
       </c>
       <c r="F20" t="n">
-        <v>-2615152</v>
+        <v>-2658217</v>
       </c>
       <c r="G20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4500209</v>
+        <v>4553290</v>
       </c>
       <c r="I20" t="n">
-        <v>272.08</v>
+        <v>271.29</v>
       </c>
       <c r="J20" t="n">
-        <v>7753899</v>
+        <v>7770684</v>
       </c>
       <c r="K20" t="n">
-        <v>7753899</v>
+        <v>7770683</v>
       </c>
       <c r="L20" t="n">
         <v>-0</v>
       </c>
       <c r="M20" t="n">
-        <v>7753899</v>
+        <v>7770683</v>
       </c>
       <c r="N20" t="n">
         <v>-0</v>
@@ -2467,34 +2514,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2452081</v>
+        <v>2496431</v>
       </c>
       <c r="F21" t="n">
-        <v>2452081</v>
+        <v>2496431</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>9567442</v>
+        <v>9707938</v>
       </c>
       <c r="I21" t="n">
-        <v>290.18</v>
+        <v>288.87</v>
       </c>
       <c r="J21" t="n">
-        <v>-7678698</v>
+        <v>-7695289</v>
       </c>
       <c r="K21" t="n">
-        <v>-7678697</v>
+        <v>-7695289</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M21" t="n">
-        <v>-7678697</v>
+        <v>-7695289</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="22">
@@ -2519,31 +2566,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-1016991</v>
+        <v>-1038861</v>
       </c>
       <c r="F22" t="n">
-        <v>-1016991</v>
+        <v>-1038861</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>6098370</v>
+        <v>6172646</v>
       </c>
       <c r="I22" t="n">
-        <v>699.65</v>
+        <v>694.17</v>
       </c>
       <c r="J22" t="n">
-        <v>-22212472</v>
+        <v>-22149059</v>
       </c>
       <c r="K22" t="n">
-        <v>-22212470</v>
+        <v>-22149057</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-22212470</v>
+        <v>-22149057</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2571,34 +2618,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4519476</v>
+        <v>6144663</v>
       </c>
       <c r="F23" t="n">
-        <v>4519476</v>
+        <v>6144663</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>63756825</v>
+        <v>66863557</v>
       </c>
       <c r="I23" t="n">
-        <v>1310.71</v>
+        <v>988.16</v>
       </c>
       <c r="J23" t="n">
-        <v>-3172771</v>
+        <v>-3111407</v>
       </c>
       <c r="K23" t="n">
-        <v>-3172767</v>
+        <v>-3111408</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M23" t="n">
-        <v>-3172767</v>
+        <v>-3111408</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="24">
@@ -2623,31 +2670,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-22737120</v>
+        <v>-21071075</v>
       </c>
       <c r="F24" t="n">
-        <v>-22737120</v>
+        <v>-21071075</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>36500229</v>
+        <v>39647819</v>
       </c>
       <c r="I24" t="n">
-        <v>260.53</v>
+        <v>288.16</v>
       </c>
       <c r="J24" t="n">
-        <v>9342308</v>
+        <v>9457052</v>
       </c>
       <c r="K24" t="n">
-        <v>9342310</v>
+        <v>9457052</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>9342310</v>
+        <v>9457052</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -2675,34 +2722,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-57437669</v>
+        <v>-55765417</v>
       </c>
       <c r="F25" t="n">
-        <v>-57437669</v>
+        <v>-55765417</v>
       </c>
       <c r="G25" t="n">
         <v>-0</v>
       </c>
       <c r="H25" t="n">
-        <v>1799680</v>
+        <v>4953477</v>
       </c>
       <c r="I25" t="n">
-        <v>103.13</v>
+        <v>108.88</v>
       </c>
       <c r="J25" t="n">
-        <v>23821284</v>
+        <v>23961488</v>
       </c>
       <c r="K25" t="n">
-        <v>23821285</v>
+        <v>23961486</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M25" t="n">
-        <v>23821285</v>
+        <v>23961486</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="26">
@@ -2727,34 +2774,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>58398507</v>
+        <v>60050067</v>
       </c>
       <c r="F26" t="n">
-        <v>58398507</v>
+        <v>60050067</v>
       </c>
       <c r="G26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>117635856</v>
+        <v>120768961</v>
       </c>
       <c r="I26" t="n">
-        <v>101.44</v>
+        <v>101.11</v>
       </c>
       <c r="J26" t="n">
-        <v>-20793636</v>
+        <v>-20772481</v>
       </c>
       <c r="K26" t="n">
-        <v>-20793634</v>
+        <v>-20772482</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M26" t="n">
-        <v>-20793634</v>
+        <v>-20772482</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="27">
@@ -2779,31 +2826,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-26450458</v>
+        <v>-24751691</v>
       </c>
       <c r="F27" t="n">
-        <v>-26450458</v>
+        <v>-24751691</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H27" t="n">
-        <v>32786891</v>
+        <v>35967203</v>
       </c>
       <c r="I27" t="n">
-        <v>223.96</v>
+        <v>245.31</v>
       </c>
       <c r="J27" t="n">
-        <v>12527276</v>
+        <v>12669193</v>
       </c>
       <c r="K27" t="n">
-        <v>12527281</v>
+        <v>12669195</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>12527281</v>
+        <v>12669195</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2831,31 +2878,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>27328160</v>
+        <v>28953150</v>
       </c>
       <c r="F28" t="n">
-        <v>27328160</v>
+        <v>28953150</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H28" t="n">
-        <v>86565509</v>
+        <v>89672044</v>
       </c>
       <c r="I28" t="n">
-        <v>216.76</v>
+        <v>209.71</v>
       </c>
       <c r="J28" t="n">
-        <v>-11926964</v>
+        <v>-11883977</v>
       </c>
       <c r="K28" t="n">
-        <v>-11926961</v>
+        <v>-11883977</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-11926961</v>
+        <v>-11883977</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2883,34 +2930,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3853247</v>
+        <v>5547774</v>
       </c>
       <c r="F29" t="n">
-        <v>3853247</v>
+        <v>5547774</v>
       </c>
       <c r="G29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>63090596</v>
+        <v>66266668</v>
       </c>
       <c r="I29" t="n">
-        <v>1537.34</v>
+        <v>1094.47</v>
       </c>
       <c r="J29" t="n">
-        <v>1267052</v>
+        <v>1374049</v>
       </c>
       <c r="K29" t="n">
-        <v>1267052</v>
+        <v>1374051</v>
       </c>
       <c r="L29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1267052</v>
+        <v>1374051</v>
       </c>
       <c r="N29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2935,34 +2982,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>930867</v>
+        <v>926007</v>
       </c>
       <c r="F30" t="n">
-        <v>930867</v>
+        <v>926007</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>9270442</v>
+        <v>9230626</v>
       </c>
       <c r="I30" t="n">
-        <v>895.89</v>
+        <v>896.8200000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>17612200</v>
+        <v>17779833</v>
       </c>
       <c r="K30" t="n">
-        <v>17612201</v>
+        <v>17779832</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M30" t="n">
-        <v>17612201</v>
+        <v>17779832</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="31">
@@ -2987,34 +3034,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-994990</v>
+        <v>-990448</v>
       </c>
       <c r="F31" t="n">
-        <v>-994990</v>
+        <v>-990448</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>7344585</v>
+        <v>7314171</v>
       </c>
       <c r="I31" t="n">
-        <v>838.16</v>
+        <v>838.47</v>
       </c>
       <c r="J31" t="n">
-        <v>20273758</v>
+        <v>20433166</v>
       </c>
       <c r="K31" t="n">
-        <v>20273760</v>
+        <v>20433165</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" t="n">
-        <v>20273760</v>
+        <v>20433165</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3039,31 +3086,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-2374763</v>
+        <v>-2363696</v>
       </c>
       <c r="F32" t="n">
-        <v>-2374763</v>
+        <v>-2363696</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>5964812</v>
+        <v>5940923</v>
       </c>
       <c r="I32" t="n">
-        <v>351.17</v>
+        <v>351.34</v>
       </c>
       <c r="J32" t="n">
-        <v>52265900</v>
+        <v>52679712</v>
       </c>
       <c r="K32" t="n">
-        <v>52265903</v>
+        <v>52679713</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>52265903</v>
+        <v>52679713</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3091,34 +3138,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2230752</v>
+        <v>2220042</v>
       </c>
       <c r="F33" t="n">
-        <v>2230752</v>
+        <v>2220042</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>10570327</v>
+        <v>10524661</v>
       </c>
       <c r="I33" t="n">
-        <v>373.85</v>
+        <v>374.07</v>
       </c>
       <c r="J33" t="n">
-        <v>-47273519</v>
+        <v>-47639412</v>
       </c>
       <c r="K33" t="n">
-        <v>-47273517</v>
+        <v>-47639414</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M33" t="n">
-        <v>-47273517</v>
+        <v>-47639414</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="34">
@@ -3143,34 +3190,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-1892349</v>
+        <v>-1883298</v>
       </c>
       <c r="F34" t="n">
-        <v>-1892349</v>
+        <v>-1883298</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>6447226</v>
+        <v>6421321</v>
       </c>
       <c r="I34" t="n">
-        <v>440.7</v>
+        <v>440.96</v>
       </c>
       <c r="J34" t="n">
-        <v>4640993</v>
+        <v>4651603</v>
       </c>
       <c r="K34" t="n">
-        <v>4640993</v>
+        <v>4651602</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M34" t="n">
-        <v>4640993</v>
+        <v>4651602</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="35">
@@ -3195,31 +3242,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1746999</v>
+        <v>1738312</v>
       </c>
       <c r="F35" t="n">
-        <v>1746999</v>
+        <v>1738312</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>10086574</v>
+        <v>10042931</v>
       </c>
       <c r="I35" t="n">
-        <v>477.37</v>
+        <v>477.74</v>
       </c>
       <c r="J35" t="n">
-        <v>-4597654</v>
+        <v>-4608206</v>
       </c>
       <c r="K35" t="n">
-        <v>-4597654</v>
+        <v>-4608209</v>
       </c>
       <c r="L35" t="n">
         <v>-0</v>
       </c>
       <c r="M35" t="n">
-        <v>-4597654</v>
+        <v>-4608209</v>
       </c>
       <c r="N35" t="n">
         <v>-0</v>
@@ -3247,34 +3294,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-714972</v>
+        <v>-711480</v>
       </c>
       <c r="F36" t="n">
-        <v>-714972</v>
+        <v>-711480</v>
       </c>
       <c r="G36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>7624603</v>
+        <v>7593139</v>
       </c>
       <c r="I36" t="n">
-        <v>1166.42</v>
+        <v>1167.23</v>
       </c>
       <c r="J36" t="n">
-        <v>-21412385</v>
+        <v>-21605002</v>
       </c>
       <c r="K36" t="n">
-        <v>-21412382</v>
+        <v>-21605004</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M36" t="n">
-        <v>-21412382</v>
+        <v>-21605004</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="37">
@@ -3299,31 +3346,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-1970841</v>
+        <v>-1628025</v>
       </c>
       <c r="F37" t="n">
-        <v>-2054977</v>
+        <v>-1719045</v>
       </c>
       <c r="G37" t="n">
-        <v>-4.27</v>
+        <v>-5.59</v>
       </c>
       <c r="H37" t="n">
-        <v>28665731</v>
+        <v>29398589</v>
       </c>
       <c r="I37" t="n">
-        <v>1554.49</v>
+        <v>1905.78</v>
       </c>
       <c r="J37" t="n">
-        <v>-7210840</v>
+        <v>-7653607</v>
       </c>
       <c r="K37" t="n">
-        <v>-7210838</v>
+        <v>-7653605</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-7210838</v>
+        <v>-7653605</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -3351,31 +3398,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-10665292</v>
+        <v>-10323105</v>
       </c>
       <c r="F38" t="n">
-        <v>-10661606</v>
+        <v>-10317702</v>
       </c>
       <c r="G38" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="H38" t="n">
-        <v>20059102</v>
+        <v>20799932</v>
       </c>
       <c r="I38" t="n">
-        <v>288.08</v>
+        <v>301.49</v>
       </c>
       <c r="J38" t="n">
-        <v>13322112</v>
+        <v>12919082</v>
       </c>
       <c r="K38" t="n">
-        <v>13322113</v>
+        <v>12919084</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>13322113</v>
+        <v>12919084</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -3403,31 +3450,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-26051899</v>
+        <v>-25714165</v>
       </c>
       <c r="F39" t="n">
-        <v>-26041605</v>
+        <v>-25701399</v>
       </c>
       <c r="G39" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H39" t="n">
-        <v>4679103</v>
+        <v>5416235</v>
       </c>
       <c r="I39" t="n">
-        <v>117.96</v>
+        <v>121.06</v>
       </c>
       <c r="J39" t="n">
-        <v>33763879</v>
+        <v>32650266</v>
       </c>
       <c r="K39" t="n">
-        <v>33763879</v>
+        <v>32650267</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>33763879</v>
+        <v>32650267</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -3455,31 +3502,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>25311252</v>
+        <v>25663847</v>
       </c>
       <c r="F40" t="n">
-        <v>25299537</v>
+        <v>25652087</v>
       </c>
       <c r="G40" t="n">
         <v>-0.05</v>
       </c>
       <c r="H40" t="n">
-        <v>56020245</v>
+        <v>56769721</v>
       </c>
       <c r="I40" t="n">
-        <v>121.33</v>
+        <v>121.21</v>
       </c>
       <c r="J40" t="n">
-        <v>-31619221</v>
+        <v>-30570258</v>
       </c>
       <c r="K40" t="n">
-        <v>-31619219</v>
+        <v>-30570255</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-31619219</v>
+        <v>-30570255</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -3507,31 +3554,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-9290936</v>
+        <v>-8946674</v>
       </c>
       <c r="F41" t="n">
-        <v>-9212971</v>
+        <v>-8859782</v>
       </c>
       <c r="G41" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
       <c r="H41" t="n">
-        <v>21507737</v>
+        <v>22257852</v>
       </c>
       <c r="I41" t="n">
-        <v>331.49</v>
+        <v>348.78</v>
       </c>
       <c r="J41" t="n">
-        <v>20022208</v>
+        <v>20046721</v>
       </c>
       <c r="K41" t="n">
-        <v>20022209</v>
+        <v>20046722</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>20022209</v>
+        <v>20046722</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -3559,31 +3606,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>8507491</v>
+        <v>8853541</v>
       </c>
       <c r="F42" t="n">
-        <v>8427926</v>
+        <v>8767460</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.97</v>
       </c>
       <c r="H42" t="n">
-        <v>39148634</v>
+        <v>39885094</v>
       </c>
       <c r="I42" t="n">
-        <v>360.17</v>
+        <v>350.5</v>
       </c>
       <c r="J42" t="n">
-        <v>-19609415</v>
+        <v>-19554195</v>
       </c>
       <c r="K42" t="n">
-        <v>-19609412</v>
+        <v>-19554191</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>-19609412</v>
+        <v>-19554191</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -3611,31 +3658,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4257475</v>
+        <v>4605718</v>
       </c>
       <c r="F43" t="n">
-        <v>4332374</v>
+        <v>4689147</v>
       </c>
       <c r="G43" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="H43" t="n">
-        <v>35053082</v>
+        <v>35806781</v>
       </c>
       <c r="I43" t="n">
-        <v>723.33</v>
+        <v>677.4400000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>3246588</v>
+        <v>3832374</v>
       </c>
       <c r="K43" t="n">
-        <v>3246589</v>
+        <v>3832375</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3246589</v>
+        <v>3832375</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3663,31 +3710,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>202098</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>202098</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>2305929</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1040.99</v>
-      </c>
+        <v>87271</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>28746491</v>
+        <v>20456566</v>
       </c>
       <c r="K44" t="n">
-        <v>28746491</v>
+        <v>20456566</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>28746491</v>
+        <v>20456566</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -3715,31 +3758,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-158710</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>-158710</v>
-      </c>
-      <c r="G45" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>1945121</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1325.58</v>
-      </c>
+        <v>87271</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>34445377</v>
+        <v>23897384</v>
       </c>
       <c r="K45" t="n">
-        <v>34445377</v>
+        <v>23897384</v>
       </c>
       <c r="L45" t="n">
         <v>-0</v>
       </c>
       <c r="M45" t="n">
-        <v>34445377</v>
+        <v>23897384</v>
       </c>
       <c r="N45" t="n">
         <v>-0</v>
@@ -3767,34 +3806,30 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-395306</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>-395306</v>
-      </c>
-      <c r="G46" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>1708525</v>
-      </c>
-      <c r="I46" t="n">
-        <v>532.2</v>
-      </c>
+        <v>87271</v>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>88422946</v>
+        <v>61309111</v>
       </c>
       <c r="K46" t="n">
-        <v>88422946</v>
+        <v>61309111</v>
       </c>
       <c r="L46" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>88422946</v>
+        <v>61309111</v>
       </c>
       <c r="N46" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3819,31 +3854,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>400234</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>400234</v>
-      </c>
-      <c r="G47" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>2504065</v>
-      </c>
-      <c r="I47" t="n">
-        <v>525.65</v>
-      </c>
+        <v>87271</v>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>-81069124</v>
+        <v>-56318431</v>
       </c>
       <c r="K47" t="n">
-        <v>-81069124</v>
+        <v>-56318431</v>
       </c>
       <c r="L47" t="n">
         <v>-0</v>
       </c>
       <c r="M47" t="n">
-        <v>-81069124</v>
+        <v>-56318431</v>
       </c>
       <c r="N47" t="n">
         <v>-0</v>
@@ -3871,34 +3902,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-337475</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>-337475</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>1766356</v>
-      </c>
-      <c r="I48" t="n">
-        <v>623.4</v>
-      </c>
+        <v>87271</v>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>8898993</v>
+        <v>5700492</v>
       </c>
       <c r="K48" t="n">
-        <v>8898993</v>
+        <v>5700492</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M48" t="n">
-        <v>8898993</v>
+        <v>5700492</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="49">
@@ -3923,31 +3950,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>341060</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>341060</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>2444891</v>
-      </c>
-      <c r="I49" t="n">
-        <v>616.85</v>
-      </c>
+        <v>87271</v>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>-8812891</v>
+        <v>-5650283</v>
       </c>
       <c r="K49" t="n">
-        <v>-8812891</v>
+        <v>-5650283</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-8812891</v>
+        <v>-5650283</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3975,34 +3998,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-136297</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>-136297</v>
-      </c>
-      <c r="G50" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>1967534</v>
-      </c>
-      <c r="I50" t="n">
-        <v>1543.56</v>
-      </c>
+        <v>87271</v>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>-35656473</v>
+        <v>-25261942</v>
       </c>
       <c r="K50" t="n">
-        <v>-35656473</v>
+        <v>-25261942</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M50" t="n">
-        <v>-35656473</v>
+        <v>-25261942</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="51">
@@ -4027,34 +4046,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-469226</v>
+        <v>159565</v>
       </c>
       <c r="F51" t="n">
-        <v>-350840</v>
+        <v>177397</v>
       </c>
       <c r="G51" t="n">
-        <v>25.23</v>
+        <v>11.18</v>
       </c>
       <c r="H51" t="n">
-        <v>8278604</v>
+        <v>9249901</v>
       </c>
       <c r="I51" t="n">
-        <v>1864.31</v>
+        <v>5696.96</v>
       </c>
       <c r="J51" t="n">
-        <v>-7681254</v>
+        <v>-8551705</v>
       </c>
       <c r="K51" t="n">
-        <v>-8507822</v>
+        <v>-8551705</v>
       </c>
       <c r="L51" t="n">
-        <v>-10.76</v>
+        <v>-0</v>
       </c>
       <c r="M51" t="n">
-        <v>-8507822</v>
+        <v>-8551705</v>
       </c>
       <c r="N51" t="n">
-        <v>-10.76</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="52">
@@ -4079,34 +4098,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-7280671</v>
+        <v>-8382646</v>
       </c>
       <c r="F52" t="n">
-        <v>-7351875</v>
+        <v>-8379002</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.98</v>
+        <v>0.04</v>
       </c>
       <c r="H52" t="n">
-        <v>1277569</v>
+        <v>693502</v>
       </c>
       <c r="I52" t="n">
-        <v>117.55</v>
+        <v>108.27</v>
       </c>
       <c r="J52" t="n">
-        <v>5561635</v>
+        <v>6243945</v>
       </c>
       <c r="K52" t="n">
-        <v>6049871</v>
+        <v>6243945</v>
       </c>
       <c r="L52" t="n">
-        <v>8.779999999999999</v>
+        <v>-0</v>
       </c>
       <c r="M52" t="n">
-        <v>6049871</v>
+        <v>6243945</v>
       </c>
       <c r="N52" t="n">
-        <v>8.779999999999999</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="53">
@@ -4131,34 +4150,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>-18134854</v>
+        <v>-20880107</v>
       </c>
       <c r="F53" t="n">
-        <v>-18312104</v>
+        <v>-20870995</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.98</v>
+        <v>0.04</v>
       </c>
       <c r="H53" t="n">
-        <v>-9682660</v>
+        <v>-11798491</v>
       </c>
       <c r="I53" t="n">
-        <v>46.61</v>
+        <v>43.49</v>
       </c>
       <c r="J53" t="n">
-        <v>13791192</v>
+        <v>15391601</v>
       </c>
       <c r="K53" t="n">
-        <v>15014875</v>
+        <v>15391601</v>
       </c>
       <c r="L53" t="n">
-        <v>8.869999999999999</v>
+        <v>-0</v>
       </c>
       <c r="M53" t="n">
-        <v>15014875</v>
+        <v>15391601</v>
       </c>
       <c r="N53" t="n">
-        <v>8.869999999999999</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="54">
@@ -4183,34 +4202,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>18365578</v>
+        <v>21141081</v>
       </c>
       <c r="F54" t="n">
-        <v>18544857</v>
+        <v>21131888</v>
       </c>
       <c r="G54" t="n">
-        <v>0.98</v>
+        <v>-0.04</v>
       </c>
       <c r="H54" t="n">
-        <v>27174301</v>
+        <v>30204392</v>
       </c>
       <c r="I54" t="n">
-        <v>47.96</v>
+        <v>42.87</v>
       </c>
       <c r="J54" t="n">
-        <v>-13417447</v>
+        <v>-14858227</v>
       </c>
       <c r="K54" t="n">
-        <v>-14630873</v>
+        <v>-14858227</v>
       </c>
       <c r="L54" t="n">
-        <v>-9.039999999999999</v>
+        <v>-0</v>
       </c>
       <c r="M54" t="n">
-        <v>-14630873</v>
+        <v>-14858227</v>
       </c>
       <c r="N54" t="n">
-        <v>-9.039999999999999</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="55">
@@ -4235,34 +4254,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>-6876979</v>
+        <v>-8537527</v>
       </c>
       <c r="F55" t="n">
-        <v>-7054217</v>
+        <v>-8549946</v>
       </c>
       <c r="G55" t="n">
-        <v>-2.58</v>
+        <v>-0.15</v>
       </c>
       <c r="H55" t="n">
-        <v>1575227</v>
+        <v>522558</v>
       </c>
       <c r="I55" t="n">
-        <v>122.91</v>
+        <v>106.12</v>
       </c>
       <c r="J55" t="n">
-        <v>12590001</v>
+        <v>14122411</v>
       </c>
       <c r="K55" t="n">
-        <v>13822606</v>
+        <v>14122411</v>
       </c>
       <c r="L55" t="n">
-        <v>9.789999999999999</v>
+        <v>-0</v>
       </c>
       <c r="M55" t="n">
-        <v>13822606</v>
+        <v>14122411</v>
       </c>
       <c r="N55" t="n">
-        <v>9.789999999999999</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="56">
@@ -4287,34 +4306,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6920518</v>
+        <v>8592938</v>
       </c>
       <c r="F56" t="n">
-        <v>7098362</v>
+        <v>8605277</v>
       </c>
       <c r="G56" t="n">
-        <v>2.57</v>
+        <v>0.14</v>
       </c>
       <c r="H56" t="n">
-        <v>15727806</v>
+        <v>17677781</v>
       </c>
       <c r="I56" t="n">
-        <v>127.26</v>
+        <v>105.72</v>
       </c>
       <c r="J56" t="n">
-        <v>-12260886</v>
+        <v>-13635747</v>
       </c>
       <c r="K56" t="n">
-        <v>-13484030</v>
+        <v>-13635747</v>
       </c>
       <c r="L56" t="n">
-        <v>-9.98</v>
+        <v>-0</v>
       </c>
       <c r="M56" t="n">
-        <v>-13484030</v>
+        <v>-13635747</v>
       </c>
       <c r="N56" t="n">
-        <v>-9.98</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="57">
@@ -4339,40 +4358,40 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2718169</v>
+        <v>2484155</v>
       </c>
       <c r="F57" t="n">
-        <v>2629957</v>
+        <v>2466212</v>
       </c>
       <c r="G57" t="n">
-        <v>-3.25</v>
+        <v>-0.72</v>
       </c>
       <c r="H57" t="n">
-        <v>11259401</v>
+        <v>11538716</v>
       </c>
       <c r="I57" t="n">
-        <v>314.23</v>
+        <v>364.49</v>
       </c>
       <c r="J57" t="n">
-        <v>5643705</v>
+        <v>6402358</v>
       </c>
       <c r="K57" t="n">
-        <v>6258509</v>
+        <v>6402358</v>
       </c>
       <c r="L57" t="n">
-        <v>10.89</v>
+        <v>-0</v>
       </c>
       <c r="M57" t="n">
-        <v>6258509</v>
+        <v>6402358</v>
       </c>
       <c r="N57" t="n">
-        <v>10.89</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4391,32 +4410,40 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>9420915</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="inlineStr"/>
+        <v>9420915</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
       <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="inlineStr"/>
+        <v>6527477</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-30.71</v>
+      </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>-356970</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="inlineStr"/>
+        <v>-356970</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
       <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="inlineStr"/>
+        <v>-356970</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4435,32 +4462,40 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>-4137695</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="inlineStr"/>
+        <v>-4137695</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
       <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="inlineStr"/>
+        <v>-7031133</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-69.93000000000001</v>
+      </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>142487</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="inlineStr"/>
+        <v>142487</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-0</v>
+      </c>
       <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="inlineStr"/>
+        <v>142487</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4479,32 +4514,40 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>-9928353</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="inlineStr"/>
+        <v>-9928353</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
       <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="inlineStr"/>
+        <v>-12821791</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-29.14</v>
+      </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>356178</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="inlineStr"/>
+        <v>356178</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
       <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="inlineStr"/>
+        <v>356178</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4523,32 +4566,40 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>9385852</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="inlineStr"/>
+        <v>9385852</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
       <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="inlineStr"/>
+        <v>6492414</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-30.83</v>
+      </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>-355680</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="inlineStr"/>
+        <v>-355680</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-0</v>
+      </c>
       <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="inlineStr"/>
+        <v>-355680</v>
+      </c>
+      <c r="N61" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4567,32 +4618,40 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>-12786163</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="inlineStr"/>
+        <v>-12786163</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
       <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="inlineStr"/>
+        <v>-15679601</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-22.63</v>
+      </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>461723</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="inlineStr"/>
+        <v>461723</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-0</v>
+      </c>
       <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="inlineStr"/>
+        <v>461723</v>
+      </c>
+      <c r="N62" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4611,32 +4670,40 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>12249532</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="inlineStr"/>
+        <v>12249532</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
       <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="inlineStr"/>
+        <v>9356094</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-23.62</v>
+      </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>-461011</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="inlineStr"/>
+        <v>-461011</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
       <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr"/>
+        <v>-461011</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4655,32 +4722,40 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>-8022838</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="inlineStr"/>
+        <v>-8022838</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
       <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="inlineStr"/>
+        <v>-10916276</v>
+      </c>
+      <c r="I64" t="n">
+        <v>-36.07</v>
+      </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>285834</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="inlineStr"/>
+        <v>285834</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
       <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="inlineStr"/>
+        <v>285834</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4699,40 +4774,32 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>942981</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>937532</v>
-      </c>
-      <c r="G65" t="n">
-        <v>-0.58</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>14962726</v>
-      </c>
-      <c r="I65" t="n">
-        <v>1486.75</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
-        <v>1390129</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>1390130</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
-        <v>1390130</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4751,40 +4818,32 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>-3970504</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>-3910306</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1.52</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>10114888</v>
-      </c>
-      <c r="I66" t="n">
-        <v>354.75</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
-        <v>4053227</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>4053228</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
-        <v>4053228</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4803,40 +4862,32 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>-10011903</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>-9855545</v>
-      </c>
-      <c r="G67" t="n">
-        <v>1.56</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>4169649</v>
-      </c>
-      <c r="I67" t="n">
-        <v>141.65</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
-        <v>10335420</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>10335419</v>
-      </c>
-      <c r="L67" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
-        <v>10335419</v>
-      </c>
-      <c r="N67" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4855,40 +4906,32 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>10155091</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>9993011</v>
-      </c>
-      <c r="G68" t="n">
-        <v>-1.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>24018205</v>
-      </c>
-      <c r="I68" t="n">
-        <v>136.51</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
-        <v>-9456748</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>-9456748</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
-        <v>-9456748</v>
-      </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4907,40 +4950,32 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>-4766716</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>-4704486</v>
-      </c>
-      <c r="G69" t="n">
-        <v>1.31</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>9320708</v>
-      </c>
-      <c r="I69" t="n">
-        <v>295.54</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="n">
-        <v>2870069</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>2870069</v>
-      </c>
-      <c r="L69" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="n">
-        <v>2870069</v>
-      </c>
-      <c r="N69" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4959,40 +4994,32 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4895812</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>4826866</v>
-      </c>
-      <c r="G70" t="n">
-        <v>-1.41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>18852060</v>
-      </c>
-      <c r="I70" t="n">
-        <v>285.07</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="n">
-        <v>-2773967</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>-2773968</v>
-      </c>
-      <c r="L70" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
-        <v>-2773968</v>
-      </c>
-      <c r="N70" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5011,45 +5038,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>503698</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>482079</v>
-      </c>
-      <c r="G71" t="n">
-        <v>-4.29</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>14507273</v>
-      </c>
-      <c r="I71" t="n">
-        <v>2780.15</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="n">
-        <v>-2278649</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>-2278649</v>
-      </c>
-      <c r="L71" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
-        <v>-2278649</v>
-      </c>
-      <c r="N71" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5063,45 +5082,45 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>-980817</v>
+        <v>1389715</v>
       </c>
       <c r="F72" t="n">
-        <v>-965426</v>
+        <v>1368173</v>
       </c>
       <c r="G72" t="n">
-        <v>1.57</v>
+        <v>-1.55</v>
       </c>
       <c r="H72" t="n">
-        <v>-6838395</v>
+        <v>15657277</v>
       </c>
       <c r="I72" t="n">
-        <v>-597.21</v>
+        <v>1026.65</v>
       </c>
       <c r="J72" t="n">
-        <v>5568843</v>
+        <v>1359511</v>
       </c>
       <c r="K72" t="n">
-        <v>6136143</v>
+        <v>1359510</v>
       </c>
       <c r="L72" t="n">
-        <v>10.19</v>
+        <v>-0</v>
       </c>
       <c r="M72" t="n">
-        <v>6136143</v>
+        <v>1359510</v>
       </c>
       <c r="N72" t="n">
-        <v>10.19</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5115,45 +5134,45 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6038230</v>
+        <v>-3664753</v>
       </c>
       <c r="F73" t="n">
-        <v>6047349</v>
+        <v>-3580481</v>
       </c>
       <c r="G73" t="n">
-        <v>0.15</v>
+        <v>2.3</v>
       </c>
       <c r="H73" t="n">
-        <v>174380</v>
+        <v>10708623</v>
       </c>
       <c r="I73" t="n">
-        <v>-97.11</v>
+        <v>392.21</v>
       </c>
       <c r="J73" t="n">
-        <v>-3756494</v>
+        <v>3982246</v>
       </c>
       <c r="K73" t="n">
-        <v>-4091586</v>
+        <v>3982246</v>
       </c>
       <c r="L73" t="n">
-        <v>-8.92</v>
+        <v>-0</v>
       </c>
       <c r="M73" t="n">
-        <v>-4091586</v>
+        <v>3982246</v>
       </c>
       <c r="N73" t="n">
-        <v>-8.92</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5167,45 +5186,45 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>15043851</v>
+        <v>-9717891</v>
       </c>
       <c r="F74" t="n">
-        <v>15066179</v>
+        <v>-9468608</v>
       </c>
       <c r="G74" t="n">
-        <v>0.15</v>
+        <v>2.57</v>
       </c>
       <c r="H74" t="n">
-        <v>9193210</v>
+        <v>4820496</v>
       </c>
       <c r="I74" t="n">
-        <v>-38.89</v>
+        <v>149.6</v>
       </c>
       <c r="J74" t="n">
-        <v>-9304287</v>
+        <v>10104696</v>
       </c>
       <c r="K74" t="n">
-        <v>-10144140</v>
+        <v>10104695</v>
       </c>
       <c r="L74" t="n">
-        <v>-9.029999999999999</v>
+        <v>-0</v>
       </c>
       <c r="M74" t="n">
-        <v>-10144140</v>
+        <v>10104695</v>
       </c>
       <c r="N74" t="n">
-        <v>-9.029999999999999</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5219,45 +5238,45 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>-15221233</v>
+        <v>10488225</v>
       </c>
       <c r="F75" t="n">
-        <v>-15244817</v>
+        <v>10189110</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.15</v>
+        <v>-2.85</v>
       </c>
       <c r="H75" t="n">
-        <v>-21117786</v>
+        <v>24478214</v>
       </c>
       <c r="I75" t="n">
-        <v>-38.74</v>
+        <v>133.39</v>
       </c>
       <c r="J75" t="n">
-        <v>9051346</v>
+        <v>-9211359</v>
       </c>
       <c r="K75" t="n">
-        <v>9884159</v>
+        <v>-9211360</v>
       </c>
       <c r="L75" t="n">
-        <v>9.199999999999999</v>
+        <v>-0</v>
       </c>
       <c r="M75" t="n">
-        <v>9884159</v>
+        <v>-9211360</v>
       </c>
       <c r="N75" t="n">
-        <v>9.199999999999999</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5271,45 +5290,45 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6920249</v>
+        <v>-4579591</v>
       </c>
       <c r="F76" t="n">
-        <v>6916313</v>
+        <v>-4498284</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.06</v>
+        <v>1.78</v>
       </c>
       <c r="H76" t="n">
-        <v>1043344</v>
+        <v>9790820</v>
       </c>
       <c r="I76" t="n">
-        <v>-84.92</v>
+        <v>313.79</v>
       </c>
       <c r="J76" t="n">
-        <v>-8847426</v>
+        <v>2849086</v>
       </c>
       <c r="K76" t="n">
-        <v>-9693402</v>
+        <v>2849085</v>
       </c>
       <c r="L76" t="n">
-        <v>-9.56</v>
+        <v>-0</v>
       </c>
       <c r="M76" t="n">
-        <v>-9693402</v>
+        <v>2849085</v>
       </c>
       <c r="N76" t="n">
-        <v>-9.56</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5323,45 +5342,45 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>-6961002</v>
+        <v>5336067</v>
       </c>
       <c r="F77" t="n">
-        <v>-6956884</v>
+        <v>5204276</v>
       </c>
       <c r="G77" t="n">
-        <v>0.06</v>
+        <v>-2.47</v>
       </c>
       <c r="H77" t="n">
-        <v>-12829853</v>
+        <v>19493380</v>
       </c>
       <c r="I77" t="n">
-        <v>-84.31</v>
+        <v>265.31</v>
       </c>
       <c r="J77" t="n">
-        <v>8617516</v>
+        <v>-2699686</v>
       </c>
       <c r="K77" t="n">
-        <v>9456999</v>
+        <v>-2699687</v>
       </c>
       <c r="L77" t="n">
-        <v>9.74</v>
+        <v>-0</v>
       </c>
       <c r="M77" t="n">
-        <v>9456999</v>
+        <v>-2699687</v>
       </c>
       <c r="N77" t="n">
-        <v>9.74</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5375,45 +5394,45 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>-990097</v>
+        <v>696743</v>
       </c>
       <c r="F78" t="n">
-        <v>-1006119</v>
+        <v>633546</v>
       </c>
       <c r="G78" t="n">
-        <v>-1.62</v>
+        <v>-9.07</v>
       </c>
       <c r="H78" t="n">
-        <v>-6879088</v>
+        <v>14922650</v>
       </c>
       <c r="I78" t="n">
-        <v>-594.79</v>
+        <v>2041.77</v>
       </c>
       <c r="J78" t="n">
-        <v>-4175502</v>
+        <v>-2178780</v>
       </c>
       <c r="K78" t="n">
-        <v>-4597461</v>
+        <v>-2178781</v>
       </c>
       <c r="L78" t="n">
-        <v>-10.11</v>
+        <v>-0</v>
       </c>
       <c r="M78" t="n">
-        <v>-4597461</v>
+        <v>-2178781</v>
       </c>
       <c r="N78" t="n">
-        <v>-10.11</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5427,37 +5446,45 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>411359</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" t="inlineStr"/>
+        <v>411359</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
       <c r="H79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" t="inlineStr"/>
+        <v>-4903781</v>
+      </c>
+      <c r="I79" t="n">
+        <v>-1292.09</v>
+      </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>6952797</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="inlineStr"/>
+        <v>6952797</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-0</v>
+      </c>
       <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="inlineStr"/>
+        <v>6952797</v>
+      </c>
+      <c r="N79" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5471,37 +5498,45 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>4284730</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="inlineStr"/>
+        <v>4284730</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
       <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="inlineStr"/>
+        <v>-1030410</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-124.05</v>
+      </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>-5335174</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="inlineStr"/>
+        <v>-5335174</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
       <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="inlineStr"/>
+        <v>-5335174</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5515,37 +5550,45 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>10672486</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="inlineStr"/>
+        <v>10672486</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
       <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="inlineStr"/>
+        <v>5357346</v>
+      </c>
+      <c r="I81" t="n">
+        <v>-49.8</v>
+      </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>-13310384</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="inlineStr"/>
+        <v>-13310384</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
       <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="inlineStr"/>
+        <v>-13310384</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5559,37 +5602,45 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>-10808138</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="inlineStr"/>
+        <v>-10808138</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-0</v>
+      </c>
       <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="inlineStr"/>
+        <v>-16123278</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-49.18</v>
+      </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>13042366</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="inlineStr"/>
+        <v>13042366</v>
+      </c>
+      <c r="L82" t="n">
+        <v>-0</v>
+      </c>
       <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="inlineStr"/>
+        <v>13042366</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5603,37 +5654,45 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>3925257</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" t="inlineStr"/>
+        <v>3925257</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
       <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="inlineStr"/>
+        <v>-1389883</v>
+      </c>
+      <c r="I83" t="n">
+        <v>-135.41</v>
+      </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>-11662031</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="inlineStr"/>
+        <v>-11662031</v>
+      </c>
+      <c r="L83" t="n">
+        <v>-0</v>
+      </c>
       <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="inlineStr"/>
+        <v>-11662031</v>
+      </c>
+      <c r="N83" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5647,37 +5706,45 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>-3951431</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="inlineStr"/>
+        <v>-3951431</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
       <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="inlineStr"/>
+        <v>-9266571</v>
+      </c>
+      <c r="I84" t="n">
+        <v>-134.51</v>
+      </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>11444387</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="inlineStr"/>
+        <v>11444387</v>
+      </c>
+      <c r="L84" t="n">
+        <v>-0</v>
+      </c>
       <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="inlineStr"/>
+        <v>11444387</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5691,32 +5758,40 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>-1726762</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" t="inlineStr"/>
+        <v>-1726762</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
       <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="inlineStr"/>
+        <v>-7041902</v>
+      </c>
+      <c r="I85" t="n">
+        <v>-307.81</v>
+      </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>-4914269</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="inlineStr"/>
+        <v>-4914269</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-0</v>
+      </c>
       <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="inlineStr"/>
+        <v>-4914269</v>
+      </c>
+      <c r="N85" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5760,7 +5835,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5804,7 +5879,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5848,7 +5923,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5892,7 +5967,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5936,7 +6011,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5980,7 +6055,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6024,7 +6099,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6068,7 +6143,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6112,7 +6187,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6156,7 +6231,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6200,7 +6275,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6244,7 +6319,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6288,7 +6363,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6332,12 +6407,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6362,30 +6437,26 @@
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="n">
-        <v>-59169899</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>-59169899</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
       <c r="M100" t="n">
-        <v>-59169899</v>
-      </c>
-      <c r="N100" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6410,30 +6481,26 @@
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="n">
-        <v>-66519544</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>-66519544</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
       <c r="M101" t="n">
-        <v>-66519544</v>
-      </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6458,30 +6525,26 @@
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="n">
-        <v>-171520564</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>-171520564</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
       <c r="M102" t="n">
-        <v>-171520564</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6506,30 +6569,26 @@
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="n">
-        <v>155015097</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>155015097</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
       <c r="M103" t="n">
-        <v>155015097</v>
-      </c>
-      <c r="N103" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6554,30 +6613,26 @@
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="n">
-        <v>-13999828</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>-13999828</v>
-      </c>
-      <c r="L104" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="n">
-        <v>-13999828</v>
-      </c>
-      <c r="N104" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6602,30 +6657,26 @@
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="n">
-        <v>13875773</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>13875773</v>
-      </c>
-      <c r="L105" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
       <c r="M105" t="n">
-        <v>13875773</v>
-      </c>
-      <c r="N105" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6650,25 +6701,21 @@
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="n">
-        <v>71464391</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>71464391</v>
-      </c>
-      <c r="L106" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
       <c r="M106" t="n">
-        <v>71464391</v>
-      </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6687,31 +6734,27 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>115085</v>
+        <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>115085</v>
-      </c>
-      <c r="G107" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>115085</v>
-      </c>
-      <c r="I107" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="n">
-        <v>175740</v>
+        <v>-59621281</v>
       </c>
       <c r="K107" t="n">
-        <v>175740</v>
+        <v>-59621281</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>175740</v>
+        <v>-59621281</v>
       </c>
       <c r="N107" t="n">
         <v>0</v>
@@ -6720,7 +6763,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6739,40 +6782,36 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>115085</v>
+        <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>115085</v>
-      </c>
-      <c r="G108" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>115085</v>
-      </c>
-      <c r="I108" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="n">
-        <v>93008</v>
+        <v>-66957822</v>
       </c>
       <c r="K108" t="n">
-        <v>93008</v>
+        <v>-66957822</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M108" t="n">
-        <v>93008</v>
+        <v>-66957822</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6791,31 +6830,27 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>115085</v>
+        <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>115085</v>
-      </c>
-      <c r="G109" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>115085</v>
-      </c>
-      <c r="I109" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="n">
-        <v>60160</v>
+        <v>-172655395</v>
       </c>
       <c r="K109" t="n">
-        <v>60160</v>
+        <v>-172655395</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>60160</v>
+        <v>-172655395</v>
       </c>
       <c r="N109" t="n">
         <v>0</v>
@@ -6824,7 +6859,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6843,31 +6878,27 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>115085</v>
+        <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>115085</v>
-      </c>
-      <c r="G110" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>115085</v>
-      </c>
-      <c r="I110" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="n">
-        <v>169640</v>
+        <v>156027140</v>
       </c>
       <c r="K110" t="n">
-        <v>169640</v>
+        <v>156027140</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>169640</v>
+        <v>156027140</v>
       </c>
       <c r="N110" t="n">
         <v>0</v>
@@ -6876,7 +6907,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6895,40 +6926,36 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>115085</v>
+        <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>115085</v>
-      </c>
-      <c r="G111" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>115085</v>
-      </c>
-      <c r="I111" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="n">
-        <v>38676</v>
+        <v>-14037282</v>
       </c>
       <c r="K111" t="n">
-        <v>38676</v>
+        <v>-14037282</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M111" t="n">
-        <v>38676</v>
+        <v>-14037282</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6947,31 +6974,27 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>115085</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>115085</v>
-      </c>
-      <c r="G112" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>115085</v>
-      </c>
-      <c r="I112" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="n">
-        <v>191116</v>
+        <v>13913112</v>
       </c>
       <c r="K112" t="n">
-        <v>191116</v>
+        <v>13913112</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>191116</v>
+        <v>13913112</v>
       </c>
       <c r="N112" t="n">
         <v>0</v>
@@ -6980,7 +7003,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6999,31 +7022,27 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>115085</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>115085</v>
-      </c>
-      <c r="G113" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>115085</v>
-      </c>
-      <c r="I113" t="n">
-        <v>-0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
-        <v>65520</v>
+        <v>71987818</v>
       </c>
       <c r="K113" t="n">
-        <v>65520</v>
+        <v>71987818</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>65520</v>
+        <v>71987818</v>
       </c>
       <c r="N113" t="n">
         <v>0</v>
@@ -7032,7 +7051,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7051,40 +7070,40 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>-20614596</v>
+        <v>115085</v>
       </c>
       <c r="F114" t="n">
-        <v>-20614596</v>
+        <v>115085</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H114" t="n">
-        <v>-28429954</v>
+        <v>115085</v>
       </c>
       <c r="I114" t="n">
-        <v>-37.91</v>
+        <v>-0</v>
       </c>
       <c r="J114" t="n">
-        <v>7619305</v>
+        <v>175740</v>
       </c>
       <c r="K114" t="n">
-        <v>7619305</v>
+        <v>175740</v>
       </c>
       <c r="L114" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>7619305</v>
+        <v>175740</v>
       </c>
       <c r="N114" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7103,31 +7122,31 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>10225113</v>
+        <v>115085</v>
       </c>
       <c r="F115" t="n">
-        <v>10225113</v>
+        <v>115085</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H115" t="n">
-        <v>2409755</v>
+        <v>115085</v>
       </c>
       <c r="I115" t="n">
-        <v>-76.43000000000001</v>
+        <v>-0</v>
       </c>
       <c r="J115" t="n">
-        <v>-4506587</v>
+        <v>93008</v>
       </c>
       <c r="K115" t="n">
-        <v>-4506587</v>
+        <v>93008</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>-4506587</v>
+        <v>93008</v>
       </c>
       <c r="N115" t="n">
         <v>0</v>
@@ -7136,7 +7155,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7155,31 +7174,31 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>25519979</v>
+        <v>115085</v>
       </c>
       <c r="F116" t="n">
-        <v>25519979</v>
+        <v>115085</v>
       </c>
       <c r="G116" t="n">
         <v>-0</v>
       </c>
       <c r="H116" t="n">
-        <v>17704621</v>
+        <v>115085</v>
       </c>
       <c r="I116" t="n">
-        <v>-30.62</v>
+        <v>-0</v>
       </c>
       <c r="J116" t="n">
-        <v>-11294479</v>
+        <v>60160</v>
       </c>
       <c r="K116" t="n">
-        <v>-11294479</v>
+        <v>60160</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>-11294479</v>
+        <v>60160</v>
       </c>
       <c r="N116" t="n">
         <v>0</v>
@@ -7188,7 +7207,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7207,31 +7226,31 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>-25663686</v>
+        <v>115085</v>
       </c>
       <c r="F117" t="n">
-        <v>-25663686</v>
+        <v>115085</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H117" t="n">
-        <v>-33479044</v>
+        <v>115085</v>
       </c>
       <c r="I117" t="n">
-        <v>-30.45</v>
+        <v>-0</v>
       </c>
       <c r="J117" t="n">
-        <v>11200724</v>
+        <v>169640</v>
       </c>
       <c r="K117" t="n">
-        <v>11200724</v>
+        <v>169640</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>11200724</v>
+        <v>169640</v>
       </c>
       <c r="N117" t="n">
         <v>0</v>
@@ -7240,7 +7259,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7259,31 +7278,31 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>28542148</v>
+        <v>115085</v>
       </c>
       <c r="F118" t="n">
-        <v>28542148</v>
+        <v>115085</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H118" t="n">
-        <v>20726790</v>
+        <v>115085</v>
       </c>
       <c r="I118" t="n">
-        <v>-27.38</v>
+        <v>-0</v>
       </c>
       <c r="J118" t="n">
-        <v>-11368952</v>
+        <v>38676</v>
       </c>
       <c r="K118" t="n">
-        <v>-11368952</v>
+        <v>38676</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>-11368952</v>
+        <v>38676</v>
       </c>
       <c r="N118" t="n">
         <v>0</v>
@@ -7292,7 +7311,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7311,31 +7330,31 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>-28695947</v>
+        <v>115085</v>
       </c>
       <c r="F119" t="n">
-        <v>-28695947</v>
+        <v>115085</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H119" t="n">
-        <v>-36511305</v>
+        <v>115085</v>
       </c>
       <c r="I119" t="n">
-        <v>-27.24</v>
+        <v>-0</v>
       </c>
       <c r="J119" t="n">
-        <v>11280866</v>
+        <v>191116</v>
       </c>
       <c r="K119" t="n">
-        <v>11280866</v>
+        <v>191116</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>11280866</v>
+        <v>191116</v>
       </c>
       <c r="N119" t="n">
         <v>0</v>
@@ -7344,7 +7363,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7363,45 +7382,45 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>15800538</v>
+        <v>115085</v>
       </c>
       <c r="F120" t="n">
-        <v>15800538</v>
+        <v>115085</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H120" t="n">
-        <v>7985180</v>
+        <v>115085</v>
       </c>
       <c r="I120" t="n">
-        <v>-49.46</v>
+        <v>-0</v>
       </c>
       <c r="J120" t="n">
-        <v>-5666053</v>
+        <v>65520</v>
       </c>
       <c r="K120" t="n">
-        <v>-5666053</v>
+        <v>65520</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M120" t="n">
-        <v>-5666053</v>
+        <v>65520</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7415,45 +7434,45 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5095195</v>
+        <v>-20583468</v>
       </c>
       <c r="F121" t="n">
-        <v>5095195</v>
+        <v>-20583468</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>9925728</v>
+        <v>-28592231</v>
       </c>
       <c r="I121" t="n">
-        <v>94.81</v>
+        <v>-38.91</v>
       </c>
       <c r="J121" t="n">
-        <v>-133984</v>
+        <v>7629990</v>
       </c>
       <c r="K121" t="n">
-        <v>-133984</v>
+        <v>7629990</v>
       </c>
       <c r="L121" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>-133984</v>
+        <v>7629990</v>
       </c>
       <c r="N121" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7467,31 +7486,31 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>-1947982</v>
+        <v>10216101</v>
       </c>
       <c r="F122" t="n">
-        <v>-1947982</v>
+        <v>10216101</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>2882551</v>
+        <v>2207338</v>
       </c>
       <c r="I122" t="n">
-        <v>247.98</v>
+        <v>-78.39</v>
       </c>
       <c r="J122" t="n">
-        <v>53192</v>
+        <v>-4518805</v>
       </c>
       <c r="K122" t="n">
-        <v>53192</v>
+        <v>-4518804</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>53192</v>
+        <v>-4518804</v>
       </c>
       <c r="N122" t="n">
         <v>0</v>
@@ -7500,12 +7519,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7519,31 +7538,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>-4869384</v>
+        <v>25497392</v>
       </c>
       <c r="F123" t="n">
-        <v>-4869384</v>
+        <v>25497392</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>-38851</v>
+        <v>17488629</v>
       </c>
       <c r="I123" t="n">
-        <v>99.2</v>
+        <v>-31.41</v>
       </c>
       <c r="J123" t="n">
-        <v>132911</v>
+        <v>-11325156</v>
       </c>
       <c r="K123" t="n">
-        <v>132911</v>
+        <v>-11325156</v>
       </c>
       <c r="L123" t="n">
         <v>-0</v>
       </c>
       <c r="M123" t="n">
-        <v>132911</v>
+        <v>-11325156</v>
       </c>
       <c r="N123" t="n">
         <v>-0</v>
@@ -7552,12 +7571,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7571,31 +7590,31 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4872971</v>
+        <v>-25641342</v>
       </c>
       <c r="F124" t="n">
-        <v>4872971</v>
+        <v>-25641342</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>9703504</v>
+        <v>-33650105</v>
       </c>
       <c r="I124" t="n">
-        <v>99.13</v>
+        <v>-31.23</v>
       </c>
       <c r="J124" t="n">
-        <v>-132616</v>
+        <v>11230917</v>
       </c>
       <c r="K124" t="n">
-        <v>-132616</v>
+        <v>11230917</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>-132616</v>
+        <v>11230917</v>
       </c>
       <c r="N124" t="n">
         <v>0</v>
@@ -7604,12 +7623,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7623,45 +7642,45 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>-6493697</v>
+        <v>28505378</v>
       </c>
       <c r="F125" t="n">
-        <v>-6493697</v>
+        <v>28505378</v>
       </c>
       <c r="G125" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>-1663164</v>
+        <v>20496615</v>
       </c>
       <c r="I125" t="n">
-        <v>74.39</v>
+        <v>-28.1</v>
       </c>
       <c r="J125" t="n">
-        <v>173078</v>
+        <v>-11390908</v>
       </c>
       <c r="K125" t="n">
-        <v>173078</v>
+        <v>-11390908</v>
       </c>
       <c r="L125" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>173078</v>
+        <v>-11390908</v>
       </c>
       <c r="N125" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7675,31 +7694,31 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6499475</v>
+        <v>-28659209</v>
       </c>
       <c r="F126" t="n">
-        <v>6499475</v>
+        <v>-28659209</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>11330008</v>
+        <v>-36667972</v>
       </c>
       <c r="I126" t="n">
-        <v>74.31999999999999</v>
+        <v>-27.94</v>
       </c>
       <c r="J126" t="n">
-        <v>-172687</v>
+        <v>11302491</v>
       </c>
       <c r="K126" t="n">
-        <v>-172687</v>
+        <v>11302491</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>-172687</v>
+        <v>11302491</v>
       </c>
       <c r="N126" t="n">
         <v>0</v>
@@ -7708,12 +7727,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7727,31 +7746,31 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>-4096856</v>
+        <v>15774621</v>
       </c>
       <c r="F127" t="n">
-        <v>-4096856</v>
+        <v>15774621</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H127" t="n">
-        <v>733677</v>
+        <v>7765858</v>
       </c>
       <c r="I127" t="n">
-        <v>117.91</v>
+        <v>-50.77</v>
       </c>
       <c r="J127" t="n">
-        <v>107486</v>
+        <v>-5672213</v>
       </c>
       <c r="K127" t="n">
-        <v>107486</v>
+        <v>-5672213</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>107486</v>
+        <v>-5672213</v>
       </c>
       <c r="N127" t="n">
         <v>0</v>
@@ -7765,7 +7784,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7779,31 +7798,31 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>-9599792</v>
+        <v>4725478</v>
       </c>
       <c r="F128" t="n">
-        <v>-9599792</v>
+        <v>4725478</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H128" t="n">
-        <v>-19945749</v>
+        <v>10011004</v>
       </c>
       <c r="I128" t="n">
-        <v>-107.77</v>
+        <v>111.85</v>
       </c>
       <c r="J128" t="n">
-        <v>513639</v>
+        <v>-272641</v>
       </c>
       <c r="K128" t="n">
-        <v>513639</v>
+        <v>-272641</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>513639</v>
+        <v>-272641</v>
       </c>
       <c r="N128" t="n">
         <v>0</v>
@@ -7817,7 +7836,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7831,34 +7850,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3801278</v>
+        <v>-1894747</v>
       </c>
       <c r="F129" t="n">
-        <v>3801278</v>
+        <v>-1894747</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>-6544679</v>
+        <v>3390779</v>
       </c>
       <c r="I129" t="n">
-        <v>-272.17</v>
+        <v>278.96</v>
       </c>
       <c r="J129" t="n">
-        <v>-206351</v>
+        <v>109622</v>
       </c>
       <c r="K129" t="n">
-        <v>-206351</v>
+        <v>109622</v>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M129" t="n">
-        <v>-206351</v>
+        <v>109622</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="130">
@@ -7869,7 +7888,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7883,31 +7902,31 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>9499569</v>
+        <v>-4734667</v>
       </c>
       <c r="F130" t="n">
-        <v>9499569</v>
+        <v>-4734667</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>-846388</v>
+        <v>550859</v>
       </c>
       <c r="I130" t="n">
-        <v>-108.91</v>
+        <v>111.63</v>
       </c>
       <c r="J130" t="n">
-        <v>-515967</v>
+        <v>274053</v>
       </c>
       <c r="K130" t="n">
-        <v>-515967</v>
+        <v>274053</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>-515967</v>
+        <v>274053</v>
       </c>
       <c r="N130" t="n">
         <v>0</v>
@@ -7921,7 +7940,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7935,31 +7954,31 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>-9511584</v>
+        <v>4740819</v>
       </c>
       <c r="F131" t="n">
-        <v>-9511584</v>
+        <v>4740819</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H131" t="n">
-        <v>-19857541</v>
+        <v>10026345</v>
       </c>
       <c r="I131" t="n">
-        <v>-108.77</v>
+        <v>111.49</v>
       </c>
       <c r="J131" t="n">
-        <v>514892</v>
+        <v>-273525</v>
       </c>
       <c r="K131" t="n">
-        <v>514892</v>
+        <v>-273525</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>514892</v>
+        <v>-273525</v>
       </c>
       <c r="N131" t="n">
         <v>0</v>
@@ -7973,7 +7992,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7987,34 +8006,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>12359339</v>
+        <v>-6106983</v>
       </c>
       <c r="F132" t="n">
-        <v>12359339</v>
+        <v>-6106983</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>2013382</v>
+        <v>-821457</v>
       </c>
       <c r="I132" t="n">
-        <v>-83.70999999999999</v>
+        <v>86.55</v>
       </c>
       <c r="J132" t="n">
-        <v>-666146</v>
+        <v>353607</v>
       </c>
       <c r="K132" t="n">
-        <v>-666145</v>
+        <v>353607</v>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M132" t="n">
-        <v>-666145</v>
+        <v>353607</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="133">
@@ -8025,7 +8044,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8039,31 +8058,31 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>-12379415</v>
+        <v>6117463</v>
       </c>
       <c r="F133" t="n">
-        <v>-12379415</v>
+        <v>6117463</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>-22725372</v>
+        <v>11402989</v>
       </c>
       <c r="I133" t="n">
-        <v>-83.56999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J133" t="n">
-        <v>664509</v>
+        <v>-352831</v>
       </c>
       <c r="K133" t="n">
-        <v>664509</v>
+        <v>-352831</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>664509</v>
+        <v>-352831</v>
       </c>
       <c r="N133" t="n">
         <v>0</v>
@@ -8077,7 +8096,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8091,40 +8110,40 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>7674284</v>
+        <v>-3770245</v>
       </c>
       <c r="F134" t="n">
-        <v>7674284</v>
+        <v>-3770245</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>-2671673</v>
+        <v>1515281</v>
       </c>
       <c r="I134" t="n">
-        <v>-134.81</v>
+        <v>140.19</v>
       </c>
       <c r="J134" t="n">
-        <v>-411137</v>
+        <v>218183</v>
       </c>
       <c r="K134" t="n">
-        <v>-411137</v>
+        <v>218183</v>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M134" t="n">
-        <v>-411137</v>
+        <v>218183</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8143,31 +8162,31 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>-9116752</v>
+        <v>-9485152</v>
       </c>
       <c r="F135" t="n">
-        <v>-9116752</v>
+        <v>-9485152</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>-9116752</v>
+        <v>-20023131</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>-111.1</v>
       </c>
       <c r="J135" t="n">
-        <v>-3899855</v>
+        <v>527204</v>
       </c>
       <c r="K135" t="n">
-        <v>-3899855</v>
+        <v>527204</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>-3899855</v>
+        <v>527204</v>
       </c>
       <c r="N135" t="n">
         <v>0</v>
@@ -8176,7 +8195,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8195,40 +8214,40 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>9572302</v>
+        <v>3796194</v>
       </c>
       <c r="F136" t="n">
-        <v>9572302</v>
+        <v>3796194</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>9572302</v>
+        <v>-6741785</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>-277.59</v>
       </c>
       <c r="J136" t="n">
-        <v>-7987569</v>
+        <v>-211836</v>
       </c>
       <c r="K136" t="n">
-        <v>-7987569</v>
+        <v>-211836</v>
       </c>
       <c r="L136" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>-7987569</v>
+        <v>-211836</v>
       </c>
       <c r="N136" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8247,31 +8266,31 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>23919968</v>
+        <v>9486669</v>
       </c>
       <c r="F137" t="n">
-        <v>23919968</v>
+        <v>9486669</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>23919968</v>
+        <v>-1051310</v>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>-111.08</v>
       </c>
       <c r="J137" t="n">
-        <v>-20302736</v>
+        <v>-529655</v>
       </c>
       <c r="K137" t="n">
-        <v>-20302736</v>
+        <v>-529655</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>-20302736</v>
+        <v>-529655</v>
       </c>
       <c r="N137" t="n">
         <v>0</v>
@@ -8280,7 +8299,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8299,31 +8318,31 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>-23961716</v>
+        <v>-9499085</v>
       </c>
       <c r="F138" t="n">
-        <v>-23961716</v>
+        <v>-9499085</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>-23961716</v>
+        <v>-20037064</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>-110.94</v>
       </c>
       <c r="J138" t="n">
-        <v>19221026</v>
+        <v>528678</v>
       </c>
       <c r="K138" t="n">
-        <v>19221026</v>
+        <v>528678</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>19221026</v>
+        <v>528678</v>
       </c>
       <c r="N138" t="n">
         <v>0</v>
@@ -8332,7 +8351,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8351,31 +8370,31 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>17720530</v>
+        <v>12251480</v>
       </c>
       <c r="F139" t="n">
-        <v>17720530</v>
+        <v>12251480</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>17720530</v>
+        <v>1713501</v>
       </c>
       <c r="I139" t="n">
-        <v>0</v>
+        <v>-86.01000000000001</v>
       </c>
       <c r="J139" t="n">
-        <v>-4519419</v>
+        <v>-683634</v>
       </c>
       <c r="K139" t="n">
-        <v>-4519419</v>
+        <v>-683634</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>-4519419</v>
+        <v>-683634</v>
       </c>
       <c r="N139" t="n">
         <v>0</v>
@@ -8384,7 +8403,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8403,31 +8422,31 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>-17742255</v>
+        <v>-12272248</v>
       </c>
       <c r="F140" t="n">
-        <v>-17742255</v>
+        <v>-12272248</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>-17742255</v>
+        <v>-22810227</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>-85.87</v>
       </c>
       <c r="J140" t="n">
-        <v>4476162</v>
+        <v>682154</v>
       </c>
       <c r="K140" t="n">
-        <v>4476162</v>
+        <v>682154</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>4476162</v>
+        <v>682154</v>
       </c>
       <c r="N140" t="n">
         <v>0</v>
@@ -8436,52 +8455,416 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>7900</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>steep</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>7569703</v>
+      </c>
+      <c r="F141" t="n">
+        <v>7569703</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-2968276</v>
+      </c>
+      <c r="I141" t="n">
+        <v>-139.21</v>
+      </c>
+      <c r="J141" t="n">
+        <v>-421882</v>
+      </c>
+      <c r="K141" t="n">
+        <v>-421882</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>-421882</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>8000</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>-9116752</v>
+      </c>
+      <c r="F142" t="n">
+        <v>-9116752</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>-9116752</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>-3929245</v>
+      </c>
+      <c r="K142" t="n">
+        <v>-3929245</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>-3929245</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>9572302</v>
+      </c>
+      <c r="F143" t="n">
+        <v>9572302</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>9572302</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>-8047020</v>
+      </c>
+      <c r="K143" t="n">
+        <v>-8047020</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>-8047020</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>par_dn</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>23919968</v>
+      </c>
+      <c r="F144" t="n">
+        <v>23919968</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>23919968</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>-20892614</v>
+      </c>
+      <c r="K144" t="n">
+        <v>-20892614</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>-20892614</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>par_up</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>-23961716</v>
+      </c>
+      <c r="F145" t="n">
+        <v>-23961716</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>-23961716</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>19364375</v>
+      </c>
+      <c r="K145" t="n">
+        <v>19364375</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>19364375</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>sr_dn</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>17720530</v>
+      </c>
+      <c r="F146" t="n">
+        <v>17720530</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>17720530</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>-4552708</v>
+      </c>
+      <c r="K146" t="n">
+        <v>-4552708</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>-4552708</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>sr_up</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>-17742255</v>
+      </c>
+      <c r="F147" t="n">
+        <v>-17742255</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>-17742255</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>4509117</v>
+      </c>
+      <c r="K147" t="n">
+        <v>4509117</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>4509117</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
         <is>
           <t>steep</t>
         </is>
       </c>
-      <c r="E141" t="n">
+      <c r="E148" t="n">
         <v>5432057</v>
       </c>
-      <c r="F141" t="n">
+      <c r="F148" t="n">
         <v>5432057</v>
       </c>
-      <c r="G141" t="n">
-        <v>0</v>
-      </c>
-      <c r="H141" t="n">
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
         <v>5432057</v>
       </c>
-      <c r="I141" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" t="n">
-        <v>5917025</v>
-      </c>
-      <c r="K141" t="n">
-        <v>5917025</v>
-      </c>
-      <c r="L141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" t="n">
-        <v>5917025</v>
-      </c>
-      <c r="N141" t="n">
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>5961600</v>
+      </c>
+      <c r="K148" t="n">
+        <v>5961600</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>5961600</v>
+      </c>
+      <c r="N148" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8543,13 +8926,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.7735</v>
+        <v>3.6404</v>
       </c>
       <c r="C2" t="n">
-        <v>2.714</v>
+        <v>3.5931</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.15</v>
+        <v>-1.3</v>
       </c>
       <c r="E2" t="n">
         <v>1.609</v>
@@ -8654,10 +9037,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>614386177</v>
+        <v>612070585</v>
       </c>
       <c r="E2" t="n">
-        <v>614386177</v>
+        <v>612070585</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -8692,10 +9075,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2174256630</v>
+        <v>2192247143</v>
       </c>
       <c r="E3" t="n">
-        <v>2174256630</v>
+        <v>2192247143</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -8730,22 +9113,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>42626951</v>
+        <v>61073263</v>
       </c>
       <c r="E4" t="n">
-        <v>42608851</v>
+        <v>60753195</v>
       </c>
       <c r="F4" t="n">
-        <v>3.55</v>
+        <v>5.09</v>
       </c>
       <c r="G4" t="n">
-        <v>3.55</v>
+        <v>5.06</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04</v>
+        <v>-0.52</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.002</v>
+        <v>-0.027</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -8776,22 +9159,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-85376945</v>
+        <v>-56451591</v>
       </c>
       <c r="E5" t="n">
-        <v>-85757551</v>
+        <v>-56451594</v>
       </c>
       <c r="F5" t="n">
-        <v>-7.11</v>
+        <v>-4.7</v>
       </c>
       <c r="G5" t="n">
-        <v>-7.15</v>
+        <v>-4.7</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.45</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.032</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -8822,22 +9205,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-42539254</v>
+        <v>-56816160</v>
       </c>
       <c r="E6" t="n">
-        <v>-42527524</v>
+        <v>-56545000</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.54</v>
+        <v>-4.73</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.54</v>
+        <v>-4.71</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03</v>
+        <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001</v>
+        <v>0.023</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -8868,22 +9251,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>92956303</v>
+        <v>61405875</v>
       </c>
       <c r="E7" t="n">
-        <v>93340139</v>
+        <v>61405877</v>
       </c>
       <c r="F7" t="n">
-        <v>7.75</v>
+        <v>5.12</v>
       </c>
       <c r="G7" t="n">
-        <v>7.78</v>
+        <v>5.12</v>
       </c>
       <c r="H7" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -8914,22 +9297,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>32979980</v>
+        <v>26536310</v>
       </c>
       <c r="E8" t="n">
-        <v>32929026</v>
+        <v>26538599</v>
       </c>
       <c r="F8" t="n">
-        <v>2.75</v>
+        <v>2.21</v>
       </c>
       <c r="G8" t="n">
-        <v>2.74</v>
+        <v>2.21</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.15</v>
+        <v>0.01</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.004</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -8960,26 +9343,26 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-15889560</v>
+        <v>-3911609</v>
       </c>
       <c r="E9" t="n">
-        <v>-15696710</v>
+        <v>-3911606</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.32</v>
+        <v>-0.33</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.31</v>
+        <v>-0.33</v>
       </c>
       <c r="H9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -9006,22 +9389,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-29938964</v>
+        <v>-16482595</v>
       </c>
       <c r="E10" t="n">
-        <v>-29894772</v>
+        <v>-16577325</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.49</v>
+        <v>-1.37</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.49</v>
+        <v>-1.38</v>
       </c>
       <c r="H10" t="n">
-        <v>0.15</v>
+        <v>-0.57</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004</v>
+        <v>-0.008</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -9052,26 +9435,26 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7679373</v>
+        <v>-1311343</v>
       </c>
       <c r="E11" t="n">
-        <v>7420111</v>
+        <v>-1311344</v>
       </c>
       <c r="F11" t="n">
-        <v>0.64</v>
+        <v>-0.11</v>
       </c>
       <c r="G11" t="n">
-        <v>0.62</v>
+        <v>-0.11</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.38</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.022</v>
+        <v>-0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -9098,26 +9481,26 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-9643667</v>
+        <v>9155647</v>
       </c>
       <c r="E12" t="n">
-        <v>-9610215</v>
+        <v>8950114</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8</v>
+        <v>0.76</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8</v>
+        <v>0.75</v>
       </c>
       <c r="H12" t="n">
-        <v>0.35</v>
+        <v>-2.24</v>
       </c>
       <c r="I12" t="n">
-        <v>0.003</v>
+        <v>-0.017</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -9144,26 +9527,26 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-29156513</v>
+        <v>-24938632</v>
       </c>
       <c r="E13" t="n">
-        <v>-29540169</v>
+        <v>-24938633</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.43</v>
+        <v>-2.08</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.46</v>
+        <v>-2.08</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.32</v>
+        <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.032</v>
+        <v>-0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -9190,26 +9573,26 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9588789</v>
+        <v>-5077214</v>
       </c>
       <c r="E14" t="n">
-        <v>9547811</v>
+        <v>-4921435</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8</v>
+        <v>-0.42</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8</v>
+        <v>-0.41</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.43</v>
+        <v>3.07</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.003</v>
+        <v>0.013</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -9236,26 +9619,26 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>30551372</v>
+        <v>26790116</v>
       </c>
       <c r="E15" t="n">
-        <v>30938006</v>
+        <v>26790115</v>
       </c>
       <c r="F15" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="G15" t="n">
-        <v>2.58</v>
+        <v>2.23</v>
       </c>
       <c r="H15" t="n">
-        <v>1.27</v>
+        <v>-0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.032</v>
+        <v>-0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -9282,22 +9665,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-16991582</v>
+        <v>-21484633</v>
       </c>
       <c r="E16" t="n">
-        <v>-16989782</v>
+        <v>-21391314</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.42</v>
+        <v>-1.79</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.42</v>
+        <v>-1.78</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01</v>
+        <v>0.43</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -9328,22 +9711,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>36673523</v>
+        <v>24726512</v>
       </c>
       <c r="E17" t="n">
-        <v>36826672</v>
+        <v>24726512</v>
       </c>
       <c r="F17" t="n">
-        <v>3.06</v>
+        <v>2.06</v>
       </c>
       <c r="G17" t="n">
-        <v>3.07</v>
+        <v>2.06</v>
       </c>
       <c r="H17" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -9374,20 +9757,20 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>-2.15</v>
+        <v>-1.3</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -9444,7 +9827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9529,20 +9912,20 @@
         <v>1800000000</v>
       </c>
       <c r="E2" t="n">
-        <v>15.4577</v>
+        <v>15.4375</v>
       </c>
       <c r="F2" t="n">
-        <v>15.4577</v>
+        <v>15.4375</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.208654</v>
+        <v>1.204055</v>
       </c>
       <c r="J2" t="n">
-        <v>1.208654</v>
+        <v>1.204055</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -9571,20 +9954,20 @@
         <v>600000000</v>
       </c>
       <c r="E3" t="n">
-        <v>13.0693</v>
+        <v>13.0671</v>
       </c>
       <c r="F3" t="n">
-        <v>13.0693</v>
+        <v>13.0671</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.20317</v>
+        <v>1.208762</v>
       </c>
       <c r="J3" t="n">
-        <v>1.20317</v>
+        <v>1.208762</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -9613,20 +9996,20 @@
         <v>1000000000</v>
       </c>
       <c r="E4" t="n">
-        <v>7.418</v>
+        <v>7.3602</v>
       </c>
       <c r="F4" t="n">
-        <v>7.418</v>
+        <v>7.3602</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1.036984</v>
+        <v>1.038313</v>
       </c>
       <c r="J4" t="n">
-        <v>1.036984</v>
+        <v>1.038313</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -9655,20 +10038,20 @@
         <v>2800000000</v>
       </c>
       <c r="E5" t="n">
-        <v>7.3742</v>
+        <v>7.3391</v>
       </c>
       <c r="F5" t="n">
-        <v>7.3742</v>
+        <v>7.3391</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1.067913</v>
+        <v>1.068395</v>
       </c>
       <c r="J5" t="n">
-        <v>1.067913</v>
+        <v>1.068395</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -9697,20 +10080,20 @@
         <v>600000000</v>
       </c>
       <c r="E6" t="n">
-        <v>6.9982</v>
+        <v>6.8716</v>
       </c>
       <c r="F6" t="n">
-        <v>6.9982</v>
+        <v>6.8716</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1.044762</v>
+        <v>1.043497</v>
       </c>
       <c r="J6" t="n">
-        <v>1.044762</v>
+        <v>1.043497</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -9736,23 +10119,23 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1200000000</v>
+        <v>800000000</v>
       </c>
       <c r="E7" t="n">
-        <v>6.431</v>
+        <v>6.4844</v>
       </c>
       <c r="F7" t="n">
-        <v>6.431</v>
+        <v>6.4844</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1.049889</v>
+        <v>1.048341</v>
       </c>
       <c r="J7" t="n">
-        <v>1.049889</v>
+        <v>1.048341</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -9781,20 +10164,20 @@
         <v>200000000</v>
       </c>
       <c r="E8" t="n">
-        <v>5.5679</v>
+        <v>5.7952</v>
       </c>
       <c r="F8" t="n">
-        <v>5.5679</v>
+        <v>5.7952</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>1.000024</v>
+        <v>1.000014</v>
       </c>
       <c r="J8" t="n">
-        <v>1.000024</v>
+        <v>1.000014</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -9823,22 +10206,24 @@
         <v>1600000000</v>
       </c>
       <c r="E9" t="n">
-        <v>5.0779</v>
+        <v>5.6888</v>
       </c>
       <c r="F9" t="n">
-        <v>5.0779</v>
+        <v>5.6888</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.889111</v>
+        <v>1.006951</v>
       </c>
       <c r="J9" t="n">
-        <v>0.889111</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>1.006951</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
       <c r="L9" t="b">
         <v>1</v>
       </c>
@@ -9846,7 +10231,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -9860,25 +10245,27 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>420000000</v>
+        <v>400000000</v>
       </c>
       <c r="E10" t="n">
-        <v>4.5044</v>
+        <v>5.1067</v>
       </c>
       <c r="F10" t="n">
-        <v>4.5044</v>
+        <v>5.1067</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.11988</v>
+        <v>1.000025</v>
       </c>
       <c r="J10" t="n">
-        <v>0.11988</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+        <v>1.000025</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" t="b">
         <v>1</v>
       </c>
@@ -9886,7 +10273,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -9900,23 +10287,23 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>200000000</v>
+        <v>420000000</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>4.5044</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>4.5044</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.120171</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.120171</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="b">
@@ -9926,12 +10313,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -9940,7 +10327,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>400000000</v>
+        <v>200000000</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -9966,7 +10353,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -10006,7 +10393,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -10046,12 +10433,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -10060,7 +10447,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3400000000</v>
+        <v>400000000</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10073,10 +10460,10 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.885872</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.885872</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="b">
@@ -10086,7 +10473,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -10100,23 +10487,23 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>400000000</v>
+        <v>3400000000</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0288</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0288</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-1</v>
+        <v>-0.888948</v>
       </c>
       <c r="J16" t="n">
-        <v>-1</v>
+        <v>-0.888948</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="b">
@@ -10126,7 +10513,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -10140,23 +10527,23 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1600000000</v>
+        <v>400000000</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.5067</v>
+        <v>-0.0288</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.5067</v>
+        <v>-0.0288</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.977088</v>
+        <v>-1</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.977088</v>
+        <v>-1</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="b">
@@ -10166,7 +10553,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -10180,23 +10567,23 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1800000000</v>
+        <v>1600000000</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.8373</v>
+        <v>-3.5067</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.8373</v>
+        <v>-3.5067</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.997497</v>
+        <v>-0.979131</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.997497</v>
+        <v>-0.979131</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="b">
@@ -10206,7 +10593,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -10220,23 +10607,23 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1200000000</v>
+        <v>1800000000</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.2845</v>
+        <v>-4.837</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.2845</v>
+        <v>-4.837</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.900323</v>
+        <v>-0.99749</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.900323</v>
+        <v>-0.99749</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="b">
@@ -10273,10 +10660,10 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.140065</v>
+        <v>-0.136045</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.140065</v>
+        <v>-0.136045</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="b">
@@ -10286,7 +10673,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -10300,28 +10687,70 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>400000000</v>
+        <v>1200000000</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.739</v>
+        <v>-5.6836</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.739</v>
+        <v>-5.6836</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="n">
+        <v>-1.012372</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-1.012372</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>7900</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>400000000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-5.787</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-5.787</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
         <v>-1.000014</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>-1.000014</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="b">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="b">
         <v>1</v>
       </c>
     </row>

--- a/optimize_prep/output/approx_accuracy_report.xlsx
+++ b/optimize_prep/output/approx_accuracy_report.xlsx
@@ -504,16 +504,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18918685</v>
+        <v>18912329</v>
       </c>
       <c r="E2" t="n">
-        <v>18918685</v>
+        <v>18912329</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>18918685</v>
+        <v>18912329</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -522,10 +522,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50471836</v>
+        <v>51541880</v>
       </c>
       <c r="K2" t="n">
-        <v>50471836</v>
+        <v>51541880</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -551,16 +551,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-23726519</v>
+        <v>-16333649</v>
       </c>
       <c r="E3" t="n">
-        <v>-23726519</v>
+        <v>-16333649</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-23726519</v>
+        <v>-16333649</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -569,10 +569,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-57138860</v>
+        <v>-43648352</v>
       </c>
       <c r="K3" t="n">
-        <v>-57138860</v>
+        <v>-43648352</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -598,34 +598,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>73602100</v>
+        <v>62524947</v>
       </c>
       <c r="E4" t="n">
-        <v>73602100</v>
+        <v>62524947</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>56013584</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-10.41</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6511363</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1040741358</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1040741358</v>
+      </c>
+      <c r="L4" t="n">
         <v>-0</v>
       </c>
-      <c r="G4" t="n">
-        <v>66390593</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="I4" t="n">
-        <v>7211507</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1038312661</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1038312661</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -645,34 +645,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>205495042</v>
+        <v>161220249</v>
       </c>
       <c r="E5" t="n">
-        <v>205495042</v>
+        <v>161220249</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G5" t="n">
-        <v>144776148</v>
+        <v>107719453</v>
       </c>
       <c r="H5" t="n">
-        <v>-29.55</v>
+        <v>-33.18</v>
       </c>
       <c r="I5" t="n">
-        <v>60718894</v>
+        <v>53500797</v>
       </c>
       <c r="J5" t="n">
-        <v>2991506171</v>
+        <v>3002169303</v>
       </c>
       <c r="K5" t="n">
-        <v>2991506171</v>
+        <v>3002169303</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -692,28 +692,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>78402720</v>
+        <v>103931989</v>
       </c>
       <c r="E6" t="n">
-        <v>78402720</v>
+        <v>103931989</v>
       </c>
       <c r="F6" t="n">
         <v>-0</v>
       </c>
       <c r="G6" t="n">
-        <v>70098101</v>
+        <v>93674632</v>
       </c>
       <c r="H6" t="n">
-        <v>-10.59</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>8304619</v>
+        <v>10257358</v>
       </c>
       <c r="J6" t="n">
-        <v>725257243</v>
+        <v>1087394962</v>
       </c>
       <c r="K6" t="n">
-        <v>725257243</v>
+        <v>1087394962</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -739,34 +739,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>277875695</v>
+        <v>206226421</v>
       </c>
       <c r="E7" t="n">
-        <v>277875695</v>
+        <v>206226421</v>
       </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>183854038</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-10.85</v>
+      </c>
+      <c r="I7" t="n">
+        <v>22372383</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1794438346</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1794438346</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>-0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>246758061</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-11.2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>31117634</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2167298715</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2167298715</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -786,28 +786,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>51875442</v>
+        <v>64363634</v>
       </c>
       <c r="E8" t="n">
-        <v>51875442</v>
+        <v>64363634</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>51788172</v>
+        <v>62835467</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.17</v>
+        <v>-2.37</v>
       </c>
       <c r="I8" t="n">
-        <v>87271</v>
+        <v>1528167</v>
       </c>
       <c r="J8" t="n">
-        <v>838672584</v>
+        <v>1365717822</v>
       </c>
       <c r="K8" t="n">
-        <v>838672584</v>
+        <v>1365717822</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -833,34 +833,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>91020058</v>
+        <v>44879720</v>
       </c>
       <c r="E9" t="n">
-        <v>91020058</v>
+        <v>44879720</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>81947554</v>
+        <v>43924259</v>
       </c>
       <c r="H9" t="n">
-        <v>-9.970000000000001</v>
+        <v>-2.13</v>
       </c>
       <c r="I9" t="n">
-        <v>9072504</v>
+        <v>955461</v>
       </c>
       <c r="J9" t="n">
-        <v>1611121593</v>
+        <v>1139220439</v>
       </c>
       <c r="K9" t="n">
-        <v>1611121593</v>
+        <v>1139220439</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -880,28 +880,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20426849</v>
+        <v>6016986</v>
       </c>
       <c r="E10" t="n">
-        <v>20426849</v>
+        <v>6016986</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>23320287</v>
+        <v>7479859</v>
       </c>
       <c r="H10" t="n">
-        <v>14.16</v>
+        <v>24.31</v>
       </c>
       <c r="I10" t="n">
-        <v>-2893438</v>
+        <v>-1462873</v>
       </c>
       <c r="J10" t="n">
-        <v>400010075</v>
+        <v>199999668</v>
       </c>
       <c r="K10" t="n">
-        <v>400010075</v>
+        <v>199999668</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -968,28 +968,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>41229538</v>
+        <v>30917064</v>
       </c>
       <c r="E12" t="n">
-        <v>41229538</v>
+        <v>30917064</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>26940434</v>
+        <v>20450890</v>
       </c>
       <c r="H12" t="n">
-        <v>-34.66</v>
+        <v>-33.85</v>
       </c>
       <c r="I12" t="n">
-        <v>14289104</v>
+        <v>10466173</v>
       </c>
       <c r="J12" t="n">
-        <v>626098087</v>
+        <v>622779011</v>
       </c>
       <c r="K12" t="n">
-        <v>626098087</v>
+        <v>622779011</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1015,31 +1015,31 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-68203209</v>
+        <v>-47087873</v>
       </c>
       <c r="E13" t="n">
-        <v>-68203209</v>
+        <v>-47087873</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G13" t="n">
-        <v>-62888069</v>
+        <v>-45743687</v>
       </c>
       <c r="H13" t="n">
-        <v>7.79</v>
+        <v>2.85</v>
       </c>
       <c r="I13" t="n">
-        <v>-5315140</v>
+        <v>-1344186</v>
       </c>
       <c r="J13" t="n">
-        <v>-1214846259</v>
+        <v>-1207014536</v>
       </c>
       <c r="K13" t="n">
-        <v>-1214846259</v>
+        <v>-1207014536</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1199,10 +1199,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-3022423710</v>
+        <v>-3107336432</v>
       </c>
       <c r="K17" t="n">
-        <v>-3022423710</v>
+        <v>-3107336432</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-115085</v>
+        <v>-37591</v>
       </c>
       <c r="E18" t="n">
-        <v>-115085</v>
+        <v>-37591</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G18" t="n">
-        <v>-115085</v>
+        <v>-37591</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1246,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-399999852</v>
+        <v>-399999987</v>
       </c>
       <c r="K18" t="n">
-        <v>-399999852</v>
+        <v>-399999987</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1275,28 +1275,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-87065677</v>
+        <v>-59930073</v>
       </c>
       <c r="E19" t="n">
-        <v>-87065677</v>
+        <v>-59930073</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-79056914</v>
+        <v>-54701293</v>
       </c>
       <c r="H19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-8008763</v>
+        <v>-5228780</v>
       </c>
       <c r="J19" t="n">
-        <v>-1795481344</v>
+        <v>-1769437421</v>
       </c>
       <c r="K19" t="n">
-        <v>-1795481344</v>
+        <v>-1769437421</v>
       </c>
       <c r="L19" t="n">
         <v>-0</v>
@@ -1322,28 +1322,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11590471</v>
+        <v>7123275</v>
       </c>
       <c r="E20" t="n">
-        <v>11590471</v>
+        <v>7123275</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G20" t="n">
-        <v>6304945</v>
+        <v>4094832</v>
       </c>
       <c r="H20" t="n">
-        <v>-45.6</v>
+        <v>-42.51</v>
       </c>
       <c r="I20" t="n">
-        <v>5285526</v>
+        <v>3028443</v>
       </c>
       <c r="J20" t="n">
-        <v>200002790</v>
+        <v>200001856</v>
       </c>
       <c r="K20" t="n">
-        <v>200002790</v>
+        <v>200001856</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1369,28 +1369,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-23147982</v>
+        <v>-14836517</v>
       </c>
       <c r="E21" t="n">
-        <v>-23147982</v>
+        <v>-14836517</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-12610003</v>
+        <v>-8189827</v>
       </c>
       <c r="H21" t="n">
-        <v>45.52</v>
+        <v>44.8</v>
       </c>
       <c r="I21" t="n">
-        <v>-10537979</v>
+        <v>-6646690</v>
       </c>
       <c r="J21" t="n">
-        <v>-400005771</v>
+        <v>-400003152</v>
       </c>
       <c r="K21" t="n">
-        <v>-400005771</v>
+        <v>-400003152</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1416,16 +1416,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-56107546</v>
+        <v>-37628267</v>
       </c>
       <c r="E22" t="n">
-        <v>-56107546</v>
+        <v>-37628267</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-56107546</v>
+        <v>-37628267</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1434,10 +1434,10 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-1566608815</v>
+        <v>-1568101452</v>
       </c>
       <c r="K22" t="n">
-        <v>-1566608815</v>
+        <v>-1568101452</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1565,16 +1565,16 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>362910</v>
+        <v>376792</v>
       </c>
       <c r="K2" t="n">
-        <v>362910</v>
+        <v>376792</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>362910</v>
+        <v>376792</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -1613,16 +1613,16 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>812915</v>
+        <v>834529</v>
       </c>
       <c r="K3" t="n">
-        <v>812915</v>
+        <v>834529</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>812915</v>
+        <v>834529</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -1661,19 +1661,19 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>2063806</v>
+        <v>2118813</v>
       </c>
       <c r="K4" t="n">
-        <v>2063806</v>
+        <v>2118813</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2063806</v>
+        <v>2118813</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1709,16 +1709,16 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>-1961472</v>
+        <v>-2013346</v>
       </c>
       <c r="K5" t="n">
-        <v>-1961472</v>
+        <v>-2013346</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1961472</v>
+        <v>-2013346</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1757,19 +1757,19 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>490284</v>
+        <v>499522</v>
       </c>
       <c r="K6" t="n">
-        <v>490284</v>
+        <v>499522</v>
       </c>
       <c r="L6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>490284</v>
+        <v>499522</v>
       </c>
       <c r="N6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1805,16 +1805,16 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>-485140</v>
+        <v>-494294</v>
       </c>
       <c r="K7" t="n">
-        <v>-485140</v>
+        <v>-494294</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-485140</v>
+        <v>-494294</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1853,16 +1853,16 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>-573587</v>
+        <v>-592634</v>
       </c>
       <c r="K8" t="n">
-        <v>-573587</v>
+        <v>-592634</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-573587</v>
+        <v>-592634</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1890,31 +1890,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>-342721</v>
+        <v>-358241</v>
       </c>
       <c r="F9" t="n">
-        <v>-342721</v>
+        <v>-358241</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-342721</v>
+        <v>-358241</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>9605830</v>
+        <v>9854888</v>
       </c>
       <c r="K9" t="n">
-        <v>9605830</v>
+        <v>9854888</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>9605830</v>
+        <v>9854888</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1942,31 +1942,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2346887</v>
+        <v>2329966</v>
       </c>
       <c r="F10" t="n">
-        <v>2346887</v>
+        <v>2329966</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2346887</v>
+        <v>2329966</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>8546347</v>
+        <v>8869291</v>
       </c>
       <c r="K10" t="n">
-        <v>8546347</v>
+        <v>8869291</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>8546347</v>
+        <v>8869291</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1994,31 +1994,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5848750</v>
+        <v>5805855</v>
       </c>
       <c r="F11" t="n">
-        <v>5848750</v>
+        <v>5805855</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5848750</v>
+        <v>5805855</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>21829742</v>
+        <v>22660022</v>
       </c>
       <c r="K11" t="n">
-        <v>21829742</v>
+        <v>22660022</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>21829742</v>
+        <v>22660022</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -2046,31 +2046,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>-5913592</v>
+        <v>-5869068</v>
       </c>
       <c r="F12" t="n">
-        <v>-5913592</v>
+        <v>-5869068</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-5913592</v>
+        <v>-5869068</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J12" t="n">
-        <v>-20299034</v>
+        <v>-21083423</v>
       </c>
       <c r="K12" t="n">
-        <v>-20299034</v>
+        <v>-21083423</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-20299034</v>
+        <v>-21083423</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2098,31 +2098,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2655201</v>
+        <v>2652353</v>
       </c>
       <c r="F13" t="n">
-        <v>2655201</v>
+        <v>2652353</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2655201</v>
+        <v>2652353</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-37802</v>
+        <v>59379</v>
       </c>
       <c r="K13" t="n">
-        <v>-37802</v>
+        <v>59379</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-37802</v>
+        <v>59379</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2150,34 +2150,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>-2671728</v>
+        <v>-2668023</v>
       </c>
       <c r="F14" t="n">
-        <v>-2671728</v>
+        <v>-2668023</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-2671728</v>
+        <v>-2668023</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>45354</v>
+        <v>-59448</v>
       </c>
       <c r="K14" t="n">
-        <v>45354</v>
+        <v>-59448</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M14" t="n">
-        <v>45354</v>
+        <v>-59448</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -2202,31 +2202,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>-419360</v>
+        <v>-398719</v>
       </c>
       <c r="F15" t="n">
-        <v>-419360</v>
+        <v>-398719</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-419360</v>
+        <v>-398719</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-11262611</v>
+        <v>-11592419</v>
       </c>
       <c r="K15" t="n">
-        <v>-11262611</v>
+        <v>-11592419</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-11262611</v>
+        <v>-11592419</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2254,31 +2254,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1380735</v>
+        <v>515466</v>
       </c>
       <c r="F16" t="n">
-        <v>1380735</v>
+        <v>515466</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>8592242</v>
+        <v>7026829</v>
       </c>
       <c r="I16" t="n">
-        <v>522.29</v>
+        <v>1263.2</v>
       </c>
       <c r="J16" t="n">
-        <v>17335131</v>
+        <v>19127645</v>
       </c>
       <c r="K16" t="n">
-        <v>17335132</v>
+        <v>19127645</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>17335132</v>
+        <v>19127645</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2306,31 +2306,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-1351464</v>
+        <v>-2112710</v>
       </c>
       <c r="F17" t="n">
-        <v>-1351464</v>
+        <v>-2112710</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5860043</v>
+        <v>4398653</v>
       </c>
       <c r="I17" t="n">
-        <v>533.61</v>
+        <v>308.2</v>
       </c>
       <c r="J17" t="n">
-        <v>23159912</v>
+        <v>24548392</v>
       </c>
       <c r="K17" t="n">
-        <v>23159912</v>
+        <v>24548393</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>23159912</v>
+        <v>24548393</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2358,34 +2358,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>-3252215</v>
+        <v>-3951763</v>
       </c>
       <c r="F18" t="n">
-        <v>-3252215</v>
+        <v>-3951763</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3959292</v>
+        <v>2559600</v>
       </c>
       <c r="I18" t="n">
-        <v>221.74</v>
+        <v>164.77</v>
       </c>
       <c r="J18" t="n">
-        <v>59438266</v>
+        <v>63098557</v>
       </c>
       <c r="K18" t="n">
-        <v>59438268</v>
+        <v>63098556</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
-        <v>59438268</v>
+        <v>63098556</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="19">
@@ -2410,34 +2410,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3092118</v>
+        <v>2186709</v>
       </c>
       <c r="F19" t="n">
-        <v>3092118</v>
+        <v>2186709</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H19" t="n">
-        <v>10303625</v>
+        <v>8698072</v>
       </c>
       <c r="I19" t="n">
-        <v>233.22</v>
+        <v>297.77</v>
       </c>
       <c r="J19" t="n">
-        <v>-54554826</v>
+        <v>-57630359</v>
       </c>
       <c r="K19" t="n">
-        <v>-54554828</v>
+        <v>-57630359</v>
       </c>
       <c r="L19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-54554828</v>
+        <v>-57630359</v>
       </c>
       <c r="N19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2462,34 +2462,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-2658217</v>
+        <v>-3362379</v>
       </c>
       <c r="F20" t="n">
-        <v>-2658217</v>
+        <v>-3362379</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4553290</v>
+        <v>3148984</v>
       </c>
       <c r="I20" t="n">
-        <v>271.29</v>
+        <v>193.65</v>
       </c>
       <c r="J20" t="n">
-        <v>7770684</v>
+        <v>7570213</v>
       </c>
       <c r="K20" t="n">
-        <v>7770683</v>
+        <v>7570217</v>
       </c>
       <c r="L20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7770683</v>
+        <v>7570217</v>
       </c>
       <c r="N20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2514,34 +2514,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2496431</v>
+        <v>1596634</v>
       </c>
       <c r="F21" t="n">
-        <v>2496431</v>
+        <v>1596634</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H21" t="n">
-        <v>9707938</v>
+        <v>8107997</v>
       </c>
       <c r="I21" t="n">
-        <v>288.87</v>
+        <v>407.82</v>
       </c>
       <c r="J21" t="n">
-        <v>-7695289</v>
+        <v>-7497146</v>
       </c>
       <c r="K21" t="n">
-        <v>-7695289</v>
+        <v>-7497143</v>
       </c>
       <c r="L21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-7695289</v>
+        <v>-7497143</v>
       </c>
       <c r="N21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2566,31 +2566,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-1038861</v>
+        <v>-1796051</v>
       </c>
       <c r="F22" t="n">
-        <v>-1038861</v>
+        <v>-1796051</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H22" t="n">
-        <v>6172646</v>
+        <v>4715312</v>
       </c>
       <c r="I22" t="n">
-        <v>694.17</v>
+        <v>362.54</v>
       </c>
       <c r="J22" t="n">
-        <v>-22149059</v>
+        <v>-24082355</v>
       </c>
       <c r="K22" t="n">
-        <v>-22149057</v>
+        <v>-24082353</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-22149057</v>
+        <v>-24082353</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2618,31 +2618,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6144663</v>
+        <v>3879646</v>
       </c>
       <c r="F23" t="n">
-        <v>6144663</v>
+        <v>3879646</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H23" t="n">
-        <v>66863557</v>
+        <v>57380443</v>
       </c>
       <c r="I23" t="n">
-        <v>988.16</v>
+        <v>1379.01</v>
       </c>
       <c r="J23" t="n">
-        <v>-3111407</v>
+        <v>-1919071</v>
       </c>
       <c r="K23" t="n">
-        <v>-3111408</v>
+        <v>-1919072</v>
       </c>
       <c r="L23" t="n">
         <v>-0</v>
       </c>
       <c r="M23" t="n">
-        <v>-3111408</v>
+        <v>-1919072</v>
       </c>
       <c r="N23" t="n">
         <v>-0</v>
@@ -2670,34 +2670,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-21071075</v>
+        <v>-23448148</v>
       </c>
       <c r="F24" t="n">
-        <v>-21071075</v>
+        <v>-23448148</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H24" t="n">
-        <v>39647819</v>
+        <v>30052649</v>
       </c>
       <c r="I24" t="n">
-        <v>288.16</v>
+        <v>228.17</v>
       </c>
       <c r="J24" t="n">
-        <v>9457052</v>
+        <v>10387181</v>
       </c>
       <c r="K24" t="n">
-        <v>9457052</v>
+        <v>10385387</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="M24" t="n">
-        <v>9457052</v>
+        <v>10385387</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="25">
@@ -2722,31 +2722,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-55765417</v>
+        <v>-58010321</v>
       </c>
       <c r="F25" t="n">
-        <v>-55765417</v>
+        <v>-58010322</v>
       </c>
       <c r="G25" t="n">
         <v>-0</v>
       </c>
       <c r="H25" t="n">
-        <v>4953477</v>
+        <v>-4509525</v>
       </c>
       <c r="I25" t="n">
-        <v>108.88</v>
+        <v>92.23</v>
       </c>
       <c r="J25" t="n">
-        <v>23961488</v>
+        <v>26923019</v>
       </c>
       <c r="K25" t="n">
-        <v>23961486</v>
+        <v>26923013</v>
       </c>
       <c r="L25" t="n">
         <v>-0</v>
       </c>
       <c r="M25" t="n">
-        <v>23961486</v>
+        <v>26923013</v>
       </c>
       <c r="N25" t="n">
         <v>-0</v>
@@ -2774,31 +2774,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>60050067</v>
+        <v>57364290</v>
       </c>
       <c r="F26" t="n">
-        <v>60050067</v>
+        <v>57364290</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>120768961</v>
+        <v>110865087</v>
       </c>
       <c r="I26" t="n">
-        <v>101.11</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-20772481</v>
+        <v>-23761984</v>
       </c>
       <c r="K26" t="n">
-        <v>-20772482</v>
+        <v>-23761986</v>
       </c>
       <c r="L26" t="n">
         <v>-0</v>
       </c>
       <c r="M26" t="n">
-        <v>-20772482</v>
+        <v>-23761986</v>
       </c>
       <c r="N26" t="n">
         <v>-0</v>
@@ -2826,31 +2826,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-24751691</v>
+        <v>-27304620</v>
       </c>
       <c r="F27" t="n">
-        <v>-24751691</v>
+        <v>-27304620</v>
       </c>
       <c r="G27" t="n">
         <v>-0</v>
       </c>
       <c r="H27" t="n">
-        <v>35967203</v>
+        <v>26196177</v>
       </c>
       <c r="I27" t="n">
-        <v>245.31</v>
+        <v>195.94</v>
       </c>
       <c r="J27" t="n">
-        <v>12669193</v>
+        <v>12288176</v>
       </c>
       <c r="K27" t="n">
-        <v>12669195</v>
+        <v>12288177</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>12669195</v>
+        <v>12288177</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2878,34 +2878,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>28953150</v>
+        <v>26578322</v>
       </c>
       <c r="F28" t="n">
-        <v>28953150</v>
+        <v>26578322</v>
       </c>
       <c r="G28" t="n">
         <v>-0</v>
       </c>
       <c r="H28" t="n">
-        <v>89672044</v>
+        <v>80079119</v>
       </c>
       <c r="I28" t="n">
-        <v>209.71</v>
+        <v>201.29</v>
       </c>
       <c r="J28" t="n">
-        <v>-11883977</v>
+        <v>-12087800</v>
       </c>
       <c r="K28" t="n">
-        <v>-11883977</v>
+        <v>-12087802</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M28" t="n">
-        <v>-11883977</v>
+        <v>-12087802</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="29">
@@ -2930,34 +2930,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5547774</v>
+        <v>2871407</v>
       </c>
       <c r="F29" t="n">
-        <v>5547774</v>
+        <v>2871407</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H29" t="n">
-        <v>66266668</v>
+        <v>56372204</v>
       </c>
       <c r="I29" t="n">
-        <v>1094.47</v>
+        <v>1863.23</v>
       </c>
       <c r="J29" t="n">
-        <v>1374049</v>
+        <v>-530212</v>
       </c>
       <c r="K29" t="n">
-        <v>1374051</v>
+        <v>-530212</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M29" t="n">
-        <v>1374051</v>
+        <v>-530212</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="30">
@@ -2982,31 +2982,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>926007</v>
+        <v>1427855</v>
       </c>
       <c r="F30" t="n">
-        <v>926007</v>
+        <v>1427855</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>9230626</v>
+        <v>11685213</v>
       </c>
       <c r="I30" t="n">
-        <v>896.8200000000001</v>
+        <v>718.38</v>
       </c>
       <c r="J30" t="n">
-        <v>17779833</v>
+        <v>27223787</v>
       </c>
       <c r="K30" t="n">
-        <v>17779832</v>
+        <v>27223786</v>
       </c>
       <c r="L30" t="n">
         <v>-0</v>
       </c>
       <c r="M30" t="n">
-        <v>17779832</v>
+        <v>27223786</v>
       </c>
       <c r="N30" t="n">
         <v>-0</v>
@@ -3034,31 +3034,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-990448</v>
+        <v>-1481620</v>
       </c>
       <c r="F31" t="n">
-        <v>-990448</v>
+        <v>-1481620</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>7314171</v>
+        <v>8775738</v>
       </c>
       <c r="I31" t="n">
-        <v>838.47</v>
+        <v>692.3099999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>20433166</v>
+        <v>31064292</v>
       </c>
       <c r="K31" t="n">
-        <v>20433165</v>
+        <v>31064292</v>
       </c>
       <c r="L31" t="n">
         <v>-0</v>
       </c>
       <c r="M31" t="n">
-        <v>20433165</v>
+        <v>31064292</v>
       </c>
       <c r="N31" t="n">
         <v>-0</v>
@@ -3086,34 +3086,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-2363696</v>
+        <v>-3580552</v>
       </c>
       <c r="F32" t="n">
-        <v>-2363696</v>
+        <v>-3580552</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>5940923</v>
+        <v>6676806</v>
       </c>
       <c r="I32" t="n">
-        <v>351.34</v>
+        <v>286.47</v>
       </c>
       <c r="J32" t="n">
-        <v>52679712</v>
+        <v>80106383</v>
       </c>
       <c r="K32" t="n">
-        <v>52679713</v>
+        <v>80106383</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M32" t="n">
-        <v>52679713</v>
+        <v>80106383</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="33">
@@ -3138,31 +3138,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2220042</v>
+        <v>3425504</v>
       </c>
       <c r="F33" t="n">
-        <v>2220042</v>
+        <v>3425504</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>10524661</v>
+        <v>13682862</v>
       </c>
       <c r="I33" t="n">
-        <v>374.07</v>
+        <v>299.44</v>
       </c>
       <c r="J33" t="n">
-        <v>-47639412</v>
+        <v>-72388761</v>
       </c>
       <c r="K33" t="n">
-        <v>-47639414</v>
+        <v>-72388764</v>
       </c>
       <c r="L33" t="n">
         <v>-0</v>
       </c>
       <c r="M33" t="n">
-        <v>-47639414</v>
+        <v>-72388764</v>
       </c>
       <c r="N33" t="n">
         <v>-0</v>
@@ -3190,34 +3190,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-1883298</v>
+        <v>-2827786</v>
       </c>
       <c r="F34" t="n">
-        <v>-1883298</v>
+        <v>-2827786</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>6421321</v>
+        <v>7429572</v>
       </c>
       <c r="I34" t="n">
-        <v>440.96</v>
+        <v>362.73</v>
       </c>
       <c r="J34" t="n">
-        <v>4651603</v>
+        <v>6900166</v>
       </c>
       <c r="K34" t="n">
-        <v>4651602</v>
+        <v>6900167</v>
       </c>
       <c r="L34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4651602</v>
+        <v>6900167</v>
       </c>
       <c r="N34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3242,31 +3242,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1738312</v>
+        <v>2671575</v>
       </c>
       <c r="F35" t="n">
-        <v>1738312</v>
+        <v>2671575</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>10042931</v>
+        <v>12928933</v>
       </c>
       <c r="I35" t="n">
-        <v>477.74</v>
+        <v>383.94</v>
       </c>
       <c r="J35" t="n">
-        <v>-4608206</v>
+        <v>-6836046</v>
       </c>
       <c r="K35" t="n">
-        <v>-4608209</v>
+        <v>-6836047</v>
       </c>
       <c r="L35" t="n">
         <v>-0</v>
       </c>
       <c r="M35" t="n">
-        <v>-4608209</v>
+        <v>-6836047</v>
       </c>
       <c r="N35" t="n">
         <v>-0</v>
@@ -3294,34 +3294,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-711480</v>
+        <v>-1036988</v>
       </c>
       <c r="F36" t="n">
-        <v>-711480</v>
+        <v>-1036988</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>7593139</v>
+        <v>9220370</v>
       </c>
       <c r="I36" t="n">
-        <v>1167.23</v>
+        <v>989.15</v>
       </c>
       <c r="J36" t="n">
-        <v>-21605002</v>
+        <v>-33007158</v>
       </c>
       <c r="K36" t="n">
-        <v>-21605004</v>
+        <v>-33007157</v>
       </c>
       <c r="L36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-21605004</v>
+        <v>-33007157</v>
       </c>
       <c r="N36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3346,34 +3346,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-1628025</v>
+        <v>-480472</v>
       </c>
       <c r="F37" t="n">
-        <v>-1719045</v>
+        <v>-570033</v>
       </c>
       <c r="G37" t="n">
-        <v>-5.59</v>
+        <v>-18.64</v>
       </c>
       <c r="H37" t="n">
-        <v>29398589</v>
+        <v>21802350</v>
       </c>
       <c r="I37" t="n">
-        <v>1905.78</v>
+        <v>4637.69</v>
       </c>
       <c r="J37" t="n">
-        <v>-7653607</v>
+        <v>-5459093</v>
       </c>
       <c r="K37" t="n">
-        <v>-7653605</v>
+        <v>-5459093</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M37" t="n">
-        <v>-7653605</v>
+        <v>-5459093</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="38">
@@ -3398,34 +3398,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-10323105</v>
+        <v>-9761534</v>
       </c>
       <c r="F38" t="n">
-        <v>-10317702</v>
+        <v>-9762189</v>
       </c>
       <c r="G38" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="H38" t="n">
-        <v>20799932</v>
+        <v>12610194</v>
       </c>
       <c r="I38" t="n">
-        <v>301.49</v>
+        <v>229.18</v>
       </c>
       <c r="J38" t="n">
-        <v>12919082</v>
+        <v>9648193</v>
       </c>
       <c r="K38" t="n">
-        <v>12919084</v>
+        <v>9647834</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M38" t="n">
-        <v>12919084</v>
+        <v>9647834</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="39">
@@ -3450,34 +3450,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-25714165</v>
+        <v>-23843007</v>
       </c>
       <c r="F39" t="n">
-        <v>-25701399</v>
+        <v>-23843212</v>
       </c>
       <c r="G39" t="n">
-        <v>0.05</v>
+        <v>-0</v>
       </c>
       <c r="H39" t="n">
-        <v>5416235</v>
+        <v>-1470829</v>
       </c>
       <c r="I39" t="n">
-        <v>121.06</v>
+        <v>93.83</v>
       </c>
       <c r="J39" t="n">
-        <v>32650266</v>
+        <v>24559799</v>
       </c>
       <c r="K39" t="n">
-        <v>32650267</v>
+        <v>24559798</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M39" t="n">
-        <v>32650267</v>
+        <v>24559798</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="40">
@@ -3502,34 +3502,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>25663847</v>
+        <v>23163020</v>
       </c>
       <c r="F40" t="n">
-        <v>25652087</v>
+        <v>23161359</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="H40" t="n">
-        <v>56769721</v>
+        <v>45533742</v>
       </c>
       <c r="I40" t="n">
-        <v>121.21</v>
+        <v>96.58</v>
       </c>
       <c r="J40" t="n">
-        <v>-30570258</v>
+        <v>-23063001</v>
       </c>
       <c r="K40" t="n">
-        <v>-30570255</v>
+        <v>-23063001</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M40" t="n">
-        <v>-30570255</v>
+        <v>-23063001</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="41">
@@ -3554,31 +3554,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-8946674</v>
+        <v>-9681693</v>
       </c>
       <c r="F41" t="n">
-        <v>-8859782</v>
+        <v>-9603532</v>
       </c>
       <c r="G41" t="n">
-        <v>0.97</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>22257852</v>
+        <v>12768851</v>
       </c>
       <c r="I41" t="n">
-        <v>348.78</v>
+        <v>231.89</v>
       </c>
       <c r="J41" t="n">
-        <v>20046721</v>
+        <v>14666900</v>
       </c>
       <c r="K41" t="n">
-        <v>20046722</v>
+        <v>14666901</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>20046722</v>
+        <v>14666901</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -3606,34 +3606,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>8853541</v>
+        <v>8966590</v>
       </c>
       <c r="F42" t="n">
-        <v>8767460</v>
+        <v>8886285</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.97</v>
+        <v>-0.9</v>
       </c>
       <c r="H42" t="n">
-        <v>39885094</v>
+        <v>31258668</v>
       </c>
       <c r="I42" t="n">
-        <v>350.5</v>
+        <v>248.61</v>
       </c>
       <c r="J42" t="n">
-        <v>-19554195</v>
+        <v>-14471370</v>
       </c>
       <c r="K42" t="n">
-        <v>-19554191</v>
+        <v>-14471371</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M42" t="n">
-        <v>-19554191</v>
+        <v>-14471371</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="43">
@@ -3658,34 +3658,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4605718</v>
+        <v>2672956</v>
       </c>
       <c r="F43" t="n">
-        <v>4689147</v>
+        <v>2753700</v>
       </c>
       <c r="G43" t="n">
-        <v>1.81</v>
+        <v>3.02</v>
       </c>
       <c r="H43" t="n">
-        <v>35806781</v>
+        <v>25126083</v>
       </c>
       <c r="I43" t="n">
-        <v>677.4400000000001</v>
+        <v>840.01</v>
       </c>
       <c r="J43" t="n">
-        <v>3832374</v>
+        <v>2451429</v>
       </c>
       <c r="K43" t="n">
-        <v>3832375</v>
+        <v>2451428</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M43" t="n">
-        <v>3832375</v>
+        <v>2451428</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="44">
@@ -3710,30 +3710,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>121593</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
+        <v>121593</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
       <c r="H44" t="n">
-        <v>87271</v>
-      </c>
-      <c r="I44" t="inlineStr"/>
+        <v>1649760</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1256.78</v>
+      </c>
       <c r="J44" t="n">
-        <v>20456566</v>
+        <v>38066062</v>
       </c>
       <c r="K44" t="n">
-        <v>20456566</v>
+        <v>39815929</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M44" t="n">
-        <v>20456566</v>
+        <v>39815929</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="45">
@@ -3758,30 +3762,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>-165856</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
+        <v>-165856</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
       <c r="H45" t="n">
-        <v>87271</v>
-      </c>
-      <c r="I45" t="inlineStr"/>
+        <v>1362311</v>
+      </c>
+      <c r="I45" t="n">
+        <v>921.38</v>
+      </c>
       <c r="J45" t="n">
-        <v>23897384</v>
+        <v>41732637</v>
       </c>
       <c r="K45" t="n">
-        <v>23897384</v>
+        <v>43900369</v>
       </c>
       <c r="L45" t="n">
-        <v>-0</v>
+        <v>5.19</v>
       </c>
       <c r="M45" t="n">
-        <v>23897384</v>
+        <v>43900369</v>
       </c>
       <c r="N45" t="n">
-        <v>-0</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="46">
@@ -3806,30 +3814,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>-412318</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
+        <v>-412318</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-0</v>
+      </c>
       <c r="H46" t="n">
-        <v>87271</v>
-      </c>
-      <c r="I46" t="inlineStr"/>
+        <v>1115849</v>
+      </c>
+      <c r="I46" t="n">
+        <v>370.63</v>
+      </c>
       <c r="J46" t="n">
-        <v>61309111</v>
+        <v>107196047</v>
       </c>
       <c r="K46" t="n">
-        <v>61309111</v>
+        <v>112752316</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="M46" t="n">
-        <v>61309111</v>
+        <v>112752316</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="47">
@@ -3854,30 +3866,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>420124</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="inlineStr"/>
+        <v>420124</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
       <c r="H47" t="n">
-        <v>87271</v>
-      </c>
-      <c r="I47" t="inlineStr"/>
+        <v>1948291</v>
+      </c>
+      <c r="I47" t="n">
+        <v>363.74</v>
+      </c>
       <c r="J47" t="n">
-        <v>-56318431</v>
+        <v>-98062148</v>
       </c>
       <c r="K47" t="n">
-        <v>-56318431</v>
+        <v>-103181099</v>
       </c>
       <c r="L47" t="n">
-        <v>-0</v>
+        <v>-5.22</v>
       </c>
       <c r="M47" t="n">
-        <v>-56318431</v>
+        <v>-103181099</v>
       </c>
       <c r="N47" t="n">
-        <v>-0</v>
+        <v>-5.22</v>
       </c>
     </row>
     <row r="48">
@@ -3902,30 +3918,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>-273441</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
+        <v>-273441</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
       <c r="H48" t="n">
-        <v>87271</v>
-      </c>
-      <c r="I48" t="inlineStr"/>
+        <v>1254726</v>
+      </c>
+      <c r="I48" t="n">
+        <v>558.86</v>
+      </c>
       <c r="J48" t="n">
-        <v>5700492</v>
+        <v>7890942</v>
       </c>
       <c r="K48" t="n">
-        <v>5700492</v>
+        <v>8503379</v>
       </c>
       <c r="L48" t="n">
-        <v>-0</v>
+        <v>7.76</v>
       </c>
       <c r="M48" t="n">
-        <v>5700492</v>
+        <v>8503379</v>
       </c>
       <c r="N48" t="n">
-        <v>-0</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="49">
@@ -3950,30 +3970,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>276853</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
+        <v>276853</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
       <c r="H49" t="n">
-        <v>87271</v>
-      </c>
-      <c r="I49" t="inlineStr"/>
+        <v>1805020</v>
+      </c>
+      <c r="I49" t="n">
+        <v>551.98</v>
+      </c>
       <c r="J49" t="n">
-        <v>-5650283</v>
+        <v>-7824022</v>
       </c>
       <c r="K49" t="n">
-        <v>-5650283</v>
+        <v>-8430858</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>-7.76</v>
       </c>
       <c r="M49" t="n">
-        <v>-5650283</v>
+        <v>-8430858</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>-7.76</v>
       </c>
     </row>
     <row r="50">
@@ -3998,30 +4022,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>-60138</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
+        <v>-60138</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
       <c r="H50" t="n">
-        <v>87271</v>
-      </c>
-      <c r="I50" t="inlineStr"/>
+        <v>1468029</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2541.08</v>
+      </c>
       <c r="J50" t="n">
-        <v>-25261942</v>
+        <v>-46094447</v>
       </c>
       <c r="K50" t="n">
-        <v>-25261942</v>
+        <v>-48290913</v>
       </c>
       <c r="L50" t="n">
-        <v>-0</v>
+        <v>-4.77</v>
       </c>
       <c r="M50" t="n">
-        <v>-25261942</v>
+        <v>-48290913</v>
       </c>
       <c r="N50" t="n">
-        <v>-0</v>
+        <v>-4.77</v>
       </c>
     </row>
     <row r="51">
@@ -4046,34 +4074,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>159565</v>
+        <v>7450</v>
       </c>
       <c r="F51" t="n">
-        <v>177397</v>
+        <v>36255</v>
       </c>
       <c r="G51" t="n">
-        <v>11.18</v>
+        <v>386.66</v>
       </c>
       <c r="H51" t="n">
-        <v>9249901</v>
+        <v>991716</v>
       </c>
       <c r="I51" t="n">
-        <v>5696.96</v>
+        <v>13212.11</v>
       </c>
       <c r="J51" t="n">
-        <v>-8551705</v>
+        <v>-5851574</v>
       </c>
       <c r="K51" t="n">
-        <v>-8551705</v>
+        <v>-6156836</v>
       </c>
       <c r="L51" t="n">
-        <v>-0</v>
+        <v>-5.22</v>
       </c>
       <c r="M51" t="n">
-        <v>-8551705</v>
+        <v>-6156836</v>
       </c>
       <c r="N51" t="n">
-        <v>-0</v>
+        <v>-5.22</v>
       </c>
     </row>
     <row r="52">
@@ -4098,34 +4126,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-8382646</v>
+        <v>-5817299</v>
       </c>
       <c r="F52" t="n">
-        <v>-8379002</v>
+        <v>-5827879</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04</v>
+        <v>-0.18</v>
       </c>
       <c r="H52" t="n">
-        <v>693502</v>
+        <v>-4872418</v>
       </c>
       <c r="I52" t="n">
-        <v>108.27</v>
+        <v>16.24</v>
       </c>
       <c r="J52" t="n">
-        <v>6243945</v>
+        <v>3676911</v>
       </c>
       <c r="K52" t="n">
-        <v>6243945</v>
+        <v>3857129</v>
       </c>
       <c r="L52" t="n">
-        <v>-0</v>
+        <v>4.9</v>
       </c>
       <c r="M52" t="n">
-        <v>6243945</v>
+        <v>3857129</v>
       </c>
       <c r="N52" t="n">
-        <v>-0</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="53">
@@ -4150,34 +4178,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>-20880107</v>
+        <v>-14490522</v>
       </c>
       <c r="F53" t="n">
-        <v>-20870995</v>
+        <v>-14516811</v>
       </c>
       <c r="G53" t="n">
-        <v>0.04</v>
+        <v>-0.18</v>
       </c>
       <c r="H53" t="n">
-        <v>-11798491</v>
+        <v>-13561350</v>
       </c>
       <c r="I53" t="n">
-        <v>43.49</v>
+        <v>6.41</v>
       </c>
       <c r="J53" t="n">
-        <v>15391601</v>
+        <v>9199669</v>
       </c>
       <c r="K53" t="n">
-        <v>15391601</v>
+        <v>9651357</v>
       </c>
       <c r="L53" t="n">
-        <v>-0</v>
+        <v>4.91</v>
       </c>
       <c r="M53" t="n">
-        <v>15391601</v>
+        <v>9651357</v>
       </c>
       <c r="N53" t="n">
-        <v>-0</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="54">
@@ -4202,34 +4230,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>21141081</v>
+        <v>14668923</v>
       </c>
       <c r="F54" t="n">
-        <v>21131888</v>
+        <v>14695686</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.04</v>
+        <v>0.18</v>
       </c>
       <c r="H54" t="n">
-        <v>30204392</v>
+        <v>15651147</v>
       </c>
       <c r="I54" t="n">
-        <v>42.87</v>
+        <v>6.7</v>
       </c>
       <c r="J54" t="n">
-        <v>-14858227</v>
+        <v>-9078936</v>
       </c>
       <c r="K54" t="n">
-        <v>-14858227</v>
+        <v>-9526834</v>
       </c>
       <c r="L54" t="n">
-        <v>-0</v>
+        <v>-4.93</v>
       </c>
       <c r="M54" t="n">
-        <v>-14858227</v>
+        <v>-9526834</v>
       </c>
       <c r="N54" t="n">
-        <v>-0</v>
+        <v>-4.93</v>
       </c>
     </row>
     <row r="55">
@@ -4254,34 +4282,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>-8537527</v>
+        <v>-5838721</v>
       </c>
       <c r="F55" t="n">
-        <v>-8549946</v>
+        <v>-5875013</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.15</v>
+        <v>-0.62</v>
       </c>
       <c r="H55" t="n">
-        <v>522558</v>
+        <v>-4919552</v>
       </c>
       <c r="I55" t="n">
-        <v>106.12</v>
+        <v>15.74</v>
       </c>
       <c r="J55" t="n">
-        <v>14122411</v>
+        <v>8963080</v>
       </c>
       <c r="K55" t="n">
-        <v>14122411</v>
+        <v>9418206</v>
       </c>
       <c r="L55" t="n">
-        <v>-0</v>
+        <v>5.08</v>
       </c>
       <c r="M55" t="n">
-        <v>14122411</v>
+        <v>9418206</v>
       </c>
       <c r="N55" t="n">
-        <v>-0</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="56">
@@ -4306,34 +4334,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>8592938</v>
+        <v>5870155</v>
       </c>
       <c r="F56" t="n">
-        <v>8605277</v>
+        <v>5906698</v>
       </c>
       <c r="G56" t="n">
-        <v>0.14</v>
+        <v>0.62</v>
       </c>
       <c r="H56" t="n">
-        <v>17677781</v>
+        <v>6862159</v>
       </c>
       <c r="I56" t="n">
-        <v>105.72</v>
+        <v>16.9</v>
       </c>
       <c r="J56" t="n">
-        <v>-13635747</v>
+        <v>-8862275</v>
       </c>
       <c r="K56" t="n">
-        <v>-13635747</v>
+        <v>-9313903</v>
       </c>
       <c r="L56" t="n">
-        <v>-0</v>
+        <v>-5.1</v>
       </c>
       <c r="M56" t="n">
-        <v>-13635747</v>
+        <v>-9313903</v>
       </c>
       <c r="N56" t="n">
-        <v>-0</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="57">
@@ -4358,34 +4386,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2484155</v>
+        <v>1813524</v>
       </c>
       <c r="F57" t="n">
-        <v>2466212</v>
+        <v>1789997</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.72</v>
+        <v>-1.3</v>
       </c>
       <c r="H57" t="n">
-        <v>11538716</v>
+        <v>2745458</v>
       </c>
       <c r="I57" t="n">
-        <v>364.49</v>
+        <v>51.39</v>
       </c>
       <c r="J57" t="n">
-        <v>6402358</v>
+        <v>4319808</v>
       </c>
       <c r="K57" t="n">
-        <v>6402358</v>
+        <v>4546894</v>
       </c>
       <c r="L57" t="n">
-        <v>-0</v>
+        <v>5.26</v>
       </c>
       <c r="M57" t="n">
-        <v>6402358</v>
+        <v>4546894</v>
       </c>
       <c r="N57" t="n">
-        <v>-0</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="58">
@@ -4410,31 +4438,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>9420915</v>
+        <v>4921446</v>
       </c>
       <c r="F58" t="n">
-        <v>9420915</v>
+        <v>4921446</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>6527477</v>
+        <v>3458573</v>
       </c>
       <c r="I58" t="n">
-        <v>-30.71</v>
+        <v>-29.72</v>
       </c>
       <c r="J58" t="n">
-        <v>-356970</v>
+        <v>-123901</v>
       </c>
       <c r="K58" t="n">
-        <v>-356970</v>
+        <v>-123901</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-356970</v>
+        <v>-123901</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
@@ -4462,31 +4490,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>-4137695</v>
+        <v>-1937096</v>
       </c>
       <c r="F59" t="n">
-        <v>-4137695</v>
+        <v>-1937096</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H59" t="n">
-        <v>-7031133</v>
+        <v>-3399969</v>
       </c>
       <c r="I59" t="n">
-        <v>-69.93000000000001</v>
+        <v>-75.52</v>
       </c>
       <c r="J59" t="n">
-        <v>142487</v>
+        <v>49268</v>
       </c>
       <c r="K59" t="n">
-        <v>142487</v>
+        <v>49268</v>
       </c>
       <c r="L59" t="n">
         <v>-0</v>
       </c>
       <c r="M59" t="n">
-        <v>142487</v>
+        <v>49268</v>
       </c>
       <c r="N59" t="n">
         <v>-0</v>
@@ -4514,31 +4542,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>-9928353</v>
+        <v>-4862462</v>
       </c>
       <c r="F60" t="n">
-        <v>-9928353</v>
+        <v>-4862462</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-12821791</v>
+        <v>-6325334</v>
       </c>
       <c r="I60" t="n">
-        <v>-29.14</v>
+        <v>-30.09</v>
       </c>
       <c r="J60" t="n">
-        <v>356178</v>
+        <v>123220</v>
       </c>
       <c r="K60" t="n">
-        <v>356178</v>
+        <v>123220</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>356178</v>
+        <v>123220</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -4566,34 +4594,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>9385852</v>
+        <v>4893104</v>
       </c>
       <c r="F61" t="n">
-        <v>9385852</v>
+        <v>4893104</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>6492414</v>
+        <v>3430231</v>
       </c>
       <c r="I61" t="n">
-        <v>-30.83</v>
+        <v>-29.9</v>
       </c>
       <c r="J61" t="n">
-        <v>-355680</v>
+        <v>-123186</v>
       </c>
       <c r="K61" t="n">
-        <v>-355680</v>
+        <v>-123186</v>
       </c>
       <c r="L61" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-355680</v>
+        <v>-123186</v>
       </c>
       <c r="N61" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -4618,34 +4646,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>-12786163</v>
+        <v>-6306809</v>
       </c>
       <c r="F62" t="n">
-        <v>-12786163</v>
+        <v>-6306809</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-15679601</v>
+        <v>-7769682</v>
       </c>
       <c r="I62" t="n">
-        <v>-22.63</v>
+        <v>-23.2</v>
       </c>
       <c r="J62" t="n">
-        <v>461723</v>
+        <v>159753</v>
       </c>
       <c r="K62" t="n">
-        <v>461723</v>
+        <v>159753</v>
       </c>
       <c r="L62" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>461723</v>
+        <v>159753</v>
       </c>
       <c r="N62" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4670,31 +4698,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>12249532</v>
+        <v>6348583</v>
       </c>
       <c r="F63" t="n">
-        <v>12249532</v>
+        <v>6348583</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>9356094</v>
+        <v>4885710</v>
       </c>
       <c r="I63" t="n">
-        <v>-23.62</v>
+        <v>-23.04</v>
       </c>
       <c r="J63" t="n">
-        <v>-461011</v>
+        <v>-159896</v>
       </c>
       <c r="K63" t="n">
-        <v>-461011</v>
+        <v>-159896</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-461011</v>
+        <v>-159896</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -4722,34 +4750,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>-8022838</v>
+        <v>-3909617</v>
       </c>
       <c r="F64" t="n">
-        <v>-8022838</v>
+        <v>-3909617</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-10916276</v>
+        <v>-5372490</v>
       </c>
       <c r="I64" t="n">
-        <v>-36.07</v>
+        <v>-37.42</v>
       </c>
       <c r="J64" t="n">
-        <v>285834</v>
+        <v>99127</v>
       </c>
       <c r="K64" t="n">
-        <v>285834</v>
+        <v>99127</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M64" t="n">
-        <v>285834</v>
+        <v>99127</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="65">
@@ -5082,31 +5110,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1389715</v>
+        <v>1029233</v>
       </c>
       <c r="F72" t="n">
-        <v>1368173</v>
+        <v>1022051</v>
       </c>
       <c r="G72" t="n">
-        <v>-1.55</v>
+        <v>-0.7</v>
       </c>
       <c r="H72" t="n">
-        <v>15657277</v>
+        <v>11488224</v>
       </c>
       <c r="I72" t="n">
-        <v>1026.65</v>
+        <v>1016.19</v>
       </c>
       <c r="J72" t="n">
-        <v>1359511</v>
+        <v>1409442</v>
       </c>
       <c r="K72" t="n">
-        <v>1359510</v>
+        <v>1409441</v>
       </c>
       <c r="L72" t="n">
         <v>-0</v>
       </c>
       <c r="M72" t="n">
-        <v>1359510</v>
+        <v>1409441</v>
       </c>
       <c r="N72" t="n">
         <v>-0</v>
@@ -5134,31 +5162,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>-3664753</v>
+        <v>-4119060</v>
       </c>
       <c r="F73" t="n">
-        <v>-3580481</v>
+        <v>-4011869</v>
       </c>
       <c r="G73" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="H73" t="n">
-        <v>10708623</v>
+        <v>6454304</v>
       </c>
       <c r="I73" t="n">
-        <v>392.21</v>
+        <v>256.69</v>
       </c>
       <c r="J73" t="n">
-        <v>3982246</v>
+        <v>3914832</v>
       </c>
       <c r="K73" t="n">
-        <v>3982246</v>
+        <v>3914669</v>
       </c>
       <c r="L73" t="n">
         <v>-0</v>
       </c>
       <c r="M73" t="n">
-        <v>3982246</v>
+        <v>3914669</v>
       </c>
       <c r="N73" t="n">
         <v>-0</v>
@@ -5186,31 +5214,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>-9717891</v>
+        <v>-10196588</v>
       </c>
       <c r="F74" t="n">
-        <v>-9468608</v>
+        <v>-9935313</v>
       </c>
       <c r="G74" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="H74" t="n">
-        <v>4820496</v>
+        <v>530860</v>
       </c>
       <c r="I74" t="n">
-        <v>149.6</v>
+        <v>105.21</v>
       </c>
       <c r="J74" t="n">
-        <v>10104696</v>
+        <v>10026157</v>
       </c>
       <c r="K74" t="n">
-        <v>10104695</v>
+        <v>10026157</v>
       </c>
       <c r="L74" t="n">
         <v>-0</v>
       </c>
       <c r="M74" t="n">
-        <v>10104695</v>
+        <v>10026157</v>
       </c>
       <c r="N74" t="n">
         <v>-0</v>
@@ -5238,31 +5266,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>10488225</v>
+        <v>10091019</v>
       </c>
       <c r="F75" t="n">
-        <v>10189110</v>
+        <v>9840957</v>
       </c>
       <c r="G75" t="n">
-        <v>-2.85</v>
+        <v>-2.48</v>
       </c>
       <c r="H75" t="n">
-        <v>24478214</v>
+        <v>20307130</v>
       </c>
       <c r="I75" t="n">
-        <v>133.39</v>
+        <v>101.24</v>
       </c>
       <c r="J75" t="n">
-        <v>-9211359</v>
+        <v>-9226156</v>
       </c>
       <c r="K75" t="n">
-        <v>-9211360</v>
+        <v>-9226156</v>
       </c>
       <c r="L75" t="n">
         <v>-0</v>
       </c>
       <c r="M75" t="n">
-        <v>-9211360</v>
+        <v>-9226156</v>
       </c>
       <c r="N75" t="n">
         <v>-0</v>
@@ -5290,31 +5318,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>-4579591</v>
+        <v>-5101862</v>
       </c>
       <c r="F76" t="n">
-        <v>-4498284</v>
+        <v>-4983534</v>
       </c>
       <c r="G76" t="n">
-        <v>1.78</v>
+        <v>2.32</v>
       </c>
       <c r="H76" t="n">
-        <v>9790820</v>
+        <v>5482639</v>
       </c>
       <c r="I76" t="n">
-        <v>313.79</v>
+        <v>207.46</v>
       </c>
       <c r="J76" t="n">
-        <v>2849086</v>
+        <v>2689258</v>
       </c>
       <c r="K76" t="n">
-        <v>2849085</v>
+        <v>2689258</v>
       </c>
       <c r="L76" t="n">
         <v>-0</v>
       </c>
       <c r="M76" t="n">
-        <v>2849085</v>
+        <v>2689258</v>
       </c>
       <c r="N76" t="n">
         <v>-0</v>
@@ -5342,31 +5370,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5336067</v>
+        <v>4983624</v>
       </c>
       <c r="F77" t="n">
-        <v>5204276</v>
+        <v>4875375</v>
       </c>
       <c r="G77" t="n">
-        <v>-2.47</v>
+        <v>-2.17</v>
       </c>
       <c r="H77" t="n">
-        <v>19493380</v>
+        <v>15341548</v>
       </c>
       <c r="I77" t="n">
-        <v>265.31</v>
+        <v>207.84</v>
       </c>
       <c r="J77" t="n">
-        <v>-2699686</v>
+        <v>-2649708</v>
       </c>
       <c r="K77" t="n">
-        <v>-2699687</v>
+        <v>-2649708</v>
       </c>
       <c r="L77" t="n">
         <v>-0</v>
       </c>
       <c r="M77" t="n">
-        <v>-2699687</v>
+        <v>-2649708</v>
       </c>
       <c r="N77" t="n">
         <v>-0</v>
@@ -5394,31 +5422,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>696743</v>
+        <v>192490</v>
       </c>
       <c r="F78" t="n">
-        <v>633546</v>
+        <v>176612</v>
       </c>
       <c r="G78" t="n">
-        <v>-9.07</v>
+        <v>-8.25</v>
       </c>
       <c r="H78" t="n">
-        <v>14922650</v>
+        <v>10642785</v>
       </c>
       <c r="I78" t="n">
-        <v>2041.77</v>
+        <v>5429.02</v>
       </c>
       <c r="J78" t="n">
-        <v>-2178780</v>
+        <v>-2322410</v>
       </c>
       <c r="K78" t="n">
-        <v>-2178781</v>
+        <v>-2322410</v>
       </c>
       <c r="L78" t="n">
         <v>-0</v>
       </c>
       <c r="M78" t="n">
-        <v>-2178781</v>
+        <v>-2322410</v>
       </c>
       <c r="N78" t="n">
         <v>-0</v>
@@ -5446,31 +5474,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>411359</v>
+        <v>479101</v>
       </c>
       <c r="F79" t="n">
-        <v>411359</v>
+        <v>479101</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-4903781</v>
+        <v>-865085</v>
       </c>
       <c r="I79" t="n">
-        <v>-1292.09</v>
+        <v>-280.56</v>
       </c>
       <c r="J79" t="n">
-        <v>6952797</v>
+        <v>6667523</v>
       </c>
       <c r="K79" t="n">
-        <v>6952797</v>
+        <v>6667523</v>
       </c>
       <c r="L79" t="n">
         <v>-0</v>
       </c>
       <c r="M79" t="n">
-        <v>6952797</v>
+        <v>6667523</v>
       </c>
       <c r="N79" t="n">
         <v>-0</v>
@@ -5498,34 +5526,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4284730</v>
+        <v>5664618</v>
       </c>
       <c r="F80" t="n">
-        <v>4284730</v>
+        <v>5664618</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-1030410</v>
+        <v>4320432</v>
       </c>
       <c r="I80" t="n">
-        <v>-124.05</v>
+        <v>-23.73</v>
       </c>
       <c r="J80" t="n">
-        <v>-5335174</v>
+        <v>-4720020</v>
       </c>
       <c r="K80" t="n">
-        <v>-5335174</v>
+        <v>-4720021</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M80" t="n">
-        <v>-5335174</v>
+        <v>-4720021</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="81">
@@ -5550,31 +5578,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>10672486</v>
+        <v>14109429</v>
       </c>
       <c r="F81" t="n">
-        <v>10672486</v>
+        <v>14109429</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>5357346</v>
+        <v>12765243</v>
       </c>
       <c r="I81" t="n">
-        <v>-49.8</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="J81" t="n">
-        <v>-13310384</v>
+        <v>-11820692</v>
       </c>
       <c r="K81" t="n">
-        <v>-13310384</v>
+        <v>-11820692</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-13310384</v>
+        <v>-11820692</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
@@ -5602,31 +5630,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>-10808138</v>
+        <v>-14282337</v>
       </c>
       <c r="F82" t="n">
-        <v>-10808138</v>
+        <v>-14282337</v>
       </c>
       <c r="G82" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-16123278</v>
+        <v>-15626523</v>
       </c>
       <c r="I82" t="n">
-        <v>-49.18</v>
+        <v>-9.41</v>
       </c>
       <c r="J82" t="n">
-        <v>13042366</v>
+        <v>11653823</v>
       </c>
       <c r="K82" t="n">
-        <v>13042366</v>
+        <v>11653823</v>
       </c>
       <c r="L82" t="n">
         <v>-0</v>
       </c>
       <c r="M82" t="n">
-        <v>13042366</v>
+        <v>11653823</v>
       </c>
       <c r="N82" t="n">
         <v>-0</v>
@@ -5654,31 +5682,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3925257</v>
+        <v>5250634</v>
       </c>
       <c r="F83" t="n">
-        <v>3925257</v>
+        <v>5250634</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>-1389883</v>
+        <v>3906448</v>
       </c>
       <c r="I83" t="n">
-        <v>-135.41</v>
+        <v>-25.6</v>
       </c>
       <c r="J83" t="n">
-        <v>-11662031</v>
+        <v>-10750191</v>
       </c>
       <c r="K83" t="n">
-        <v>-11662031</v>
+        <v>-10750191</v>
       </c>
       <c r="L83" t="n">
         <v>-0</v>
       </c>
       <c r="M83" t="n">
-        <v>-11662031</v>
+        <v>-10750191</v>
       </c>
       <c r="N83" t="n">
         <v>-0</v>
@@ -5706,34 +5734,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>-3951431</v>
+        <v>-5279611</v>
       </c>
       <c r="F84" t="n">
-        <v>-3951431</v>
+        <v>-5279611</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>-9266571</v>
+        <v>-6623797</v>
       </c>
       <c r="I84" t="n">
-        <v>-134.51</v>
+        <v>-25.46</v>
       </c>
       <c r="J84" t="n">
-        <v>11444387</v>
+        <v>10622577</v>
       </c>
       <c r="K84" t="n">
-        <v>11444387</v>
+        <v>10622577</v>
       </c>
       <c r="L84" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>11444387</v>
+        <v>10622577</v>
       </c>
       <c r="N84" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5758,34 +5786,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>-1726762</v>
+        <v>-2218536</v>
       </c>
       <c r="F85" t="n">
-        <v>-1726762</v>
+        <v>-2218536</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>-7041902</v>
+        <v>-3562722</v>
       </c>
       <c r="I85" t="n">
-        <v>-307.81</v>
+        <v>-60.59</v>
       </c>
       <c r="J85" t="n">
-        <v>-4914269</v>
+        <v>-4755791</v>
       </c>
       <c r="K85" t="n">
-        <v>-4914269</v>
+        <v>-4755791</v>
       </c>
       <c r="L85" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>-4914269</v>
+        <v>-4755791</v>
       </c>
       <c r="N85" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -6745,16 +6773,16 @@
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="n">
-        <v>-59621281</v>
+        <v>-63357815</v>
       </c>
       <c r="K107" t="n">
-        <v>-59621281</v>
+        <v>-63357815</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>-59621281</v>
+        <v>-63357815</v>
       </c>
       <c r="N107" t="n">
         <v>0</v>
@@ -6793,19 +6821,19 @@
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="n">
-        <v>-66957822</v>
+        <v>-70534127</v>
       </c>
       <c r="K108" t="n">
-        <v>-66957822</v>
+        <v>-70534127</v>
       </c>
       <c r="L108" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>-66957822</v>
+        <v>-70534127</v>
       </c>
       <c r="N108" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -6841,16 +6869,16 @@
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="n">
-        <v>-172655395</v>
+        <v>-181921970</v>
       </c>
       <c r="K109" t="n">
-        <v>-172655395</v>
+        <v>-181921970</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>-172655395</v>
+        <v>-181921970</v>
       </c>
       <c r="N109" t="n">
         <v>0</v>
@@ -6889,16 +6917,16 @@
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="n">
-        <v>156027140</v>
+        <v>164270778</v>
       </c>
       <c r="K110" t="n">
-        <v>156027140</v>
+        <v>164270778</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>156027140</v>
+        <v>164270778</v>
       </c>
       <c r="N110" t="n">
         <v>0</v>
@@ -6937,19 +6965,19 @@
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="n">
-        <v>-14037282</v>
+        <v>-14295464</v>
       </c>
       <c r="K111" t="n">
-        <v>-14037282</v>
+        <v>-14295464</v>
       </c>
       <c r="L111" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>-14037282</v>
+        <v>-14295464</v>
       </c>
       <c r="N111" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -6985,16 +7013,16 @@
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="n">
-        <v>13913112</v>
+        <v>14170671</v>
       </c>
       <c r="K112" t="n">
-        <v>13913112</v>
+        <v>14170671</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>13913112</v>
+        <v>14170671</v>
       </c>
       <c r="N112" t="n">
         <v>0</v>
@@ -7033,16 +7061,16 @@
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
-        <v>71987818</v>
+        <v>76300973</v>
       </c>
       <c r="K113" t="n">
-        <v>71987818</v>
+        <v>76300973</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>71987818</v>
+        <v>76300973</v>
       </c>
       <c r="N113" t="n">
         <v>0</v>
@@ -7070,31 +7098,31 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="F114" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="G114" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="I114" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>175740</v>
+        <v>68115</v>
       </c>
       <c r="K114" t="n">
-        <v>175740</v>
+        <v>68115</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>175740</v>
+        <v>68115</v>
       </c>
       <c r="N114" t="n">
         <v>0</v>
@@ -7122,31 +7150,31 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="F115" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="G115" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="I115" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>93008</v>
+        <v>26623</v>
       </c>
       <c r="K115" t="n">
-        <v>93008</v>
+        <v>26623</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>93008</v>
+        <v>26623</v>
       </c>
       <c r="N115" t="n">
         <v>0</v>
@@ -7174,31 +7202,31 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="F116" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="G116" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="I116" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>60160</v>
+        <v>10199</v>
       </c>
       <c r="K116" t="n">
-        <v>60160</v>
+        <v>10199</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>60160</v>
+        <v>10199</v>
       </c>
       <c r="N116" t="n">
         <v>0</v>
@@ -7226,31 +7254,31 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="F117" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="G117" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="I117" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>169640</v>
+        <v>64951</v>
       </c>
       <c r="K117" t="n">
-        <v>169640</v>
+        <v>64951</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>169640</v>
+        <v>64951</v>
       </c>
       <c r="N117" t="n">
         <v>0</v>
@@ -7278,34 +7306,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="F118" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>37591</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>-13</v>
+      </c>
+      <c r="K118" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L118" t="n">
         <v>-0</v>
       </c>
-      <c r="H118" t="n">
-        <v>115085</v>
-      </c>
-      <c r="I118" t="n">
+      <c r="M118" t="n">
+        <v>-13</v>
+      </c>
+      <c r="N118" t="n">
         <v>-0</v>
-      </c>
-      <c r="J118" t="n">
-        <v>38676</v>
-      </c>
-      <c r="K118" t="n">
-        <v>38676</v>
-      </c>
-      <c r="L118" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" t="n">
-        <v>38676</v>
-      </c>
-      <c r="N118" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -7330,31 +7358,31 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="F119" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="G119" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="I119" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>191116</v>
+        <v>75795</v>
       </c>
       <c r="K119" t="n">
-        <v>191116</v>
+        <v>75795</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>191116</v>
+        <v>75795</v>
       </c>
       <c r="N119" t="n">
         <v>0</v>
@@ -7382,34 +7410,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="F120" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="G120" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>115085</v>
+        <v>37591</v>
       </c>
       <c r="I120" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>65520</v>
+        <v>12771</v>
       </c>
       <c r="K120" t="n">
-        <v>65520</v>
+        <v>12771</v>
       </c>
       <c r="L120" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>65520</v>
+        <v>12771</v>
       </c>
       <c r="N120" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -7434,34 +7462,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>-20583468</v>
+        <v>-19790474</v>
       </c>
       <c r="F121" t="n">
-        <v>-20583468</v>
+        <v>-19790474</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H121" t="n">
-        <v>-28592231</v>
+        <v>-25019254</v>
       </c>
       <c r="I121" t="n">
-        <v>-38.91</v>
+        <v>-26.42</v>
       </c>
       <c r="J121" t="n">
-        <v>7629990</v>
+        <v>7635515</v>
       </c>
       <c r="K121" t="n">
-        <v>7629990</v>
+        <v>7694427</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="M121" t="n">
-        <v>7629990</v>
+        <v>7694427</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="122">
@@ -7486,34 +7514,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>10216101</v>
+        <v>9923133</v>
       </c>
       <c r="F122" t="n">
-        <v>10216101</v>
+        <v>9923133</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H122" t="n">
-        <v>2207338</v>
+        <v>4694353</v>
       </c>
       <c r="I122" t="n">
-        <v>-78.39</v>
+        <v>-52.69</v>
       </c>
       <c r="J122" t="n">
-        <v>-4518805</v>
+        <v>-4573893</v>
       </c>
       <c r="K122" t="n">
-        <v>-4518804</v>
+        <v>-4597662</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
       <c r="M122" t="n">
-        <v>-4518804</v>
+        <v>-4597662</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="123">
@@ -7538,34 +7566,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>25497392</v>
+        <v>24765078</v>
       </c>
       <c r="F123" t="n">
-        <v>25497392</v>
+        <v>24765078</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>17488629</v>
+        <v>19536298</v>
       </c>
       <c r="I123" t="n">
-        <v>-31.41</v>
+        <v>-21.11</v>
       </c>
       <c r="J123" t="n">
-        <v>-11325156</v>
+        <v>-11463995</v>
       </c>
       <c r="K123" t="n">
-        <v>-11325156</v>
+        <v>-11523456</v>
       </c>
       <c r="L123" t="n">
-        <v>-0</v>
+        <v>-0.52</v>
       </c>
       <c r="M123" t="n">
-        <v>-11325156</v>
+        <v>-11523456</v>
       </c>
       <c r="N123" t="n">
-        <v>-0</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="124">
@@ -7590,34 +7618,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>-25641342</v>
+        <v>-24908362</v>
       </c>
       <c r="F124" t="n">
-        <v>-25641342</v>
+        <v>-24908362</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>-33650105</v>
+        <v>-30137142</v>
       </c>
       <c r="I124" t="n">
-        <v>-31.23</v>
+        <v>-20.99</v>
       </c>
       <c r="J124" t="n">
-        <v>11230917</v>
+        <v>11367007</v>
       </c>
       <c r="K124" t="n">
-        <v>11230917</v>
+        <v>11426344</v>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="M124" t="n">
-        <v>11230917</v>
+        <v>11426344</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="125">
@@ -7642,34 +7670,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>28505378</v>
+        <v>27493587</v>
       </c>
       <c r="F125" t="n">
-        <v>28505378</v>
+        <v>27493587</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>20496615</v>
+        <v>22264807</v>
       </c>
       <c r="I125" t="n">
-        <v>-28.1</v>
+        <v>-19.02</v>
       </c>
       <c r="J125" t="n">
-        <v>-11390908</v>
+        <v>-11451659</v>
       </c>
       <c r="K125" t="n">
-        <v>-11390908</v>
+        <v>-11528184</v>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>-0.67</v>
       </c>
       <c r="M125" t="n">
-        <v>-11390908</v>
+        <v>-11528184</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="126">
@@ -7694,34 +7722,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>-28659209</v>
+        <v>-27657568</v>
       </c>
       <c r="F126" t="n">
-        <v>-28659209</v>
+        <v>-27657568</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>-36667972</v>
+        <v>-32886348</v>
       </c>
       <c r="I126" t="n">
-        <v>-27.94</v>
+        <v>-18.91</v>
       </c>
       <c r="J126" t="n">
-        <v>11302491</v>
+        <v>11361895</v>
       </c>
       <c r="K126" t="n">
-        <v>11302491</v>
+        <v>11438215</v>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="M126" t="n">
-        <v>11302491</v>
+        <v>11438215</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="127">
@@ -7746,34 +7774,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>15774621</v>
+        <v>15134922</v>
       </c>
       <c r="F127" t="n">
-        <v>15774621</v>
+        <v>15134922</v>
       </c>
       <c r="G127" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>7765858</v>
+        <v>9906142</v>
       </c>
       <c r="I127" t="n">
-        <v>-50.77</v>
+        <v>-34.55</v>
       </c>
       <c r="J127" t="n">
-        <v>-5672213</v>
+        <v>-5660259</v>
       </c>
       <c r="K127" t="n">
-        <v>-5672213</v>
+        <v>-5707374</v>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="M127" t="n">
-        <v>-5672213</v>
+        <v>-5707374</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="128">
@@ -7798,31 +7826,31 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4725478</v>
+        <v>5302097</v>
       </c>
       <c r="F128" t="n">
-        <v>4725478</v>
+        <v>5302097</v>
       </c>
       <c r="G128" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>10011004</v>
+        <v>8330540</v>
       </c>
       <c r="I128" t="n">
-        <v>111.85</v>
+        <v>57.12</v>
       </c>
       <c r="J128" t="n">
-        <v>-272641</v>
+        <v>-47787</v>
       </c>
       <c r="K128" t="n">
-        <v>-272641</v>
+        <v>-47787</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>-272641</v>
+        <v>-47787</v>
       </c>
       <c r="N128" t="n">
         <v>0</v>
@@ -7850,34 +7878,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>-1894747</v>
+        <v>-1980954</v>
       </c>
       <c r="F129" t="n">
-        <v>-1894747</v>
+        <v>-1980954</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>3390779</v>
+        <v>1047489</v>
       </c>
       <c r="I129" t="n">
-        <v>278.96</v>
+        <v>152.88</v>
       </c>
       <c r="J129" t="n">
-        <v>109622</v>
+        <v>18550</v>
       </c>
       <c r="K129" t="n">
-        <v>109622</v>
+        <v>18550</v>
       </c>
       <c r="L129" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>109622</v>
+        <v>18550</v>
       </c>
       <c r="N129" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -7902,31 +7930,31 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>-4734667</v>
+        <v>-4951167</v>
       </c>
       <c r="F130" t="n">
-        <v>-4734667</v>
+        <v>-4951167</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>550859</v>
+        <v>-1922724</v>
       </c>
       <c r="I130" t="n">
-        <v>111.63</v>
+        <v>61.17</v>
       </c>
       <c r="J130" t="n">
-        <v>274053</v>
+        <v>46427</v>
       </c>
       <c r="K130" t="n">
-        <v>274053</v>
+        <v>46427</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>274053</v>
+        <v>46427</v>
       </c>
       <c r="N130" t="n">
         <v>0</v>
@@ -7954,31 +7982,31 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4740819</v>
+        <v>4952043</v>
       </c>
       <c r="F131" t="n">
-        <v>4740819</v>
+        <v>4952043</v>
       </c>
       <c r="G131" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>10026345</v>
+        <v>7980486</v>
       </c>
       <c r="I131" t="n">
-        <v>111.49</v>
+        <v>61.16</v>
       </c>
       <c r="J131" t="n">
-        <v>-273525</v>
+        <v>-46465</v>
       </c>
       <c r="K131" t="n">
-        <v>-273525</v>
+        <v>-46465</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>-273525</v>
+        <v>-46465</v>
       </c>
       <c r="N131" t="n">
         <v>0</v>
@@ -8006,34 +8034,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>-6106983</v>
+        <v>-6642409</v>
       </c>
       <c r="F132" t="n">
-        <v>-6106983</v>
+        <v>-6642409</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H132" t="n">
-        <v>-821457</v>
+        <v>-3613966</v>
       </c>
       <c r="I132" t="n">
-        <v>86.55</v>
+        <v>45.59</v>
       </c>
       <c r="J132" t="n">
-        <v>353607</v>
+        <v>60935</v>
       </c>
       <c r="K132" t="n">
-        <v>353607</v>
+        <v>60935</v>
       </c>
       <c r="L132" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>353607</v>
+        <v>60935</v>
       </c>
       <c r="N132" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -8058,31 +8086,31 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6117463</v>
+        <v>6715630</v>
       </c>
       <c r="F133" t="n">
-        <v>6117463</v>
+        <v>6715630</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>11402989</v>
+        <v>9744073</v>
       </c>
       <c r="I133" t="n">
-        <v>86.40000000000001</v>
+        <v>45.1</v>
       </c>
       <c r="J133" t="n">
-        <v>-352831</v>
+        <v>-61245</v>
       </c>
       <c r="K133" t="n">
-        <v>-352831</v>
+        <v>-61245</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>-352831</v>
+        <v>-61245</v>
       </c>
       <c r="N133" t="n">
         <v>0</v>
@@ -8110,34 +8138,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>-3770245</v>
+        <v>-4280610</v>
       </c>
       <c r="F134" t="n">
-        <v>-3770245</v>
+        <v>-4280610</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>1515281</v>
+        <v>-1252167</v>
       </c>
       <c r="I134" t="n">
-        <v>140.19</v>
+        <v>70.75</v>
       </c>
       <c r="J134" t="n">
-        <v>218183</v>
+        <v>38319</v>
       </c>
       <c r="K134" t="n">
-        <v>218183</v>
+        <v>38319</v>
       </c>
       <c r="L134" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>218183</v>
+        <v>38319</v>
       </c>
       <c r="N134" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -8162,31 +8190,31 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>-9485152</v>
+        <v>-9923964</v>
       </c>
       <c r="F135" t="n">
-        <v>-9485152</v>
+        <v>-9923964</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>-20023131</v>
+        <v>-16570654</v>
       </c>
       <c r="I135" t="n">
-        <v>-111.1</v>
+        <v>-66.98</v>
       </c>
       <c r="J135" t="n">
-        <v>527204</v>
+        <v>275711</v>
       </c>
       <c r="K135" t="n">
-        <v>527204</v>
+        <v>275711</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>527204</v>
+        <v>275711</v>
       </c>
       <c r="N135" t="n">
         <v>0</v>
@@ -8214,31 +8242,31 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3796194</v>
+        <v>3891151</v>
       </c>
       <c r="F136" t="n">
-        <v>3796194</v>
+        <v>3891151</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>-6741785</v>
+        <v>-2755539</v>
       </c>
       <c r="I136" t="n">
-        <v>-277.59</v>
+        <v>-170.82</v>
       </c>
       <c r="J136" t="n">
-        <v>-211836</v>
+        <v>-109780</v>
       </c>
       <c r="K136" t="n">
-        <v>-211836</v>
+        <v>-109780</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>-211836</v>
+        <v>-109780</v>
       </c>
       <c r="N136" t="n">
         <v>0</v>
@@ -8266,31 +8294,31 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>9486669</v>
+        <v>9725187</v>
       </c>
       <c r="F137" t="n">
-        <v>9486669</v>
+        <v>9725187</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>-1051310</v>
+        <v>3078497</v>
       </c>
       <c r="I137" t="n">
-        <v>-111.08</v>
+        <v>-68.34999999999999</v>
       </c>
       <c r="J137" t="n">
-        <v>-529655</v>
+        <v>-274610</v>
       </c>
       <c r="K137" t="n">
-        <v>-529655</v>
+        <v>-274610</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>-529655</v>
+        <v>-274610</v>
       </c>
       <c r="N137" t="n">
         <v>0</v>
@@ -8318,31 +8346,31 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>-9499085</v>
+        <v>-9731494</v>
       </c>
       <c r="F138" t="n">
-        <v>-9499085</v>
+        <v>-9731494</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>-20037064</v>
+        <v>-16378184</v>
       </c>
       <c r="I138" t="n">
-        <v>-110.94</v>
+        <v>-68.3</v>
       </c>
       <c r="J138" t="n">
-        <v>528678</v>
+        <v>274503</v>
       </c>
       <c r="K138" t="n">
-        <v>528678</v>
+        <v>274503</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>528678</v>
+        <v>274503</v>
       </c>
       <c r="N138" t="n">
         <v>0</v>
@@ -8370,31 +8398,31 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>12251480</v>
+        <v>12700572</v>
       </c>
       <c r="F139" t="n">
-        <v>12251480</v>
+        <v>12700572</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>1713501</v>
+        <v>6053882</v>
       </c>
       <c r="I139" t="n">
-        <v>-86.01000000000001</v>
+        <v>-52.33</v>
       </c>
       <c r="J139" t="n">
-        <v>-683634</v>
+        <v>-355774</v>
       </c>
       <c r="K139" t="n">
-        <v>-683634</v>
+        <v>-355774</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>-683634</v>
+        <v>-355774</v>
       </c>
       <c r="N139" t="n">
         <v>0</v>
@@ -8422,34 +8450,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>-12272248</v>
+        <v>-12755861</v>
       </c>
       <c r="F140" t="n">
-        <v>-12272248</v>
+        <v>-12755861</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>-22810227</v>
+        <v>-19402551</v>
       </c>
       <c r="I140" t="n">
-        <v>-85.87</v>
+        <v>-52.11</v>
       </c>
       <c r="J140" t="n">
-        <v>682154</v>
+        <v>355946</v>
       </c>
       <c r="K140" t="n">
-        <v>682154</v>
+        <v>355946</v>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M140" t="n">
-        <v>682154</v>
+        <v>355946</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="141">
@@ -8474,31 +8502,31 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>7569703</v>
+        <v>7950642</v>
       </c>
       <c r="F141" t="n">
-        <v>7569703</v>
+        <v>7950642</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H141" t="n">
-        <v>-2968276</v>
+        <v>1303952</v>
       </c>
       <c r="I141" t="n">
-        <v>-139.21</v>
+        <v>-83.59999999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>-421882</v>
+        <v>-220548</v>
       </c>
       <c r="K141" t="n">
-        <v>-421882</v>
+        <v>-220548</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>-421882</v>
+        <v>-220548</v>
       </c>
       <c r="N141" t="n">
         <v>0</v>
@@ -8526,31 +8554,31 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>-9116752</v>
+        <v>-9183766</v>
       </c>
       <c r="F142" t="n">
-        <v>-9116752</v>
+        <v>-9183766</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>-9116752</v>
+        <v>-9183766</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>-3929245</v>
+        <v>-4169403</v>
       </c>
       <c r="K142" t="n">
-        <v>-3929245</v>
+        <v>-4169403</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>-3929245</v>
+        <v>-4169403</v>
       </c>
       <c r="N142" t="n">
         <v>0</v>
@@ -8578,31 +8606,31 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>9572302</v>
+        <v>9589281</v>
       </c>
       <c r="F143" t="n">
-        <v>9572302</v>
+        <v>9589281</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>9572302</v>
+        <v>9589281</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>-8047020</v>
+        <v>-8143731</v>
       </c>
       <c r="K143" t="n">
-        <v>-8047020</v>
+        <v>-8143731</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>-8047020</v>
+        <v>-8143731</v>
       </c>
       <c r="N143" t="n">
         <v>0</v>
@@ -8630,31 +8658,31 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>23919968</v>
+        <v>23959652</v>
       </c>
       <c r="F144" t="n">
-        <v>23919968</v>
+        <v>23959652</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>23919968</v>
+        <v>23959652</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>-20892614</v>
+        <v>-20704108</v>
       </c>
       <c r="K144" t="n">
-        <v>-20892614</v>
+        <v>-20704108</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>-20892614</v>
+        <v>-20704108</v>
       </c>
       <c r="N144" t="n">
         <v>0</v>
@@ -8682,31 +8710,31 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>-23961716</v>
+        <v>-23999209</v>
       </c>
       <c r="F145" t="n">
-        <v>-23961716</v>
+        <v>-23999209</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>-23961716</v>
+        <v>-23999209</v>
       </c>
       <c r="I145" t="n">
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>19364375</v>
+        <v>19587609</v>
       </c>
       <c r="K145" t="n">
-        <v>19364375</v>
+        <v>19587609</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>19364375</v>
+        <v>19587609</v>
       </c>
       <c r="N145" t="n">
         <v>0</v>
@@ -8734,31 +8762,31 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>17720530</v>
+        <v>17688873</v>
       </c>
       <c r="F146" t="n">
-        <v>17720530</v>
+        <v>17688873</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>17720530</v>
+        <v>17688873</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>-4552708</v>
+        <v>-4433154</v>
       </c>
       <c r="K146" t="n">
-        <v>-4552708</v>
+        <v>-4433154</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>-4552708</v>
+        <v>-4433154</v>
       </c>
       <c r="N146" t="n">
         <v>0</v>
@@ -8786,31 +8814,31 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>-17742255</v>
+        <v>-17817745</v>
       </c>
       <c r="F147" t="n">
-        <v>-17742255</v>
+        <v>-17817745</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>-17742255</v>
+        <v>-17817745</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>4509117</v>
+        <v>4391832</v>
       </c>
       <c r="K147" t="n">
-        <v>4509117</v>
+        <v>4391832</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>4509117</v>
+        <v>4391832</v>
       </c>
       <c r="N147" t="n">
         <v>0</v>
@@ -8838,31 +8866,31 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5432057</v>
+        <v>5491903</v>
       </c>
       <c r="F148" t="n">
-        <v>5432057</v>
+        <v>5491903</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>5432057</v>
+        <v>5491903</v>
       </c>
       <c r="I148" t="n">
         <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>5961600</v>
+        <v>6207952</v>
       </c>
       <c r="K148" t="n">
-        <v>5961600</v>
+        <v>6207952</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>5961600</v>
+        <v>6207952</v>
       </c>
       <c r="N148" t="n">
         <v>0</v>
@@ -8926,13 +8954,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.6404</v>
+        <v>2.9681</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5931</v>
+        <v>2.9681</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.3</v>
+        <v>-0</v>
       </c>
       <c r="E2" t="n">
         <v>1.609</v>
@@ -9037,10 +9065,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>612070585</v>
+        <v>530262645</v>
       </c>
       <c r="E2" t="n">
-        <v>612070585</v>
+        <v>530262645</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -9075,15 +9103,15 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2192247143</v>
+        <v>2008463312</v>
       </c>
       <c r="E3" t="n">
-        <v>2192247143</v>
+        <v>2008463312</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
@@ -9113,22 +9141,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>61073263</v>
+        <v>42411855</v>
       </c>
       <c r="E4" t="n">
-        <v>60753195</v>
+        <v>42186896</v>
       </c>
       <c r="F4" t="n">
-        <v>5.09</v>
+        <v>3.53</v>
       </c>
       <c r="G4" t="n">
-        <v>5.06</v>
+        <v>3.52</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.027</v>
+        <v>-0.019</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -9159,26 +9187,26 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-56451591</v>
+        <v>-109259093</v>
       </c>
       <c r="E5" t="n">
-        <v>-56451594</v>
+        <v>-114766610</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.7</v>
+        <v>-9.1</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.7</v>
+        <v>-9.56</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>-5.04</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>-0.459</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -9205,22 +9233,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-56816160</v>
+        <v>-45895909</v>
       </c>
       <c r="E6" t="n">
-        <v>-56545000</v>
+        <v>-45661128</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.73</v>
+        <v>-3.82</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.71</v>
+        <v>-3.81</v>
       </c>
       <c r="H6" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="I6" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -9251,26 +9279,26 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61405875</v>
+        <v>119882937</v>
       </c>
       <c r="E7" t="n">
-        <v>61405877</v>
+        <v>125831427</v>
       </c>
       <c r="F7" t="n">
-        <v>5.12</v>
+        <v>9.99</v>
       </c>
       <c r="G7" t="n">
-        <v>5.12</v>
+        <v>10.49</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.496</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -9297,22 +9325,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>26536310</v>
+        <v>22464776</v>
       </c>
       <c r="E8" t="n">
-        <v>26538599</v>
+        <v>22506115</v>
       </c>
       <c r="F8" t="n">
-        <v>2.21</v>
+        <v>1.87</v>
       </c>
       <c r="G8" t="n">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01</v>
+        <v>0.18</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -9343,26 +9371,26 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-3911609</v>
+        <v>-39427854</v>
       </c>
       <c r="E9" t="n">
-        <v>-3911606</v>
+        <v>-41444349</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.33</v>
+        <v>-3.29</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.33</v>
+        <v>-3.45</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-5.11</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0.168</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -9389,22 +9417,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-16482595</v>
+        <v>-22015440</v>
       </c>
       <c r="E10" t="n">
-        <v>-16577325</v>
+        <v>-22083377</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.37</v>
+        <v>-1.83</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.38</v>
+        <v>-1.84</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.57</v>
+        <v>-0.31</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.008</v>
+        <v>-0.006</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -9435,26 +9463,26 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1311343</v>
+        <v>29776836</v>
       </c>
       <c r="E11" t="n">
-        <v>-1311344</v>
+        <v>31280349</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.11</v>
+        <v>2.48</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.11</v>
+        <v>2.61</v>
       </c>
       <c r="H11" t="n">
-        <v>-0</v>
+        <v>5.05</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>0.125</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -9481,22 +9509,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9155647</v>
+        <v>-2133251</v>
       </c>
       <c r="E12" t="n">
-        <v>8950114</v>
+        <v>-2285263</v>
       </c>
       <c r="F12" t="n">
-        <v>0.76</v>
+        <v>-0.18</v>
       </c>
       <c r="G12" t="n">
-        <v>0.75</v>
+        <v>-0.19</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.24</v>
+        <v>-7.13</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.017</v>
+        <v>-0.013</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -9527,26 +9555,26 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-24938632</v>
+        <v>-20024533</v>
       </c>
       <c r="E13" t="n">
-        <v>-24938633</v>
+        <v>-21006679</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.08</v>
+        <v>-1.67</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.08</v>
+        <v>-1.75</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>-4.9</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>-0.082</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -9573,19 +9601,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-5077214</v>
+        <v>-1516111</v>
       </c>
       <c r="E14" t="n">
-        <v>-4921435</v>
+        <v>-1355915</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.42</v>
+        <v>-0.13</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.41</v>
+        <v>-0.11</v>
       </c>
       <c r="H14" t="n">
-        <v>3.07</v>
+        <v>10.57</v>
       </c>
       <c r="I14" t="n">
         <v>0.013</v>
@@ -9619,26 +9647,26 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>26790116</v>
+        <v>20462070</v>
       </c>
       <c r="E15" t="n">
-        <v>26790115</v>
+        <v>21453113</v>
       </c>
       <c r="F15" t="n">
-        <v>2.23</v>
+        <v>1.71</v>
       </c>
       <c r="G15" t="n">
-        <v>2.23</v>
+        <v>1.79</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>4.84</v>
       </c>
       <c r="I15" t="n">
-        <v>-0</v>
+        <v>0.083</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -9665,19 +9693,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-21484633</v>
+        <v>-19388537</v>
       </c>
       <c r="E16" t="n">
-        <v>-21391314</v>
+        <v>-19292581</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.79</v>
+        <v>-1.62</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.78</v>
+        <v>-1.61</v>
       </c>
       <c r="H16" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="I16" t="n">
         <v>0.008</v>
@@ -9711,26 +9739,26 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>24726512</v>
+        <v>46689148</v>
       </c>
       <c r="E17" t="n">
-        <v>24726512</v>
+        <v>49011015</v>
       </c>
       <c r="F17" t="n">
-        <v>2.06</v>
+        <v>3.89</v>
       </c>
       <c r="G17" t="n">
-        <v>2.06</v>
+        <v>4.08</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.193</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -9757,15 +9785,15 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>-1.3</v>
+        <v>-0</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
@@ -9909,23 +9937,23 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1800000000</v>
+        <v>1500000000</v>
       </c>
       <c r="E2" t="n">
-        <v>15.4375</v>
+        <v>13.7484</v>
       </c>
       <c r="F2" t="n">
-        <v>15.4375</v>
+        <v>13.7484</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.204055</v>
+        <v>1.196292</v>
       </c>
       <c r="J2" t="n">
-        <v>1.204055</v>
+        <v>1.196292</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -9951,23 +9979,23 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>600000000</v>
+        <v>900000000</v>
       </c>
       <c r="E3" t="n">
-        <v>13.0671</v>
+        <v>11.548</v>
       </c>
       <c r="F3" t="n">
-        <v>13.0671</v>
+        <v>11.548</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.208762</v>
+        <v>1.208217</v>
       </c>
       <c r="J3" t="n">
-        <v>1.208762</v>
+        <v>1.208217</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -9996,20 +10024,20 @@
         <v>1000000000</v>
       </c>
       <c r="E4" t="n">
-        <v>7.3602</v>
+        <v>6.2525</v>
       </c>
       <c r="F4" t="n">
-        <v>7.3602</v>
+        <v>6.2525</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1.038313</v>
+        <v>1.040741</v>
       </c>
       <c r="J4" t="n">
-        <v>1.038313</v>
+        <v>1.040741</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -10038,20 +10066,20 @@
         <v>2800000000</v>
       </c>
       <c r="E5" t="n">
-        <v>7.3391</v>
+        <v>5.7579</v>
       </c>
       <c r="F5" t="n">
-        <v>7.3391</v>
+        <v>5.7579</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1.068395</v>
+        <v>1.072203</v>
       </c>
       <c r="J5" t="n">
-        <v>1.068395</v>
+        <v>1.072203</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -10080,20 +10108,20 @@
         <v>600000000</v>
       </c>
       <c r="E6" t="n">
-        <v>6.8716</v>
+        <v>5.1528</v>
       </c>
       <c r="F6" t="n">
-        <v>6.8716</v>
+        <v>5.1528</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1.043497</v>
+        <v>1.037965</v>
       </c>
       <c r="J6" t="n">
-        <v>1.043497</v>
+        <v>1.037965</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -10119,27 +10147,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>800000000</v>
+        <v>1400000000</v>
       </c>
       <c r="E7" t="n">
-        <v>6.4844</v>
+        <v>4.5974</v>
       </c>
       <c r="F7" t="n">
-        <v>6.4844</v>
+        <v>4.5974</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1.048341</v>
+        <v>0.975513</v>
       </c>
       <c r="J7" t="n">
-        <v>1.048341</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
+        <v>0.975513</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="b">
         <v>1</v>
       </c>
@@ -10147,7 +10173,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -10161,27 +10187,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>200000000</v>
+        <v>420000000</v>
       </c>
       <c r="E8" t="n">
-        <v>5.7952</v>
+        <v>4.5029</v>
       </c>
       <c r="F8" t="n">
-        <v>5.7952</v>
+        <v>4.5029</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>1.000014</v>
+        <v>0.122719</v>
       </c>
       <c r="J8" t="n">
-        <v>1.000014</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
+        <v>0.122719</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="b">
         <v>1</v>
       </c>
@@ -10203,27 +10227,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1600000000</v>
+        <v>1200000000</v>
       </c>
       <c r="E9" t="n">
-        <v>5.6888</v>
+        <v>3.74</v>
       </c>
       <c r="F9" t="n">
-        <v>5.6888</v>
+        <v>3.74</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.006951</v>
+        <v>0.94935</v>
       </c>
       <c r="J9" t="n">
-        <v>1.006951</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
+        <v>0.94935</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="b">
         <v>1</v>
       </c>
@@ -10231,7 +10253,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -10245,23 +10267,23 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>400000000</v>
+        <v>200000000</v>
       </c>
       <c r="E10" t="n">
-        <v>5.1067</v>
+        <v>3.5616</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1067</v>
+        <v>3.5616</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1.000025</v>
+        <v>1.000009</v>
       </c>
       <c r="J10" t="n">
-        <v>1.000025</v>
+        <v>1.000009</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -10273,7 +10295,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -10287,23 +10309,23 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>420000000</v>
+        <v>200000000</v>
       </c>
       <c r="E11" t="n">
-        <v>4.5044</v>
+        <v>3.0085</v>
       </c>
       <c r="F11" t="n">
-        <v>4.5044</v>
+        <v>3.0085</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.120171</v>
+        <v>0.9999980000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.120171</v>
+        <v>0.9999980000000001</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="b">
@@ -10500,10 +10522,10 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.888948</v>
+        <v>-0.913922</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.888948</v>
+        <v>-0.913922</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="b">
@@ -10530,10 +10552,10 @@
         <v>400000000</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0288</v>
+        <v>-0.0094</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0288</v>
+        <v>-0.0094</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="b">
@@ -10570,20 +10592,20 @@
         <v>1600000000</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.5067</v>
+        <v>-2.3518</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.5067</v>
+        <v>-2.3518</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.979131</v>
+        <v>-0.980063</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.979131</v>
+        <v>-0.980063</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="b">
@@ -10610,20 +10632,20 @@
         <v>1800000000</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.837</v>
+        <v>-3.3294</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.837</v>
+        <v>-3.3294</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.99749</v>
+        <v>-0.983021</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.99749</v>
+        <v>-0.983021</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="b">
@@ -10633,7 +10655,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0000</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -10647,25 +10669,27 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>420000000</v>
+        <v>400000000</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.6492</v>
+        <v>-3.7091</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.6492</v>
+        <v>-3.7091</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.136045</v>
+        <v>-1.000008</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.136045</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
+        <v>-1.000008</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
       <c r="L20" t="b">
         <v>1</v>
       </c>
@@ -10673,7 +10697,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -10687,27 +10711,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1200000000</v>
+        <v>420000000</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.6836</v>
+        <v>-3.889</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.6836</v>
+        <v>-3.889</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.012372</v>
+        <v>-0.103925</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.012372</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.103925</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="b">
         <v>1</v>
       </c>
@@ -10715,7 +10737,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10729,23 +10751,23 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>400000000</v>
+        <v>1200000000</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.787</v>
+        <v>-3.924</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.787</v>
+        <v>-3.924</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.000014</v>
+        <v>-1.005845</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.000014</v>
+        <v>-1.005845</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>

--- a/optimize_prep/output/approx_accuracy_report.xlsx
+++ b/optimize_prep/output/approx_accuracy_report.xlsx
@@ -504,16 +504,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18912329</v>
+        <v>24322192</v>
       </c>
       <c r="E2" t="n">
-        <v>18912329</v>
+        <v>24322192</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>18912329</v>
+        <v>24322192</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -522,10 +522,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>51541880</v>
+        <v>66957115</v>
       </c>
       <c r="K2" t="n">
-        <v>51541880</v>
+        <v>66957115</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -551,16 +551,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-16333649</v>
+        <v>-20997891</v>
       </c>
       <c r="E3" t="n">
-        <v>-16333649</v>
+        <v>-20997891</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-16333649</v>
+        <v>-20997891</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -569,10 +569,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-43648352</v>
+        <v>-54962565</v>
       </c>
       <c r="K3" t="n">
-        <v>-43648352</v>
+        <v>-54962565</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -598,34 +598,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>62524947</v>
+        <v>63281779</v>
       </c>
       <c r="E4" t="n">
-        <v>62524947</v>
+        <v>63281779</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>56013584</v>
+        <v>56717761</v>
       </c>
       <c r="H4" t="n">
-        <v>-10.41</v>
+        <v>-10.37</v>
       </c>
       <c r="I4" t="n">
-        <v>6511363</v>
+        <v>6564018</v>
       </c>
       <c r="J4" t="n">
-        <v>1040741358</v>
+        <v>1044642000</v>
       </c>
       <c r="K4" t="n">
-        <v>1040741358</v>
+        <v>1044642000</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>-0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -645,31 +645,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>161220249</v>
+        <v>161080947</v>
       </c>
       <c r="E5" t="n">
-        <v>161220249</v>
+        <v>161080947</v>
       </c>
       <c r="F5" t="n">
         <v>-0</v>
       </c>
       <c r="G5" t="n">
-        <v>107719453</v>
+        <v>107632430</v>
       </c>
       <c r="H5" t="n">
         <v>-33.18</v>
       </c>
       <c r="I5" t="n">
-        <v>53500797</v>
+        <v>53448516</v>
       </c>
       <c r="J5" t="n">
-        <v>3002169303</v>
+        <v>3001588278</v>
       </c>
       <c r="K5" t="n">
-        <v>3002169303</v>
+        <v>3001588278</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -692,34 +692,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>103931989</v>
+        <v>103936384</v>
       </c>
       <c r="E6" t="n">
-        <v>103931989</v>
+        <v>103936384</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>93689692</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10246692</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1087577241</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1087577241</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>-0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>93674632</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-9.869999999999999</v>
-      </c>
-      <c r="I6" t="n">
-        <v>10257358</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1087394962</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1087394962</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -739,34 +739,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>206226421</v>
+        <v>206367314</v>
       </c>
       <c r="E7" t="n">
-        <v>206226421</v>
+        <v>206367314</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>183854038</v>
+        <v>184075231</v>
       </c>
       <c r="H7" t="n">
-        <v>-10.85</v>
+        <v>-10.8</v>
       </c>
       <c r="I7" t="n">
-        <v>22372383</v>
+        <v>22292083</v>
       </c>
       <c r="J7" t="n">
-        <v>1794438346</v>
+        <v>1796114499</v>
       </c>
       <c r="K7" t="n">
-        <v>1794438346</v>
+        <v>1796114499</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -786,34 +786,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>64363634</v>
+        <v>72341794</v>
       </c>
       <c r="E8" t="n">
-        <v>64363634</v>
+        <v>72341794</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>62835467</v>
+        <v>62313424</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.37</v>
+        <v>-13.86</v>
       </c>
       <c r="I8" t="n">
-        <v>1528167</v>
+        <v>10028370</v>
       </c>
       <c r="J8" t="n">
-        <v>1365717822</v>
+        <v>1491278447</v>
       </c>
       <c r="K8" t="n">
-        <v>1365717822</v>
+        <v>1491278447</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -833,28 +833,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>44879720</v>
+        <v>43133457</v>
       </c>
       <c r="E9" t="n">
-        <v>44879720</v>
+        <v>43133457</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>43924259</v>
+        <v>42977193</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.13</v>
+        <v>-0.36</v>
       </c>
       <c r="I9" t="n">
-        <v>955461</v>
+        <v>156264</v>
       </c>
       <c r="J9" t="n">
-        <v>1139220439</v>
+        <v>1109330699</v>
       </c>
       <c r="K9" t="n">
-        <v>1139220439</v>
+        <v>1109330699</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -968,28 +968,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>30917064</v>
+        <v>32001877</v>
       </c>
       <c r="E12" t="n">
-        <v>30917064</v>
+        <v>32001877</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G12" t="n">
-        <v>20450890</v>
+        <v>20584163</v>
       </c>
       <c r="H12" t="n">
-        <v>-33.85</v>
+        <v>-35.68</v>
       </c>
       <c r="I12" t="n">
-        <v>10466173</v>
+        <v>11417714</v>
       </c>
       <c r="J12" t="n">
-        <v>622779011</v>
+        <v>627167127</v>
       </c>
       <c r="K12" t="n">
-        <v>622779011</v>
+        <v>627167127</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1015,31 +1015,31 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-47087873</v>
+        <v>-48088020</v>
       </c>
       <c r="E13" t="n">
-        <v>-47087873</v>
+        <v>-48088020</v>
       </c>
       <c r="F13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-45743687</v>
+        <v>-44594832</v>
       </c>
       <c r="H13" t="n">
-        <v>2.85</v>
+        <v>7.26</v>
       </c>
       <c r="I13" t="n">
-        <v>-1344186</v>
+        <v>-3493189</v>
       </c>
       <c r="J13" t="n">
-        <v>-1207014536</v>
+        <v>-1208239316</v>
       </c>
       <c r="K13" t="n">
-        <v>-1207014536</v>
+        <v>-1208239316</v>
       </c>
       <c r="L13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1199,10 +1199,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-3107336432</v>
+        <v>-2833159688</v>
       </c>
       <c r="K17" t="n">
-        <v>-3107336432</v>
+        <v>-2833159688</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1275,34 +1275,34 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-59930073</v>
+        <v>-69943537</v>
       </c>
       <c r="E19" t="n">
-        <v>-59930073</v>
+        <v>-69943537</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-54701293</v>
+        <v>-63769409</v>
       </c>
       <c r="H19" t="n">
-        <v>8.720000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="I19" t="n">
-        <v>-5228780</v>
+        <v>-6174127</v>
       </c>
       <c r="J19" t="n">
-        <v>-1769437421</v>
+        <v>-2065192056</v>
       </c>
       <c r="K19" t="n">
-        <v>-1769437421</v>
+        <v>-2065192056</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>-0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1322,28 +1322,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7123275</v>
+        <v>7531326</v>
       </c>
       <c r="E20" t="n">
-        <v>7123275</v>
+        <v>7531326</v>
       </c>
       <c r="F20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>4094832</v>
+        <v>4094995</v>
       </c>
       <c r="H20" t="n">
-        <v>-42.51</v>
+        <v>-45.63</v>
       </c>
       <c r="I20" t="n">
-        <v>3028443</v>
+        <v>3436331</v>
       </c>
       <c r="J20" t="n">
-        <v>200001856</v>
+        <v>200001061</v>
       </c>
       <c r="K20" t="n">
-        <v>200001856</v>
+        <v>200001061</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1369,28 +1369,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-14836517</v>
+        <v>-14772956</v>
       </c>
       <c r="E21" t="n">
-        <v>-14836517</v>
+        <v>-14772956</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-8189827</v>
+        <v>-8189953</v>
       </c>
       <c r="H21" t="n">
-        <v>44.8</v>
+        <v>44.56</v>
       </c>
       <c r="I21" t="n">
-        <v>-6646690</v>
+        <v>-6583003</v>
       </c>
       <c r="J21" t="n">
-        <v>-400003152</v>
+        <v>-400002724</v>
       </c>
       <c r="K21" t="n">
-        <v>-400003152</v>
+        <v>-400002724</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1565,16 +1565,16 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>376792</v>
+        <v>436018</v>
       </c>
       <c r="K2" t="n">
-        <v>376792</v>
+        <v>436018</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>376792</v>
+        <v>436018</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -1613,16 +1613,16 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>834529</v>
+        <v>1031684</v>
       </c>
       <c r="K3" t="n">
-        <v>834529</v>
+        <v>1031684</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>834529</v>
+        <v>1031684</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -1661,16 +1661,16 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>2118813</v>
+        <v>2618441</v>
       </c>
       <c r="K4" t="n">
-        <v>2118813</v>
+        <v>2618441</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2118813</v>
+        <v>2618441</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -1709,16 +1709,16 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>-2013346</v>
+        <v>-2491021</v>
       </c>
       <c r="K5" t="n">
-        <v>-2013346</v>
+        <v>-2491021</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2013346</v>
+        <v>-2491021</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1757,16 +1757,16 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>499522</v>
+        <v>644126</v>
       </c>
       <c r="K6" t="n">
-        <v>499522</v>
+        <v>644126</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>499522</v>
+        <v>644126</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1805,16 +1805,16 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>-494294</v>
+        <v>-637470</v>
       </c>
       <c r="K7" t="n">
-        <v>-494294</v>
+        <v>-637470</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-494294</v>
+        <v>-637470</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1853,16 +1853,16 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>-592634</v>
+        <v>-706027</v>
       </c>
       <c r="K8" t="n">
-        <v>-592634</v>
+        <v>-706027</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-592634</v>
+        <v>-706027</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1890,31 +1890,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>-358241</v>
+        <v>-356405</v>
       </c>
       <c r="F9" t="n">
-        <v>-358241</v>
+        <v>-356405</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-358241</v>
+        <v>-356405</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>9854888</v>
+        <v>12325416</v>
       </c>
       <c r="K9" t="n">
-        <v>9854888</v>
+        <v>12325416</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>9854888</v>
+        <v>12325416</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1942,31 +1942,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2329966</v>
+        <v>2933650</v>
       </c>
       <c r="F10" t="n">
-        <v>2329966</v>
+        <v>2933650</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2329966</v>
+        <v>2933650</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>8869291</v>
+        <v>11057934</v>
       </c>
       <c r="K10" t="n">
-        <v>8869291</v>
+        <v>11057934</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>8869291</v>
+        <v>11057934</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1994,31 +1994,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5805855</v>
+        <v>7309319</v>
       </c>
       <c r="F11" t="n">
-        <v>5805855</v>
+        <v>7309319</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5805855</v>
+        <v>7309319</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>22660022</v>
+        <v>28240921</v>
       </c>
       <c r="K11" t="n">
-        <v>22660022</v>
+        <v>28240921</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>22660022</v>
+        <v>28240921</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -2046,31 +2046,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>-5869068</v>
+        <v>-7391016</v>
       </c>
       <c r="F12" t="n">
-        <v>-5869068</v>
+        <v>-7391016</v>
       </c>
       <c r="G12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-5869068</v>
+        <v>-7391016</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-21083423</v>
+        <v>-26309926</v>
       </c>
       <c r="K12" t="n">
-        <v>-21083423</v>
+        <v>-26309926</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-21083423</v>
+        <v>-26309926</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2098,31 +2098,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2652353</v>
+        <v>3256283</v>
       </c>
       <c r="F13" t="n">
-        <v>2652353</v>
+        <v>3256283</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2652353</v>
+        <v>3256283</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>59379</v>
+        <v>35749</v>
       </c>
       <c r="K13" t="n">
-        <v>59379</v>
+        <v>35749</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>59379</v>
+        <v>35749</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2150,34 +2150,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>-2668023</v>
+        <v>-3274863</v>
       </c>
       <c r="F14" t="n">
-        <v>-2668023</v>
+        <v>-3274863</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-2668023</v>
+        <v>-3274863</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-59448</v>
+        <v>-35737</v>
       </c>
       <c r="K14" t="n">
-        <v>-59448</v>
+        <v>-35737</v>
       </c>
       <c r="L14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-59448</v>
+        <v>-35737</v>
       </c>
       <c r="N14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2202,31 +2202,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>-398719</v>
+        <v>-588661</v>
       </c>
       <c r="F15" t="n">
-        <v>-398719</v>
+        <v>-588661</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-398719</v>
+        <v>-588661</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-11592419</v>
+        <v>-14506127</v>
       </c>
       <c r="K15" t="n">
-        <v>-11592419</v>
+        <v>-14506127</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-11592419</v>
+        <v>-14506127</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2254,31 +2254,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>515466</v>
+        <v>497210</v>
       </c>
       <c r="F16" t="n">
-        <v>515466</v>
+        <v>497210</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
-        <v>7026829</v>
+        <v>7061228</v>
       </c>
       <c r="I16" t="n">
-        <v>1263.2</v>
+        <v>1320.17</v>
       </c>
       <c r="J16" t="n">
-        <v>19127645</v>
+        <v>19586353</v>
       </c>
       <c r="K16" t="n">
-        <v>19127645</v>
+        <v>19586355</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>19127645</v>
+        <v>19586355</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2306,34 +2306,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-2112710</v>
+        <v>-2087968</v>
       </c>
       <c r="F17" t="n">
-        <v>-2112710</v>
+        <v>-2087968</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>4398653</v>
+        <v>4476050</v>
       </c>
       <c r="I17" t="n">
-        <v>308.2</v>
+        <v>314.37</v>
       </c>
       <c r="J17" t="n">
-        <v>24548392</v>
+        <v>24939534</v>
       </c>
       <c r="K17" t="n">
-        <v>24548393</v>
+        <v>24939533</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M17" t="n">
-        <v>24548393</v>
+        <v>24939533</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -2358,31 +2358,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>-3951763</v>
+        <v>-3897341</v>
       </c>
       <c r="F18" t="n">
-        <v>-3951763</v>
+        <v>-3897341</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H18" t="n">
-        <v>2559600</v>
+        <v>2666677</v>
       </c>
       <c r="I18" t="n">
-        <v>164.77</v>
+        <v>168.42</v>
       </c>
       <c r="J18" t="n">
-        <v>63098557</v>
+        <v>64125311</v>
       </c>
       <c r="K18" t="n">
-        <v>63098556</v>
+        <v>64125309</v>
       </c>
       <c r="L18" t="n">
         <v>-0</v>
       </c>
       <c r="M18" t="n">
-        <v>63098556</v>
+        <v>64125309</v>
       </c>
       <c r="N18" t="n">
         <v>-0</v>
@@ -2410,34 +2410,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2186709</v>
+        <v>2142069</v>
       </c>
       <c r="F19" t="n">
-        <v>2186709</v>
+        <v>2142069</v>
       </c>
       <c r="G19" t="n">
         <v>-0</v>
       </c>
       <c r="H19" t="n">
-        <v>8698072</v>
+        <v>8706087</v>
       </c>
       <c r="I19" t="n">
-        <v>297.77</v>
+        <v>306.43</v>
       </c>
       <c r="J19" t="n">
-        <v>-57630359</v>
+        <v>-58505766</v>
       </c>
       <c r="K19" t="n">
-        <v>-57630359</v>
+        <v>-58505766</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M19" t="n">
-        <v>-57630359</v>
+        <v>-58505766</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="20">
@@ -2462,34 +2462,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-3362379</v>
+        <v>-3316929</v>
       </c>
       <c r="F20" t="n">
-        <v>-3362379</v>
+        <v>-3316929</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H20" t="n">
-        <v>3148984</v>
+        <v>3247089</v>
       </c>
       <c r="I20" t="n">
-        <v>193.65</v>
+        <v>197.89</v>
       </c>
       <c r="J20" t="n">
-        <v>7570213</v>
+        <v>7554739</v>
       </c>
       <c r="K20" t="n">
-        <v>7570217</v>
+        <v>7554738</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M20" t="n">
-        <v>7570217</v>
+        <v>7554738</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="21">
@@ -2514,31 +2514,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1596634</v>
+        <v>1560994</v>
       </c>
       <c r="F21" t="n">
-        <v>1596634</v>
+        <v>1560994</v>
       </c>
       <c r="G21" t="n">
         <v>-0</v>
       </c>
       <c r="H21" t="n">
-        <v>8107997</v>
+        <v>8125012</v>
       </c>
       <c r="I21" t="n">
-        <v>407.82</v>
+        <v>420.5</v>
       </c>
       <c r="J21" t="n">
-        <v>-7497146</v>
+        <v>-7481861</v>
       </c>
       <c r="K21" t="n">
-        <v>-7497143</v>
+        <v>-7481859</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-7497143</v>
+        <v>-7481859</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2566,34 +2566,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-1796051</v>
+        <v>-1775876</v>
       </c>
       <c r="F22" t="n">
-        <v>-1796051</v>
+        <v>-1775876</v>
       </c>
       <c r="G22" t="n">
         <v>-0</v>
       </c>
       <c r="H22" t="n">
-        <v>4715312</v>
+        <v>4788142</v>
       </c>
       <c r="I22" t="n">
-        <v>362.54</v>
+        <v>369.62</v>
       </c>
       <c r="J22" t="n">
-        <v>-24082355</v>
+        <v>-24588602</v>
       </c>
       <c r="K22" t="n">
-        <v>-24082353</v>
+        <v>-24588603</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M22" t="n">
-        <v>-24082353</v>
+        <v>-24588603</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="23">
@@ -2618,34 +2618,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3879646</v>
+        <v>4012611</v>
       </c>
       <c r="F23" t="n">
-        <v>3879646</v>
+        <v>4012611</v>
       </c>
       <c r="G23" t="n">
         <v>-0</v>
       </c>
       <c r="H23" t="n">
-        <v>57380443</v>
+        <v>57461127</v>
       </c>
       <c r="I23" t="n">
-        <v>1379.01</v>
+        <v>1332.01</v>
       </c>
       <c r="J23" t="n">
-        <v>-1919071</v>
+        <v>-1866014</v>
       </c>
       <c r="K23" t="n">
-        <v>-1919072</v>
+        <v>-1866011</v>
       </c>
       <c r="L23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1919072</v>
+        <v>-1866011</v>
       </c>
       <c r="N23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2670,31 +2670,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-23448148</v>
+        <v>-23483339</v>
       </c>
       <c r="F24" t="n">
-        <v>-23448148</v>
+        <v>-23483340</v>
       </c>
       <c r="G24" t="n">
         <v>-0</v>
       </c>
       <c r="H24" t="n">
-        <v>30052649</v>
+        <v>29965176</v>
       </c>
       <c r="I24" t="n">
-        <v>228.17</v>
+        <v>227.6</v>
       </c>
       <c r="J24" t="n">
-        <v>10387181</v>
+        <v>10286307</v>
       </c>
       <c r="K24" t="n">
-        <v>10385387</v>
+        <v>10284726</v>
       </c>
       <c r="L24" t="n">
         <v>-0.02</v>
       </c>
       <c r="M24" t="n">
-        <v>10385387</v>
+        <v>10284726</v>
       </c>
       <c r="N24" t="n">
         <v>-0.02</v>
@@ -2722,31 +2722,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-58010321</v>
+        <v>-58096339</v>
       </c>
       <c r="F25" t="n">
-        <v>-58010322</v>
+        <v>-58096339</v>
       </c>
       <c r="G25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-4509525</v>
+        <v>-4647823</v>
       </c>
       <c r="I25" t="n">
-        <v>92.23</v>
+        <v>92</v>
       </c>
       <c r="J25" t="n">
-        <v>26923019</v>
+        <v>26663480</v>
       </c>
       <c r="K25" t="n">
-        <v>26923013</v>
+        <v>26663480</v>
       </c>
       <c r="L25" t="n">
         <v>-0</v>
       </c>
       <c r="M25" t="n">
-        <v>26923013</v>
+        <v>26663480</v>
       </c>
       <c r="N25" t="n">
         <v>-0</v>
@@ -2774,31 +2774,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>57364290</v>
+        <v>57447918</v>
       </c>
       <c r="F26" t="n">
-        <v>57364290</v>
+        <v>57447918</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H26" t="n">
-        <v>110865087</v>
+        <v>110896434</v>
       </c>
       <c r="I26" t="n">
-        <v>93.26000000000001</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-23761984</v>
+        <v>-23521803</v>
       </c>
       <c r="K26" t="n">
-        <v>-23761986</v>
+        <v>-23521803</v>
       </c>
       <c r="L26" t="n">
         <v>-0</v>
       </c>
       <c r="M26" t="n">
-        <v>-23761986</v>
+        <v>-23521803</v>
       </c>
       <c r="N26" t="n">
         <v>-0</v>
@@ -2826,31 +2826,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-27304620</v>
+        <v>-27459403</v>
       </c>
       <c r="F27" t="n">
-        <v>-27304620</v>
+        <v>-27459403</v>
       </c>
       <c r="G27" t="n">
         <v>-0</v>
       </c>
       <c r="H27" t="n">
-        <v>26196177</v>
+        <v>25989113</v>
       </c>
       <c r="I27" t="n">
-        <v>195.94</v>
+        <v>194.65</v>
       </c>
       <c r="J27" t="n">
-        <v>12288176</v>
+        <v>12139530</v>
       </c>
       <c r="K27" t="n">
-        <v>12288177</v>
+        <v>12139531</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>12288177</v>
+        <v>12139531</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2878,34 +2878,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>26578322</v>
+        <v>26730887</v>
       </c>
       <c r="F28" t="n">
-        <v>26578322</v>
+        <v>26730887</v>
       </c>
       <c r="G28" t="n">
         <v>-0</v>
       </c>
       <c r="H28" t="n">
-        <v>80079119</v>
+        <v>80179403</v>
       </c>
       <c r="I28" t="n">
-        <v>201.29</v>
+        <v>199.95</v>
       </c>
       <c r="J28" t="n">
-        <v>-12087800</v>
+        <v>-11938824</v>
       </c>
       <c r="K28" t="n">
-        <v>-12087802</v>
+        <v>-11938822</v>
       </c>
       <c r="L28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-12087802</v>
+        <v>-11938822</v>
       </c>
       <c r="N28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2930,34 +2930,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2871407</v>
+        <v>2756796</v>
       </c>
       <c r="F29" t="n">
-        <v>2871407</v>
+        <v>2756796</v>
       </c>
       <c r="G29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>56372204</v>
+        <v>56205312</v>
       </c>
       <c r="I29" t="n">
-        <v>1863.23</v>
+        <v>1938.79</v>
       </c>
       <c r="J29" t="n">
-        <v>-530212</v>
+        <v>-552091</v>
       </c>
       <c r="K29" t="n">
-        <v>-530212</v>
+        <v>-552089</v>
       </c>
       <c r="L29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-530212</v>
+        <v>-552089</v>
       </c>
       <c r="N29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2982,34 +2982,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1427855</v>
+        <v>1423828</v>
       </c>
       <c r="F30" t="n">
-        <v>1427855</v>
+        <v>1423828</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>11685213</v>
+        <v>11670520</v>
       </c>
       <c r="I30" t="n">
-        <v>718.38</v>
+        <v>719.66</v>
       </c>
       <c r="J30" t="n">
-        <v>27223787</v>
+        <v>27259014</v>
       </c>
       <c r="K30" t="n">
-        <v>27223786</v>
+        <v>27259016</v>
       </c>
       <c r="L30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>27223786</v>
+        <v>27259016</v>
       </c>
       <c r="N30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3034,34 +3034,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>-1481620</v>
+        <v>-1488350</v>
       </c>
       <c r="F31" t="n">
-        <v>-1481620</v>
+        <v>-1488350</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>8775738</v>
+        <v>8758342</v>
       </c>
       <c r="I31" t="n">
-        <v>692.3099999999999</v>
+        <v>688.46</v>
       </c>
       <c r="J31" t="n">
-        <v>31064292</v>
+        <v>31092440</v>
       </c>
       <c r="K31" t="n">
-        <v>31064292</v>
+        <v>31092441</v>
       </c>
       <c r="L31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>31064292</v>
+        <v>31092441</v>
       </c>
       <c r="N31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3086,31 +3086,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-3580552</v>
+        <v>-3587681</v>
       </c>
       <c r="F32" t="n">
-        <v>-3580552</v>
+        <v>-3587681</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>6676806</v>
+        <v>6659011</v>
       </c>
       <c r="I32" t="n">
-        <v>286.47</v>
+        <v>285.61</v>
       </c>
       <c r="J32" t="n">
-        <v>80106383</v>
+        <v>80180835</v>
       </c>
       <c r="K32" t="n">
-        <v>80106383</v>
+        <v>80180832</v>
       </c>
       <c r="L32" t="n">
         <v>-0</v>
       </c>
       <c r="M32" t="n">
-        <v>80106383</v>
+        <v>80180832</v>
       </c>
       <c r="N32" t="n">
         <v>-0</v>
@@ -3138,34 +3138,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3425504</v>
+        <v>3419709</v>
       </c>
       <c r="F33" t="n">
-        <v>3425504</v>
+        <v>3419709</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>13682862</v>
+        <v>13666401</v>
       </c>
       <c r="I33" t="n">
-        <v>299.44</v>
+        <v>299.64</v>
       </c>
       <c r="J33" t="n">
-        <v>-72388761</v>
+        <v>-72450582</v>
       </c>
       <c r="K33" t="n">
-        <v>-72388764</v>
+        <v>-72450582</v>
       </c>
       <c r="L33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-72388764</v>
+        <v>-72450582</v>
       </c>
       <c r="N33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3190,31 +3190,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-2827786</v>
+        <v>-2836701</v>
       </c>
       <c r="F34" t="n">
-        <v>-2827786</v>
+        <v>-2836701</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>7429572</v>
+        <v>7409991</v>
       </c>
       <c r="I34" t="n">
-        <v>362.73</v>
+        <v>361.22</v>
       </c>
       <c r="J34" t="n">
-        <v>6900166</v>
+        <v>6897147</v>
       </c>
       <c r="K34" t="n">
-        <v>6900167</v>
+        <v>6897149</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>6900167</v>
+        <v>6897149</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -3242,34 +3242,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2671575</v>
+        <v>2667554</v>
       </c>
       <c r="F35" t="n">
-        <v>2671575</v>
+        <v>2667554</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>12928933</v>
+        <v>12914246</v>
       </c>
       <c r="I35" t="n">
-        <v>383.94</v>
+        <v>384.12</v>
       </c>
       <c r="J35" t="n">
-        <v>-6836046</v>
+        <v>-6833058</v>
       </c>
       <c r="K35" t="n">
-        <v>-6836047</v>
+        <v>-6833058</v>
       </c>
       <c r="L35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-6836047</v>
+        <v>-6833058</v>
       </c>
       <c r="N35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3294,34 +3294,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-1036988</v>
+        <v>-1045615</v>
       </c>
       <c r="F36" t="n">
-        <v>-1036988</v>
+        <v>-1045615</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H36" t="n">
-        <v>9220370</v>
+        <v>9201077</v>
       </c>
       <c r="I36" t="n">
-        <v>989.15</v>
+        <v>979.97</v>
       </c>
       <c r="J36" t="n">
-        <v>-33007158</v>
+        <v>-33045040</v>
       </c>
       <c r="K36" t="n">
-        <v>-33007157</v>
+        <v>-33045040</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M36" t="n">
-        <v>-33007157</v>
+        <v>-33045040</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="37">
@@ -3346,31 +3346,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-480472</v>
+        <v>-498386</v>
       </c>
       <c r="F37" t="n">
-        <v>-570033</v>
+        <v>-594569</v>
       </c>
       <c r="G37" t="n">
-        <v>-18.64</v>
+        <v>-19.3</v>
       </c>
       <c r="H37" t="n">
-        <v>21802350</v>
+        <v>21697514</v>
       </c>
       <c r="I37" t="n">
-        <v>4637.69</v>
+        <v>4453.56</v>
       </c>
       <c r="J37" t="n">
-        <v>-5459093</v>
+        <v>-5470529</v>
       </c>
       <c r="K37" t="n">
-        <v>-5459093</v>
+        <v>-5470530</v>
       </c>
       <c r="L37" t="n">
         <v>-0</v>
       </c>
       <c r="M37" t="n">
-        <v>-5459093</v>
+        <v>-5470530</v>
       </c>
       <c r="N37" t="n">
         <v>-0</v>
@@ -3398,31 +3398,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-9761534</v>
+        <v>-9764729</v>
       </c>
       <c r="F38" t="n">
-        <v>-9762189</v>
+        <v>-9765408</v>
       </c>
       <c r="G38" t="n">
         <v>-0.01</v>
       </c>
       <c r="H38" t="n">
-        <v>12610194</v>
+        <v>12526675</v>
       </c>
       <c r="I38" t="n">
-        <v>229.18</v>
+        <v>228.28</v>
       </c>
       <c r="J38" t="n">
-        <v>9648193</v>
+        <v>9668714</v>
       </c>
       <c r="K38" t="n">
-        <v>9647834</v>
+        <v>9668382</v>
       </c>
       <c r="L38" t="n">
         <v>-0</v>
       </c>
       <c r="M38" t="n">
-        <v>9647834</v>
+        <v>9668382</v>
       </c>
       <c r="N38" t="n">
         <v>-0</v>
@@ -3450,31 +3450,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-23843007</v>
+        <v>-23849876</v>
       </c>
       <c r="F39" t="n">
-        <v>-23843212</v>
+        <v>-23850048</v>
       </c>
       <c r="G39" t="n">
         <v>-0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1470829</v>
+        <v>-1557965</v>
       </c>
       <c r="I39" t="n">
-        <v>93.83</v>
+        <v>93.47</v>
       </c>
       <c r="J39" t="n">
-        <v>24559799</v>
+        <v>24611995</v>
       </c>
       <c r="K39" t="n">
-        <v>24559798</v>
+        <v>24611994</v>
       </c>
       <c r="L39" t="n">
         <v>-0</v>
       </c>
       <c r="M39" t="n">
-        <v>24559798</v>
+        <v>24611994</v>
       </c>
       <c r="N39" t="n">
         <v>-0</v>
@@ -3502,31 +3502,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>23163020</v>
+        <v>23168422</v>
       </c>
       <c r="F40" t="n">
-        <v>23161359</v>
+        <v>23166604</v>
       </c>
       <c r="G40" t="n">
         <v>-0.01</v>
       </c>
       <c r="H40" t="n">
-        <v>45533742</v>
+        <v>45458687</v>
       </c>
       <c r="I40" t="n">
-        <v>96.58</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>-23063001</v>
+        <v>-23111768</v>
       </c>
       <c r="K40" t="n">
-        <v>-23063001</v>
+        <v>-23111770</v>
       </c>
       <c r="L40" t="n">
         <v>-0</v>
       </c>
       <c r="M40" t="n">
-        <v>-23063001</v>
+        <v>-23111770</v>
       </c>
       <c r="N40" t="n">
         <v>-0</v>
@@ -3554,31 +3554,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-9681693</v>
+        <v>-9669632</v>
       </c>
       <c r="F41" t="n">
-        <v>-9603532</v>
+        <v>-9585658</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="H41" t="n">
-        <v>12768851</v>
+        <v>12706425</v>
       </c>
       <c r="I41" t="n">
-        <v>231.89</v>
+        <v>231.41</v>
       </c>
       <c r="J41" t="n">
-        <v>14666900</v>
+        <v>14697866</v>
       </c>
       <c r="K41" t="n">
-        <v>14666901</v>
+        <v>14697867</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>14666901</v>
+        <v>14697867</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -3606,31 +3606,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>8966590</v>
+        <v>8952989</v>
       </c>
       <c r="F42" t="n">
-        <v>8886285</v>
+        <v>8866729</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.9</v>
+        <v>-0.96</v>
       </c>
       <c r="H42" t="n">
-        <v>31258668</v>
+        <v>31158812</v>
       </c>
       <c r="I42" t="n">
-        <v>248.61</v>
+        <v>248.03</v>
       </c>
       <c r="J42" t="n">
-        <v>-14471370</v>
+        <v>-14502086</v>
       </c>
       <c r="K42" t="n">
-        <v>-14471371</v>
+        <v>-14502088</v>
       </c>
       <c r="L42" t="n">
         <v>-0</v>
       </c>
       <c r="M42" t="n">
-        <v>-14471371</v>
+        <v>-14502088</v>
       </c>
       <c r="N42" t="n">
         <v>-0</v>
@@ -3658,34 +3658,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2672956</v>
+        <v>2688826</v>
       </c>
       <c r="F43" t="n">
-        <v>2753700</v>
+        <v>2775550</v>
       </c>
       <c r="G43" t="n">
-        <v>3.02</v>
+        <v>3.23</v>
       </c>
       <c r="H43" t="n">
-        <v>25126083</v>
+        <v>25067633</v>
       </c>
       <c r="I43" t="n">
-        <v>840.01</v>
+        <v>832.29</v>
       </c>
       <c r="J43" t="n">
-        <v>2451429</v>
+        <v>2456723</v>
       </c>
       <c r="K43" t="n">
-        <v>2451428</v>
+        <v>2456723</v>
       </c>
       <c r="L43" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2451428</v>
+        <v>2456723</v>
       </c>
       <c r="N43" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3710,34 +3710,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>121593</v>
+        <v>1434024</v>
       </c>
       <c r="F44" t="n">
-        <v>121593</v>
+        <v>1434024</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1649760</v>
+        <v>11462394</v>
       </c>
       <c r="I44" t="n">
-        <v>1256.78</v>
+        <v>699.3200000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>38066062</v>
+        <v>32128752</v>
       </c>
       <c r="K44" t="n">
-        <v>39815929</v>
+        <v>33277421</v>
       </c>
       <c r="L44" t="n">
-        <v>4.6</v>
+        <v>3.58</v>
       </c>
       <c r="M44" t="n">
-        <v>39815929</v>
+        <v>33277421</v>
       </c>
       <c r="N44" t="n">
-        <v>4.6</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="45">
@@ -3762,34 +3762,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-165856</v>
+        <v>-1275861</v>
       </c>
       <c r="F45" t="n">
-        <v>-165856</v>
+        <v>-1275861</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1362311</v>
+        <v>8752509</v>
       </c>
       <c r="I45" t="n">
-        <v>921.38</v>
+        <v>786.01</v>
       </c>
       <c r="J45" t="n">
-        <v>41732637</v>
+        <v>38974664</v>
       </c>
       <c r="K45" t="n">
-        <v>43900369</v>
+        <v>40397633</v>
       </c>
       <c r="L45" t="n">
-        <v>5.19</v>
+        <v>3.65</v>
       </c>
       <c r="M45" t="n">
-        <v>43900369</v>
+        <v>40397633</v>
       </c>
       <c r="N45" t="n">
-        <v>5.19</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="46">
@@ -3814,34 +3814,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-412318</v>
+        <v>-3176194</v>
       </c>
       <c r="F46" t="n">
-        <v>-412318</v>
+        <v>-3176194</v>
       </c>
       <c r="G46" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1115849</v>
+        <v>6852176</v>
       </c>
       <c r="I46" t="n">
-        <v>370.63</v>
+        <v>315.74</v>
       </c>
       <c r="J46" t="n">
-        <v>107196047</v>
+        <v>100161347</v>
       </c>
       <c r="K46" t="n">
-        <v>112752316</v>
+        <v>103808661</v>
       </c>
       <c r="L46" t="n">
-        <v>5.18</v>
+        <v>3.64</v>
       </c>
       <c r="M46" t="n">
-        <v>112752316</v>
+        <v>103808661</v>
       </c>
       <c r="N46" t="n">
-        <v>5.18</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="47">
@@ -3866,34 +3866,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>420124</v>
+        <v>3221374</v>
       </c>
       <c r="F47" t="n">
-        <v>420124</v>
+        <v>3221374</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1948291</v>
+        <v>13249744</v>
       </c>
       <c r="I47" t="n">
-        <v>363.74</v>
+        <v>311.31</v>
       </c>
       <c r="J47" t="n">
-        <v>-98062148</v>
+        <v>-91498854</v>
       </c>
       <c r="K47" t="n">
-        <v>-103181099</v>
+        <v>-94859099</v>
       </c>
       <c r="L47" t="n">
-        <v>-5.22</v>
+        <v>-3.67</v>
       </c>
       <c r="M47" t="n">
-        <v>-103181099</v>
+        <v>-94859099</v>
       </c>
       <c r="N47" t="n">
-        <v>-5.22</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="48">
@@ -3918,34 +3918,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-273441</v>
+        <v>-2544336</v>
       </c>
       <c r="F48" t="n">
-        <v>-273441</v>
+        <v>-2544336</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1254726</v>
+        <v>7484034</v>
       </c>
       <c r="I48" t="n">
-        <v>558.86</v>
+        <v>394.14</v>
       </c>
       <c r="J48" t="n">
-        <v>7890942</v>
+        <v>10458290</v>
       </c>
       <c r="K48" t="n">
-        <v>8503379</v>
+        <v>10860313</v>
       </c>
       <c r="L48" t="n">
-        <v>7.76</v>
+        <v>3.84</v>
       </c>
       <c r="M48" t="n">
-        <v>8503379</v>
+        <v>10860313</v>
       </c>
       <c r="N48" t="n">
-        <v>7.76</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="49">
@@ -3970,34 +3970,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>276853</v>
+        <v>2572504</v>
       </c>
       <c r="F49" t="n">
-        <v>276853</v>
+        <v>2572504</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1805020</v>
+        <v>12600874</v>
       </c>
       <c r="I49" t="n">
-        <v>551.98</v>
+        <v>389.83</v>
       </c>
       <c r="J49" t="n">
-        <v>-7824022</v>
+        <v>-10355551</v>
       </c>
       <c r="K49" t="n">
-        <v>-8430858</v>
+        <v>-10753898</v>
       </c>
       <c r="L49" t="n">
-        <v>-7.76</v>
+        <v>-3.85</v>
       </c>
       <c r="M49" t="n">
-        <v>-8430858</v>
+        <v>-10753898</v>
       </c>
       <c r="N49" t="n">
-        <v>-7.76</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="50">
@@ -4022,34 +4022,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-60138</v>
+        <v>-920592</v>
       </c>
       <c r="F50" t="n">
-        <v>-60138</v>
+        <v>-920592</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1468029</v>
+        <v>9107778</v>
       </c>
       <c r="I50" t="n">
-        <v>2541.08</v>
+        <v>1089.34</v>
       </c>
       <c r="J50" t="n">
-        <v>-46094447</v>
+        <v>-39824788</v>
       </c>
       <c r="K50" t="n">
-        <v>-48290913</v>
+        <v>-41266619</v>
       </c>
       <c r="L50" t="n">
-        <v>-4.77</v>
+        <v>-3.62</v>
       </c>
       <c r="M50" t="n">
-        <v>-48290913</v>
+        <v>-41266619</v>
       </c>
       <c r="N50" t="n">
-        <v>-4.77</v>
+        <v>-3.62</v>
       </c>
     </row>
     <row r="51">
@@ -4074,34 +4074,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>7450</v>
+        <v>749555</v>
       </c>
       <c r="F51" t="n">
-        <v>36255</v>
+        <v>749555</v>
       </c>
       <c r="G51" t="n">
-        <v>386.66</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>991716</v>
+        <v>905819</v>
       </c>
       <c r="I51" t="n">
-        <v>13212.11</v>
+        <v>20.85</v>
       </c>
       <c r="J51" t="n">
-        <v>-5851574</v>
+        <v>-5002510</v>
       </c>
       <c r="K51" t="n">
-        <v>-6156836</v>
+        <v>-5002510</v>
       </c>
       <c r="L51" t="n">
-        <v>-5.22</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-6156836</v>
+        <v>-5002510</v>
       </c>
       <c r="N51" t="n">
-        <v>-5.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-5817299</v>
+        <v>-5623883</v>
       </c>
       <c r="F52" t="n">
-        <v>-5827879</v>
+        <v>-5623883</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-4872418</v>
+        <v>-5467619</v>
       </c>
       <c r="I52" t="n">
-        <v>16.24</v>
+        <v>2.78</v>
       </c>
       <c r="J52" t="n">
-        <v>3676911</v>
+        <v>3148918</v>
       </c>
       <c r="K52" t="n">
-        <v>3857129</v>
+        <v>3140325</v>
       </c>
       <c r="L52" t="n">
-        <v>4.9</v>
+        <v>-0.27</v>
       </c>
       <c r="M52" t="n">
-        <v>3857129</v>
+        <v>3140325</v>
       </c>
       <c r="N52" t="n">
-        <v>4.9</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="53">
@@ -4178,34 +4178,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>-14490522</v>
+        <v>-14010662</v>
       </c>
       <c r="F53" t="n">
-        <v>-14516811</v>
+        <v>-14010662</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.18</v>
+        <v>-0</v>
       </c>
       <c r="H53" t="n">
-        <v>-13561350</v>
+        <v>-13854398</v>
       </c>
       <c r="I53" t="n">
-        <v>6.41</v>
+        <v>1.12</v>
       </c>
       <c r="J53" t="n">
-        <v>9199669</v>
+        <v>7876742</v>
       </c>
       <c r="K53" t="n">
-        <v>9651357</v>
+        <v>7876741</v>
       </c>
       <c r="L53" t="n">
-        <v>4.91</v>
+        <v>-0</v>
       </c>
       <c r="M53" t="n">
-        <v>9651357</v>
+        <v>7876741</v>
       </c>
       <c r="N53" t="n">
-        <v>4.91</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="54">
@@ -4230,34 +4230,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>14668923</v>
+        <v>14188000</v>
       </c>
       <c r="F54" t="n">
-        <v>14695686</v>
+        <v>14188000</v>
       </c>
       <c r="G54" t="n">
-        <v>0.18</v>
+        <v>-0</v>
       </c>
       <c r="H54" t="n">
-        <v>15651147</v>
+        <v>14344264</v>
       </c>
       <c r="I54" t="n">
-        <v>6.7</v>
+        <v>1.1</v>
       </c>
       <c r="J54" t="n">
-        <v>-9078936</v>
+        <v>-7767111</v>
       </c>
       <c r="K54" t="n">
-        <v>-9526834</v>
+        <v>-7767111</v>
       </c>
       <c r="L54" t="n">
-        <v>-4.93</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-9526834</v>
+        <v>-7767111</v>
       </c>
       <c r="N54" t="n">
-        <v>-4.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -4282,34 +4282,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>-5838721</v>
+        <v>-6298053</v>
       </c>
       <c r="F55" t="n">
-        <v>-5875013</v>
+        <v>-6298053</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.62</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-4919552</v>
+        <v>-6141789</v>
       </c>
       <c r="I55" t="n">
-        <v>15.74</v>
+        <v>2.48</v>
       </c>
       <c r="J55" t="n">
-        <v>8963080</v>
+        <v>7669586</v>
       </c>
       <c r="K55" t="n">
-        <v>9418206</v>
+        <v>7669586</v>
       </c>
       <c r="L55" t="n">
-        <v>5.08</v>
+        <v>-0</v>
       </c>
       <c r="M55" t="n">
-        <v>9418206</v>
+        <v>7669586</v>
       </c>
       <c r="N55" t="n">
-        <v>5.08</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="56">
@@ -4334,34 +4334,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5870155</v>
+        <v>6342533</v>
       </c>
       <c r="F56" t="n">
-        <v>5906698</v>
+        <v>6342533</v>
       </c>
       <c r="G56" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>6862159</v>
+        <v>6498797</v>
       </c>
       <c r="I56" t="n">
-        <v>16.9</v>
+        <v>2.46</v>
       </c>
       <c r="J56" t="n">
-        <v>-8862275</v>
+        <v>-7579957</v>
       </c>
       <c r="K56" t="n">
-        <v>-9313903</v>
+        <v>-7579957</v>
       </c>
       <c r="L56" t="n">
-        <v>-5.1</v>
+        <v>-0</v>
       </c>
       <c r="M56" t="n">
-        <v>-9313903</v>
+        <v>-7579957</v>
       </c>
       <c r="N56" t="n">
-        <v>-5.1</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="57">
@@ -4386,34 +4386,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1813524</v>
+        <v>1073856</v>
       </c>
       <c r="F57" t="n">
-        <v>1789997</v>
+        <v>1073856</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>2745458</v>
+        <v>1230120</v>
       </c>
       <c r="I57" t="n">
-        <v>51.39</v>
+        <v>14.55</v>
       </c>
       <c r="J57" t="n">
-        <v>4319808</v>
+        <v>3696065</v>
       </c>
       <c r="K57" t="n">
-        <v>4546894</v>
+        <v>3696065</v>
       </c>
       <c r="L57" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>4546894</v>
+        <v>3696065</v>
       </c>
       <c r="N57" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -5110,31 +5110,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1029233</v>
+        <v>794440</v>
       </c>
       <c r="F72" t="n">
-        <v>1022051</v>
+        <v>801015</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.7</v>
+        <v>0.83</v>
       </c>
       <c r="H72" t="n">
-        <v>11488224</v>
+        <v>12218729</v>
       </c>
       <c r="I72" t="n">
-        <v>1016.19</v>
+        <v>1438.03</v>
       </c>
       <c r="J72" t="n">
-        <v>1409442</v>
+        <v>1901001</v>
       </c>
       <c r="K72" t="n">
-        <v>1409441</v>
+        <v>1901000</v>
       </c>
       <c r="L72" t="n">
         <v>-0</v>
       </c>
       <c r="M72" t="n">
-        <v>1409441</v>
+        <v>1901000</v>
       </c>
       <c r="N72" t="n">
         <v>-0</v>
@@ -5162,31 +5162,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>-4119060</v>
+        <v>-4096083</v>
       </c>
       <c r="F73" t="n">
-        <v>-4011869</v>
+        <v>-4027202</v>
       </c>
       <c r="G73" t="n">
-        <v>2.6</v>
+        <v>1.68</v>
       </c>
       <c r="H73" t="n">
-        <v>6454304</v>
+        <v>7390512</v>
       </c>
       <c r="I73" t="n">
-        <v>256.69</v>
+        <v>280.43</v>
       </c>
       <c r="J73" t="n">
-        <v>3914832</v>
+        <v>4389173</v>
       </c>
       <c r="K73" t="n">
-        <v>3914669</v>
+        <v>4389025</v>
       </c>
       <c r="L73" t="n">
         <v>-0</v>
       </c>
       <c r="M73" t="n">
-        <v>3914669</v>
+        <v>4389025</v>
       </c>
       <c r="N73" t="n">
         <v>-0</v>
@@ -5214,31 +5214,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>-10196588</v>
+        <v>-10128696</v>
       </c>
       <c r="F74" t="n">
-        <v>-9935313</v>
+        <v>-9962088</v>
       </c>
       <c r="G74" t="n">
-        <v>2.56</v>
+        <v>1.64</v>
       </c>
       <c r="H74" t="n">
-        <v>530860</v>
+        <v>1455626</v>
       </c>
       <c r="I74" t="n">
-        <v>105.21</v>
+        <v>114.37</v>
       </c>
       <c r="J74" t="n">
-        <v>10026157</v>
+        <v>11254091</v>
       </c>
       <c r="K74" t="n">
-        <v>10026157</v>
+        <v>11254091</v>
       </c>
       <c r="L74" t="n">
         <v>-0</v>
       </c>
       <c r="M74" t="n">
-        <v>10026157</v>
+        <v>11254091</v>
       </c>
       <c r="N74" t="n">
         <v>-0</v>
@@ -5266,31 +5266,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>10091019</v>
+        <v>10009209</v>
       </c>
       <c r="F75" t="n">
-        <v>9840957</v>
+        <v>9852007</v>
       </c>
       <c r="G75" t="n">
-        <v>-2.48</v>
+        <v>-1.57</v>
       </c>
       <c r="H75" t="n">
-        <v>20307130</v>
+        <v>21269721</v>
       </c>
       <c r="I75" t="n">
-        <v>101.24</v>
+        <v>112.5</v>
       </c>
       <c r="J75" t="n">
-        <v>-9226156</v>
+        <v>-10312100</v>
       </c>
       <c r="K75" t="n">
-        <v>-9226156</v>
+        <v>-10312101</v>
       </c>
       <c r="L75" t="n">
         <v>-0</v>
       </c>
       <c r="M75" t="n">
-        <v>-9226156</v>
+        <v>-10312101</v>
       </c>
       <c r="N75" t="n">
         <v>-0</v>
@@ -5318,31 +5318,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>-5101862</v>
+        <v>-4876534</v>
       </c>
       <c r="F76" t="n">
-        <v>-4983534</v>
+        <v>-4809563</v>
       </c>
       <c r="G76" t="n">
-        <v>2.32</v>
+        <v>1.37</v>
       </c>
       <c r="H76" t="n">
-        <v>5482639</v>
+        <v>6608151</v>
       </c>
       <c r="I76" t="n">
-        <v>207.46</v>
+        <v>235.51</v>
       </c>
       <c r="J76" t="n">
-        <v>2689258</v>
+        <v>2729219</v>
       </c>
       <c r="K76" t="n">
-        <v>2689258</v>
+        <v>2729217</v>
       </c>
       <c r="L76" t="n">
         <v>-0</v>
       </c>
       <c r="M76" t="n">
-        <v>2689258</v>
+        <v>2729217</v>
       </c>
       <c r="N76" t="n">
         <v>-0</v>
@@ -5370,31 +5370,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4983624</v>
+        <v>4743361</v>
       </c>
       <c r="F77" t="n">
-        <v>4875375</v>
+        <v>4684877</v>
       </c>
       <c r="G77" t="n">
-        <v>-2.17</v>
+        <v>-1.23</v>
       </c>
       <c r="H77" t="n">
-        <v>15341548</v>
+        <v>16102591</v>
       </c>
       <c r="I77" t="n">
-        <v>207.84</v>
+        <v>239.48</v>
       </c>
       <c r="J77" t="n">
-        <v>-2649708</v>
+        <v>-2687105</v>
       </c>
       <c r="K77" t="n">
-        <v>-2649708</v>
+        <v>-2687107</v>
       </c>
       <c r="L77" t="n">
         <v>-0</v>
       </c>
       <c r="M77" t="n">
-        <v>-2649708</v>
+        <v>-2687107</v>
       </c>
       <c r="N77" t="n">
         <v>-0</v>
@@ -5422,31 +5422,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>192490</v>
+        <v>386689</v>
       </c>
       <c r="F78" t="n">
-        <v>176612</v>
+        <v>368266</v>
       </c>
       <c r="G78" t="n">
-        <v>-8.25</v>
+        <v>-4.76</v>
       </c>
       <c r="H78" t="n">
-        <v>10642785</v>
+        <v>11785980</v>
       </c>
       <c r="I78" t="n">
-        <v>5429.02</v>
+        <v>2947.92</v>
       </c>
       <c r="J78" t="n">
-        <v>-2322410</v>
+        <v>-2884535</v>
       </c>
       <c r="K78" t="n">
-        <v>-2322410</v>
+        <v>-2884535</v>
       </c>
       <c r="L78" t="n">
         <v>-0</v>
       </c>
       <c r="M78" t="n">
-        <v>-2322410</v>
+        <v>-2884535</v>
       </c>
       <c r="N78" t="n">
         <v>-0</v>
@@ -5474,34 +5474,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>479101</v>
+        <v>514453</v>
       </c>
       <c r="F79" t="n">
-        <v>479101</v>
+        <v>378360</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>-26.45</v>
       </c>
       <c r="H79" t="n">
-        <v>-865085</v>
+        <v>-3114829</v>
       </c>
       <c r="I79" t="n">
-        <v>-280.56</v>
+        <v>-705.46</v>
       </c>
       <c r="J79" t="n">
-        <v>6667523</v>
+        <v>6585076</v>
       </c>
       <c r="K79" t="n">
-        <v>6667523</v>
+        <v>6585076</v>
       </c>
       <c r="L79" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>6667523</v>
+        <v>6585076</v>
       </c>
       <c r="N79" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -5526,34 +5526,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5664618</v>
+        <v>5744814</v>
       </c>
       <c r="F80" t="n">
-        <v>5664618</v>
+        <v>5782301</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="H80" t="n">
-        <v>4320432</v>
+        <v>2289112</v>
       </c>
       <c r="I80" t="n">
-        <v>-23.73</v>
+        <v>-60.15</v>
       </c>
       <c r="J80" t="n">
-        <v>-4720020</v>
+        <v>-4581281</v>
       </c>
       <c r="K80" t="n">
-        <v>-4720021</v>
+        <v>-4581281</v>
       </c>
       <c r="L80" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-4720021</v>
+        <v>-4581281</v>
       </c>
       <c r="N80" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5578,31 +5578,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>14109429</v>
+        <v>14308649</v>
       </c>
       <c r="F81" t="n">
-        <v>14109429</v>
+        <v>14401984</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="H81" t="n">
-        <v>12765243</v>
+        <v>10908795</v>
       </c>
       <c r="I81" t="n">
-        <v>-9.529999999999999</v>
+        <v>-23.76</v>
       </c>
       <c r="J81" t="n">
-        <v>-11820692</v>
+        <v>-11472178</v>
       </c>
       <c r="K81" t="n">
-        <v>-11820692</v>
+        <v>-11472178</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-11820692</v>
+        <v>-11472178</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
@@ -5630,34 +5630,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>-14282337</v>
+        <v>-14487728</v>
       </c>
       <c r="F82" t="n">
-        <v>-14282337</v>
+        <v>-14582330</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>-0.65</v>
       </c>
       <c r="H82" t="n">
-        <v>-15626523</v>
+        <v>-18075519</v>
       </c>
       <c r="I82" t="n">
-        <v>-9.41</v>
+        <v>-24.76</v>
       </c>
       <c r="J82" t="n">
-        <v>11653823</v>
+        <v>11312932</v>
       </c>
       <c r="K82" t="n">
-        <v>11653823</v>
+        <v>11312932</v>
       </c>
       <c r="L82" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>11653823</v>
+        <v>11312932</v>
       </c>
       <c r="N82" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -5682,34 +5682,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5250634</v>
+        <v>5301013</v>
       </c>
       <c r="F83" t="n">
-        <v>5250634</v>
+        <v>5459912</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H83" t="n">
-        <v>3906448</v>
+        <v>1966723</v>
       </c>
       <c r="I83" t="n">
-        <v>-25.6</v>
+        <v>-62.9</v>
       </c>
       <c r="J83" t="n">
-        <v>-10750191</v>
+        <v>-10535455</v>
       </c>
       <c r="K83" t="n">
-        <v>-10750191</v>
+        <v>-10535455</v>
       </c>
       <c r="L83" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>-10750191</v>
+        <v>-10535455</v>
       </c>
       <c r="N83" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5734,34 +5734,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>-5279611</v>
+        <v>-5330591</v>
       </c>
       <c r="F84" t="n">
-        <v>-5279611</v>
+        <v>-5490393</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H84" t="n">
-        <v>-6623797</v>
+        <v>-8983582</v>
       </c>
       <c r="I84" t="n">
-        <v>-25.46</v>
+        <v>-68.53</v>
       </c>
       <c r="J84" t="n">
-        <v>10622577</v>
+        <v>10412130</v>
       </c>
       <c r="K84" t="n">
-        <v>10622577</v>
+        <v>10412130</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M84" t="n">
-        <v>10622577</v>
+        <v>10412130</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="85">
@@ -5786,34 +5786,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>-2218536</v>
+        <v>-2274156</v>
       </c>
       <c r="F85" t="n">
-        <v>-2218536</v>
+        <v>-2159399</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="H85" t="n">
-        <v>-3562722</v>
+        <v>-5652588</v>
       </c>
       <c r="I85" t="n">
-        <v>-60.59</v>
+        <v>-148.56</v>
       </c>
       <c r="J85" t="n">
-        <v>-4755791</v>
+        <v>-4721182</v>
       </c>
       <c r="K85" t="n">
-        <v>-4755791</v>
+        <v>-4721182</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M85" t="n">
-        <v>-4755791</v>
+        <v>-4721182</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="86">
@@ -6773,16 +6773,16 @@
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="n">
-        <v>-63357815</v>
+        <v>-57767420</v>
       </c>
       <c r="K107" t="n">
-        <v>-63357815</v>
+        <v>-57767420</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>-63357815</v>
+        <v>-57767420</v>
       </c>
       <c r="N107" t="n">
         <v>0</v>
@@ -6821,19 +6821,19 @@
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="n">
-        <v>-70534127</v>
+        <v>-64310528</v>
       </c>
       <c r="K108" t="n">
-        <v>-70534127</v>
+        <v>-64310528</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M108" t="n">
-        <v>-70534127</v>
+        <v>-64310528</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="109">
@@ -6869,16 +6869,16 @@
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="n">
-        <v>-181921970</v>
+        <v>-165870031</v>
       </c>
       <c r="K109" t="n">
-        <v>-181921970</v>
+        <v>-165870031</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>-181921970</v>
+        <v>-165870031</v>
       </c>
       <c r="N109" t="n">
         <v>0</v>
@@ -6917,16 +6917,16 @@
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="n">
-        <v>164270778</v>
+        <v>149776297</v>
       </c>
       <c r="K110" t="n">
-        <v>164270778</v>
+        <v>149776297</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>164270778</v>
+        <v>149776297</v>
       </c>
       <c r="N110" t="n">
         <v>0</v>
@@ -6965,16 +6965,16 @@
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="n">
-        <v>-14295464</v>
+        <v>-13034099</v>
       </c>
       <c r="K111" t="n">
-        <v>-14295464</v>
+        <v>-13034099</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>-14295464</v>
+        <v>-13034099</v>
       </c>
       <c r="N111" t="n">
         <v>0</v>
@@ -7013,16 +7013,16 @@
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="n">
-        <v>14170671</v>
+        <v>12920318</v>
       </c>
       <c r="K112" t="n">
-        <v>14170671</v>
+        <v>12920318</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>14170671</v>
+        <v>12920318</v>
       </c>
       <c r="N112" t="n">
         <v>0</v>
@@ -7061,16 +7061,16 @@
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
-        <v>76300973</v>
+        <v>69568534</v>
       </c>
       <c r="K113" t="n">
-        <v>76300973</v>
+        <v>69568534</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>76300973</v>
+        <v>69568534</v>
       </c>
       <c r="N113" t="n">
         <v>0</v>
@@ -7327,13 +7327,13 @@
         <v>-13</v>
       </c>
       <c r="L118" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
         <v>-13</v>
       </c>
       <c r="N118" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -7462,34 +7462,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>-19790474</v>
+        <v>-23088081</v>
       </c>
       <c r="F121" t="n">
-        <v>-19790474</v>
+        <v>-23088081</v>
       </c>
       <c r="G121" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>-25019254</v>
+        <v>-29262208</v>
       </c>
       <c r="I121" t="n">
-        <v>-26.42</v>
+        <v>-26.74</v>
       </c>
       <c r="J121" t="n">
-        <v>7635515</v>
+        <v>8907461</v>
       </c>
       <c r="K121" t="n">
-        <v>7694427</v>
+        <v>8974430</v>
       </c>
       <c r="L121" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="M121" t="n">
-        <v>7694427</v>
+        <v>8974430</v>
       </c>
       <c r="N121" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="122">
@@ -7514,34 +7514,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>9923133</v>
+        <v>11576718</v>
       </c>
       <c r="F122" t="n">
-        <v>9923133</v>
+        <v>11576718</v>
       </c>
       <c r="G122" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>4694353</v>
+        <v>5402591</v>
       </c>
       <c r="I122" t="n">
-        <v>-52.69</v>
+        <v>-53.33</v>
       </c>
       <c r="J122" t="n">
-        <v>-4573893</v>
+        <v>-5345112</v>
       </c>
       <c r="K122" t="n">
-        <v>-4597662</v>
+        <v>-5372132</v>
       </c>
       <c r="L122" t="n">
-        <v>-0.52</v>
+        <v>-0.51</v>
       </c>
       <c r="M122" t="n">
-        <v>-4597662</v>
+        <v>-5372132</v>
       </c>
       <c r="N122" t="n">
-        <v>-0.52</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="123">
@@ -7566,34 +7566,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>24765078</v>
+        <v>28891896</v>
       </c>
       <c r="F123" t="n">
-        <v>24765078</v>
+        <v>28891896</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>19536298</v>
+        <v>22717769</v>
       </c>
       <c r="I123" t="n">
-        <v>-21.11</v>
+        <v>-21.37</v>
       </c>
       <c r="J123" t="n">
-        <v>-11463995</v>
+        <v>-13397085</v>
       </c>
       <c r="K123" t="n">
-        <v>-11523456</v>
+        <v>-13464678</v>
       </c>
       <c r="L123" t="n">
-        <v>-0.52</v>
+        <v>-0.5</v>
       </c>
       <c r="M123" t="n">
-        <v>-11523456</v>
+        <v>-13464678</v>
       </c>
       <c r="N123" t="n">
-        <v>-0.52</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="124">
@@ -7618,34 +7618,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>-24908362</v>
+        <v>-29059060</v>
       </c>
       <c r="F124" t="n">
-        <v>-24908362</v>
+        <v>-29059060</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>-30137142</v>
+        <v>-35233187</v>
       </c>
       <c r="I124" t="n">
-        <v>-20.99</v>
+        <v>-21.25</v>
       </c>
       <c r="J124" t="n">
-        <v>11367007</v>
+        <v>13283388</v>
       </c>
       <c r="K124" t="n">
-        <v>11426344</v>
+        <v>13350840</v>
       </c>
       <c r="L124" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="M124" t="n">
-        <v>11426344</v>
+        <v>13350840</v>
       </c>
       <c r="N124" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="125">
@@ -7670,34 +7670,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>27493587</v>
+        <v>32074457</v>
       </c>
       <c r="F125" t="n">
-        <v>27493587</v>
+        <v>32074457</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>22264807</v>
+        <v>25900330</v>
       </c>
       <c r="I125" t="n">
-        <v>-19.02</v>
+        <v>-19.25</v>
       </c>
       <c r="J125" t="n">
-        <v>-11451659</v>
+        <v>-13368738</v>
       </c>
       <c r="K125" t="n">
-        <v>-11528184</v>
+        <v>-13455729</v>
       </c>
       <c r="L125" t="n">
-        <v>-0.67</v>
+        <v>-0.65</v>
       </c>
       <c r="M125" t="n">
-        <v>-11528184</v>
+        <v>-13455729</v>
       </c>
       <c r="N125" t="n">
-        <v>-0.67</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="126">
@@ -7722,34 +7722,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>-27657568</v>
+        <v>-32266121</v>
       </c>
       <c r="F126" t="n">
-        <v>-27657568</v>
+        <v>-32266121</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>-32886348</v>
+        <v>-38440248</v>
       </c>
       <c r="I126" t="n">
-        <v>-18.91</v>
+        <v>-19.14</v>
       </c>
       <c r="J126" t="n">
-        <v>11361895</v>
+        <v>13263749</v>
       </c>
       <c r="K126" t="n">
-        <v>11438215</v>
+        <v>13350507</v>
       </c>
       <c r="L126" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="M126" t="n">
-        <v>11438215</v>
+        <v>13350507</v>
       </c>
       <c r="N126" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="127">
@@ -7774,34 +7774,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>15134922</v>
+        <v>17656942</v>
       </c>
       <c r="F127" t="n">
-        <v>15134922</v>
+        <v>17656942</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>9906142</v>
+        <v>11482815</v>
       </c>
       <c r="I127" t="n">
-        <v>-34.55</v>
+        <v>-34.97</v>
       </c>
       <c r="J127" t="n">
-        <v>-5660259</v>
+        <v>-6600313</v>
       </c>
       <c r="K127" t="n">
-        <v>-5707374</v>
+        <v>-6653872</v>
       </c>
       <c r="L127" t="n">
-        <v>-0.83</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M127" t="n">
-        <v>-5707374</v>
+        <v>-6653872</v>
       </c>
       <c r="N127" t="n">
-        <v>-0.83</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="128">
@@ -7826,31 +7826,31 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5302097</v>
+        <v>4763387</v>
       </c>
       <c r="F128" t="n">
-        <v>5302097</v>
+        <v>4763387</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H128" t="n">
-        <v>8330540</v>
+        <v>8199718</v>
       </c>
       <c r="I128" t="n">
-        <v>57.12</v>
+        <v>72.14</v>
       </c>
       <c r="J128" t="n">
-        <v>-47787</v>
+        <v>-245440</v>
       </c>
       <c r="K128" t="n">
-        <v>-47787</v>
+        <v>-245440</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>-47787</v>
+        <v>-245440</v>
       </c>
       <c r="N128" t="n">
         <v>0</v>
@@ -7878,31 +7878,31 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>-1980954</v>
+        <v>-1903369</v>
       </c>
       <c r="F129" t="n">
-        <v>-1980954</v>
+        <v>-1903369</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>1047489</v>
+        <v>1532962</v>
       </c>
       <c r="I129" t="n">
-        <v>152.88</v>
+        <v>180.54</v>
       </c>
       <c r="J129" t="n">
-        <v>18550</v>
+        <v>98394</v>
       </c>
       <c r="K129" t="n">
-        <v>18550</v>
+        <v>98394</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>18550</v>
+        <v>98394</v>
       </c>
       <c r="N129" t="n">
         <v>0</v>
@@ -7930,31 +7930,31 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>-4951167</v>
+        <v>-4756570</v>
       </c>
       <c r="F130" t="n">
-        <v>-4951167</v>
+        <v>-4756570</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>-1922724</v>
+        <v>-1320239</v>
       </c>
       <c r="I130" t="n">
-        <v>61.17</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="J130" t="n">
-        <v>46427</v>
+        <v>246066</v>
       </c>
       <c r="K130" t="n">
-        <v>46427</v>
+        <v>246066</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>46427</v>
+        <v>246066</v>
       </c>
       <c r="N130" t="n">
         <v>0</v>
@@ -7982,31 +7982,31 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4952043</v>
+        <v>4762308</v>
       </c>
       <c r="F131" t="n">
-        <v>4952043</v>
+        <v>4762308</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>7980486</v>
+        <v>8198639</v>
       </c>
       <c r="I131" t="n">
-        <v>61.16</v>
+        <v>72.16</v>
       </c>
       <c r="J131" t="n">
-        <v>-46465</v>
+        <v>-245695</v>
       </c>
       <c r="K131" t="n">
-        <v>-46465</v>
+        <v>-245695</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>-46465</v>
+        <v>-245695</v>
       </c>
       <c r="N131" t="n">
         <v>0</v>
@@ -8034,31 +8034,31 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>-6642409</v>
+        <v>-6146385</v>
       </c>
       <c r="F132" t="n">
-        <v>-6642409</v>
+        <v>-6146385</v>
       </c>
       <c r="G132" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>-3613966</v>
+        <v>-2710054</v>
       </c>
       <c r="I132" t="n">
-        <v>45.59</v>
+        <v>55.91</v>
       </c>
       <c r="J132" t="n">
-        <v>60935</v>
+        <v>317864</v>
       </c>
       <c r="K132" t="n">
-        <v>60935</v>
+        <v>317864</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>60935</v>
+        <v>317864</v>
       </c>
       <c r="N132" t="n">
         <v>0</v>
@@ -8086,31 +8086,31 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6715630</v>
+        <v>6159720</v>
       </c>
       <c r="F133" t="n">
-        <v>6715630</v>
+        <v>6159720</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>9744073</v>
+        <v>9596051</v>
       </c>
       <c r="I133" t="n">
-        <v>45.1</v>
+        <v>55.79</v>
       </c>
       <c r="J133" t="n">
-        <v>-61245</v>
+        <v>-317395</v>
       </c>
       <c r="K133" t="n">
-        <v>-61245</v>
+        <v>-317394</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>-61245</v>
+        <v>-317394</v>
       </c>
       <c r="N133" t="n">
         <v>0</v>
@@ -8138,31 +8138,31 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>-4280610</v>
+        <v>-3802827</v>
       </c>
       <c r="F134" t="n">
-        <v>-4280610</v>
+        <v>-3802827</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H134" t="n">
-        <v>-1252167</v>
+        <v>-366496</v>
       </c>
       <c r="I134" t="n">
-        <v>70.75</v>
+        <v>90.36</v>
       </c>
       <c r="J134" t="n">
-        <v>38319</v>
+        <v>196389</v>
       </c>
       <c r="K134" t="n">
-        <v>38319</v>
+        <v>196389</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>38319</v>
+        <v>196389</v>
       </c>
       <c r="N134" t="n">
         <v>0</v>
@@ -8190,31 +8190,31 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>-9923964</v>
+        <v>-9908943</v>
       </c>
       <c r="F135" t="n">
-        <v>-9923964</v>
+        <v>-9908943</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>-16570654</v>
+        <v>-16491946</v>
       </c>
       <c r="I135" t="n">
-        <v>-66.98</v>
+        <v>-66.43000000000001</v>
       </c>
       <c r="J135" t="n">
-        <v>275711</v>
+        <v>351243</v>
       </c>
       <c r="K135" t="n">
-        <v>275711</v>
+        <v>351243</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>275711</v>
+        <v>351243</v>
       </c>
       <c r="N135" t="n">
         <v>0</v>
@@ -8242,34 +8242,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3891151</v>
+        <v>3861466</v>
       </c>
       <c r="F136" t="n">
-        <v>3891151</v>
+        <v>3861466</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>-2755539</v>
+        <v>-2721537</v>
       </c>
       <c r="I136" t="n">
-        <v>-170.82</v>
+        <v>-170.48</v>
       </c>
       <c r="J136" t="n">
-        <v>-109780</v>
+        <v>-140368</v>
       </c>
       <c r="K136" t="n">
-        <v>-109780</v>
+        <v>-140368</v>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M136" t="n">
-        <v>-109780</v>
+        <v>-140368</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="137">
@@ -8294,34 +8294,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>9725187</v>
+        <v>9650616</v>
       </c>
       <c r="F137" t="n">
-        <v>9725187</v>
+        <v>9650616</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>3078497</v>
+        <v>3067613</v>
       </c>
       <c r="I137" t="n">
-        <v>-68.34999999999999</v>
+        <v>-68.20999999999999</v>
       </c>
       <c r="J137" t="n">
-        <v>-274610</v>
+        <v>-351054</v>
       </c>
       <c r="K137" t="n">
-        <v>-274610</v>
+        <v>-351054</v>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M137" t="n">
-        <v>-274610</v>
+        <v>-351054</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="138">
@@ -8346,31 +8346,31 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>-9731494</v>
+        <v>-9658983</v>
       </c>
       <c r="F138" t="n">
-        <v>-9731494</v>
+        <v>-9658983</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>-16378184</v>
+        <v>-16241986</v>
       </c>
       <c r="I138" t="n">
-        <v>-68.3</v>
+        <v>-68.15000000000001</v>
       </c>
       <c r="J138" t="n">
-        <v>274503</v>
+        <v>350638</v>
       </c>
       <c r="K138" t="n">
-        <v>274503</v>
+        <v>350638</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>274503</v>
+        <v>350638</v>
       </c>
       <c r="N138" t="n">
         <v>0</v>
@@ -8398,31 +8398,31 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>12700572</v>
+        <v>12644113</v>
       </c>
       <c r="F139" t="n">
-        <v>12700572</v>
+        <v>12644113</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H139" t="n">
-        <v>6053882</v>
+        <v>6061110</v>
       </c>
       <c r="I139" t="n">
-        <v>-52.33</v>
+        <v>-52.06</v>
       </c>
       <c r="J139" t="n">
-        <v>-355774</v>
+        <v>-454159</v>
       </c>
       <c r="K139" t="n">
-        <v>-355774</v>
+        <v>-454159</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>-355774</v>
+        <v>-454159</v>
       </c>
       <c r="N139" t="n">
         <v>0</v>
@@ -8450,31 +8450,31 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>-12755861</v>
+        <v>-12713682</v>
       </c>
       <c r="F140" t="n">
-        <v>-12755861</v>
+        <v>-12713682</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>-19402551</v>
+        <v>-19296685</v>
       </c>
       <c r="I140" t="n">
-        <v>-52.11</v>
+        <v>-51.78</v>
       </c>
       <c r="J140" t="n">
-        <v>355946</v>
+        <v>453830</v>
       </c>
       <c r="K140" t="n">
-        <v>355946</v>
+        <v>453830</v>
       </c>
       <c r="L140" t="n">
         <v>-0</v>
       </c>
       <c r="M140" t="n">
-        <v>355946</v>
+        <v>453830</v>
       </c>
       <c r="N140" t="n">
         <v>-0</v>
@@ -8502,34 +8502,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>7950642</v>
+        <v>7944332</v>
       </c>
       <c r="F141" t="n">
-        <v>7950642</v>
+        <v>7944332</v>
       </c>
       <c r="G141" t="n">
         <v>-0</v>
       </c>
       <c r="H141" t="n">
-        <v>1303952</v>
+        <v>1361329</v>
       </c>
       <c r="I141" t="n">
-        <v>-83.59999999999999</v>
+        <v>-82.86</v>
       </c>
       <c r="J141" t="n">
-        <v>-220548</v>
+        <v>-281077</v>
       </c>
       <c r="K141" t="n">
-        <v>-220548</v>
+        <v>-281078</v>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M141" t="n">
-        <v>-220548</v>
+        <v>-281078</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="142">
@@ -8627,13 +8627,13 @@
         <v>-8143731</v>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M143" t="n">
         <v>-8143731</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="144">
@@ -8954,22 +8954,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.9681</v>
+        <v>2.7967</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9681</v>
+        <v>2.7967</v>
       </c>
       <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.6147</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.6147</v>
+      </c>
+      <c r="G2" t="n">
         <v>-0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.609</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.609</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>530262645</v>
+        <v>528545794</v>
       </c>
       <c r="E2" t="n">
-        <v>530262645</v>
+        <v>528545794</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -9103,15 +9103,15 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2008463312</v>
+        <v>2094998347</v>
       </c>
       <c r="E3" t="n">
-        <v>2008463312</v>
+        <v>2094998347</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
@@ -9141,22 +9141,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>42411855</v>
+        <v>38693708</v>
       </c>
       <c r="E4" t="n">
-        <v>42186896</v>
+        <v>38440086</v>
       </c>
       <c r="F4" t="n">
-        <v>3.53</v>
+        <v>3.22</v>
       </c>
       <c r="G4" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.53</v>
+        <v>-0.66</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.019</v>
+        <v>-0.021</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -9187,22 +9187,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-109259093</v>
+        <v>-121961997</v>
       </c>
       <c r="E5" t="n">
-        <v>-114766610</v>
+        <v>-125254792</v>
       </c>
       <c r="F5" t="n">
-        <v>-9.1</v>
+        <v>-10.16</v>
       </c>
       <c r="G5" t="n">
-        <v>-9.56</v>
+        <v>-10.44</v>
       </c>
       <c r="H5" t="n">
-        <v>-5.04</v>
+        <v>-2.7</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.459</v>
+        <v>-0.274</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -9233,22 +9233,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-45895909</v>
+        <v>-42208099</v>
       </c>
       <c r="E6" t="n">
-        <v>-45661128</v>
+        <v>-41948327</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.82</v>
+        <v>-3.52</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.81</v>
+        <v>-3.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.51</v>
+        <v>0.62</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02</v>
+        <v>0.022</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -9279,22 +9279,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>119882937</v>
+        <v>134318193</v>
       </c>
       <c r="E7" t="n">
-        <v>125831427</v>
+        <v>137897907</v>
       </c>
       <c r="F7" t="n">
-        <v>9.99</v>
+        <v>11.19</v>
       </c>
       <c r="G7" t="n">
-        <v>10.49</v>
+        <v>11.49</v>
       </c>
       <c r="H7" t="n">
-        <v>4.96</v>
+        <v>2.67</v>
       </c>
       <c r="I7" t="n">
-        <v>0.496</v>
+        <v>0.298</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -9325,22 +9325,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>22464776</v>
+        <v>23719591</v>
       </c>
       <c r="E8" t="n">
-        <v>22506115</v>
+        <v>23902649</v>
       </c>
       <c r="F8" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="G8" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="H8" t="n">
-        <v>0.18</v>
+        <v>0.77</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -9371,22 +9371,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-39427854</v>
+        <v>-45472221</v>
       </c>
       <c r="E9" t="n">
-        <v>-41444349</v>
+        <v>-46967609</v>
       </c>
       <c r="F9" t="n">
+        <v>-3.79</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-3.91</v>
+      </c>
+      <c r="H9" t="n">
         <v>-3.29</v>
       </c>
-      <c r="G9" t="n">
-        <v>-3.45</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-5.11</v>
-      </c>
       <c r="I9" t="n">
-        <v>-0.168</v>
+        <v>-0.125</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -9417,22 +9417,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-22015440</v>
+        <v>-23887035</v>
       </c>
       <c r="E10" t="n">
-        <v>-22083377</v>
+        <v>-24112736</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.83</v>
+        <v>-1.99</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.84</v>
+        <v>-2.01</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.31</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.006</v>
+        <v>-0.019</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -9463,22 +9463,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>29776836</v>
+        <v>34903233</v>
       </c>
       <c r="E11" t="n">
-        <v>31280349</v>
+        <v>36118876</v>
       </c>
       <c r="F11" t="n">
-        <v>2.48</v>
+        <v>2.91</v>
       </c>
       <c r="G11" t="n">
-        <v>2.61</v>
+        <v>3.01</v>
       </c>
       <c r="H11" t="n">
-        <v>5.05</v>
+        <v>3.48</v>
       </c>
       <c r="I11" t="n">
-        <v>0.125</v>
+        <v>0.101</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -9509,22 +9509,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-2133251</v>
+        <v>-5286286</v>
       </c>
       <c r="E12" t="n">
-        <v>-2285263</v>
+        <v>-5590832</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.18</v>
+        <v>-0.44</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.19</v>
+        <v>-0.47</v>
       </c>
       <c r="H12" t="n">
-        <v>-7.13</v>
+        <v>-5.76</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.013</v>
+        <v>-0.025</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -9555,22 +9555,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-20024533</v>
+        <v>-21011285</v>
       </c>
       <c r="E13" t="n">
-        <v>-21006679</v>
+        <v>-21322875</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.67</v>
+        <v>-1.75</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.75</v>
+        <v>-1.78</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.9</v>
+        <v>-1.48</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.082</v>
+        <v>-0.026</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -9601,22 +9601,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1516111</v>
+        <v>1547548</v>
       </c>
       <c r="E14" t="n">
-        <v>-1355915</v>
+        <v>1857391</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.13</v>
+        <v>0.13</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.11</v>
+        <v>0.15</v>
       </c>
       <c r="H14" t="n">
-        <v>10.57</v>
+        <v>20.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.013</v>
+        <v>0.026</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -9647,22 +9647,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>20462070</v>
+        <v>21478251</v>
       </c>
       <c r="E15" t="n">
-        <v>21453113</v>
+        <v>21793286</v>
       </c>
       <c r="F15" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="G15" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="H15" t="n">
-        <v>4.84</v>
+        <v>1.47</v>
       </c>
       <c r="I15" t="n">
-        <v>0.083</v>
+        <v>0.026</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -9693,22 +9693,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-19388537</v>
+        <v>-17917160</v>
       </c>
       <c r="E16" t="n">
-        <v>-19292581</v>
+        <v>-17811471</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.62</v>
+        <v>-1.49</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.61</v>
+        <v>-1.48</v>
       </c>
       <c r="H16" t="n">
-        <v>0.49</v>
+        <v>0.59</v>
       </c>
       <c r="I16" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -9739,22 +9739,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>46689148</v>
+        <v>52242634</v>
       </c>
       <c r="E17" t="n">
-        <v>49011015</v>
+        <v>53627928</v>
       </c>
       <c r="F17" t="n">
-        <v>3.89</v>
+        <v>4.35</v>
       </c>
       <c r="G17" t="n">
-        <v>4.08</v>
+        <v>4.47</v>
       </c>
       <c r="H17" t="n">
-        <v>4.97</v>
+        <v>2.65</v>
       </c>
       <c r="I17" t="n">
-        <v>0.193</v>
+        <v>0.115</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
@@ -9831,7 +9831,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
@@ -9940,20 +9940,20 @@
         <v>1500000000</v>
       </c>
       <c r="E2" t="n">
-        <v>13.7484</v>
+        <v>13.7578</v>
       </c>
       <c r="F2" t="n">
-        <v>13.7484</v>
+        <v>13.7578</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="b">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.196292</v>
+        <v>1.19741</v>
       </c>
       <c r="J2" t="n">
-        <v>1.196292</v>
+        <v>1.19741</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -9982,20 +9982,20 @@
         <v>900000000</v>
       </c>
       <c r="E3" t="n">
-        <v>11.548</v>
+        <v>11.5485</v>
       </c>
       <c r="F3" t="n">
-        <v>11.548</v>
+        <v>11.5485</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.208217</v>
+        <v>1.208419</v>
       </c>
       <c r="J3" t="n">
-        <v>1.208217</v>
+        <v>1.208419</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -10024,20 +10024,20 @@
         <v>1000000000</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2525</v>
+        <v>6.3282</v>
       </c>
       <c r="F4" t="n">
-        <v>6.2525</v>
+        <v>6.3282</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="b">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1.040741</v>
+        <v>1.044642</v>
       </c>
       <c r="J4" t="n">
-        <v>1.040741</v>
+        <v>1.044642</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -10066,20 +10066,20 @@
         <v>2800000000</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7579</v>
+        <v>5.7529</v>
       </c>
       <c r="F5" t="n">
-        <v>5.7579</v>
+        <v>5.7529</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1.072203</v>
+        <v>1.071996</v>
       </c>
       <c r="J5" t="n">
-        <v>1.072203</v>
+        <v>1.071996</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -10108,20 +10108,20 @@
         <v>600000000</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1528</v>
+        <v>5.3336</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1528</v>
+        <v>5.3336</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1.037965</v>
+        <v>1.045279</v>
       </c>
       <c r="J6" t="n">
-        <v>1.037965</v>
+        <v>1.045279</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -10147,23 +10147,23 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1400000000</v>
+        <v>1500000000</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5974</v>
+        <v>4.8228</v>
       </c>
       <c r="F7" t="n">
-        <v>4.5974</v>
+        <v>4.8228</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.975513</v>
+        <v>0.994186</v>
       </c>
       <c r="J7" t="n">
-        <v>0.975513</v>
+        <v>0.994186</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="b">
@@ -10187,23 +10187,23 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>420000000</v>
+        <v>540000000</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5029</v>
+        <v>4.5041</v>
       </c>
       <c r="F8" t="n">
-        <v>4.5029</v>
+        <v>4.5041</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.122719</v>
+        <v>0.123995</v>
       </c>
       <c r="J8" t="n">
-        <v>0.122719</v>
+        <v>0.123995</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="b">
@@ -10227,25 +10227,27 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1200000000</v>
+        <v>1100000000</v>
       </c>
       <c r="E9" t="n">
-        <v>3.74</v>
+        <v>3.9212</v>
       </c>
       <c r="F9" t="n">
-        <v>3.74</v>
+        <v>3.9212</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.94935</v>
+        <v>1.008482</v>
       </c>
       <c r="J9" t="n">
-        <v>0.94935</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>1.008482</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
       <c r="L9" t="b">
         <v>1</v>
       </c>
@@ -10270,20 +10272,20 @@
         <v>200000000</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5616</v>
+        <v>3.7657</v>
       </c>
       <c r="F10" t="n">
-        <v>3.5616</v>
+        <v>3.7657</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1.000009</v>
+        <v>1.000005</v>
       </c>
       <c r="J10" t="n">
-        <v>1.000009</v>
+        <v>1.000005</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -10509,7 +10511,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3400000000</v>
+        <v>3100000000</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10629,23 +10631,23 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1800000000</v>
+        <v>2100000000</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3294</v>
+        <v>-3.3306</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.3294</v>
+        <v>-3.3306</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.983021</v>
+        <v>-0.983425</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.983021</v>
+        <v>-0.983425</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="b">
@@ -10672,20 +10674,20 @@
         <v>400000000</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.7091</v>
+        <v>-3.6932</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.7091</v>
+        <v>-3.6932</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.000008</v>
+        <v>-1.000007</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.000008</v>
+        <v>-1.000007</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -10711,23 +10713,23 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>420000000</v>
+        <v>540000000</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.889</v>
+        <v>-3.8885</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.889</v>
+        <v>-3.8885</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.103925</v>
+        <v>-0.101783</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.103925</v>
+        <v>-0.101783</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="b">
@@ -10754,20 +10756,20 @@
         <v>1200000000</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.924</v>
+        <v>-4.0073</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.924</v>
+        <v>-4.0073</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.005845</v>
+        <v>-1.006866</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.005845</v>
+        <v>-1.006866</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
